--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -3320,7 +3320,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Cancel, X and Escape dismiss the dialog without deactivating; clicking outside does not dismiss it</t>
+          <t>Cancel and X dismiss the Deactivate dialog; Escape and clicking outside do not</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3345,21 +3345,25 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1. Click the "Cancel" button; re-open and click the "X" close icon; re-open and press Escape.
-2. After each dismissal, check the staff member's active status.
-3. Re-open and click outside the dialog.</t>
+          <t>1. Click the "Cancel" button and watch the dialog; then re-open it.
+2. Click the "X" close icon and watch the dialog; then re-open it.
+3. Press the "Esc" key on the keyboard and watch the dialog.
+4. Re-open the dialog and click outside it (on the greyed-out background).
+5. After each action, check the staff member's active status.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon; it dismisses on Cancel, X, or Escape.
-2. Any dismissal leaves the staff member's active status unchanged.
-3. Clicking outside the dialog does NOT dismiss it.</t>
+          <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon.
+2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
+3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
+4. Clicking outside the dialog does NOT close it.
+5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R8</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R8)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3368,7 +3372,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>A valid submit shows the in-flight loading state with dismissals locked, then applies the change with assignments untouched</t>
+          <t>Valid submit locks the dialog, then deactivates keeping assignments</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3399,7 +3403,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and Cancel/X/Escape are all non-interactive during the request.
+          <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.</t>
@@ -3407,7 +3411,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -1427,7 +1427,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Location selection cascades through the contributor gate and never includes an inaccessible location</t>
+          <t>Location selection cascades; an inaccessible location's data is never included</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,19 +1455,21 @@
         <is>
           <t>1. Select only location Y.
 2. Look for rep A; read rep B's count, totals, and detail rows.
-3. Select "All Locations" and check whether any location-Z data appears.</t>
+3. Select "All Locations" and check whether any location-Z data appears.
+4. With "All Locations" active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
-3. "All Locations" means all locations the user can access — location Z's data is never included.</t>
+3. "All Locations" means all locations the user can access — location Z's data is never included.
+4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 21 S21-R3; S21-R4; S21-R5; §3</t>
+          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R3; S21-R4; S21-R5; §3 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1476,7 +1478,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>A single-location user still sees the filter with one selectable location and unchanged behavior</t>
+          <t>The Location filter is hidden for a user with access to only one location</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1501,18 +1503,19 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Open the report and open the location filter.</t>
+          <t>1. Open the report and look for the Location filter in the toolbar.
+2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. The filter is still shown, with one selectable location.
-2. Report behavior is unchanged from single-location use.</t>
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+2. For the user with access to two or more locations the Location filter IS shown.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 21 S21-N1</t>
+          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sales By Representative appears at the bottom of the Performance group and opens the report</t>
+          <t>Sales By Representative at the bottom of Performance group; titles correct</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -511,27 +511,28 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. You can see the other reports in the Performance group.
-3. You know (or note down) the current order of the Reports navigation entries before checking.</t>
+2. You can see the other reports in the Performance group.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and read the Performance group of the left-side navigation top to bottom.
-2. Compare the rest of the navigation entries with their order before this report was added.
-3. Click the "Sales By Representative" entry.</t>
+2. Click the "Sales By Representative" entry.
+3. Read the page title at the top of the report and the browser tab's title.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. "Sales By Representative" appears in the Performance group, at the BOTTOM of the group — the label is the full word "Representative," not a "Rep" shorthand.
-2. The addition is additive: no existing entry is moved, replaced, or reordered, and the relative order of every other navigation entry is unchanged.
-3. Selecting the entry opens the report in the main content area.</t>
+2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
+3. Selecting the entry opens the report in the main content area.
+4. The page title reads "Sales By Representative".
+5. The browser tab title reads "Sales By Representative - Report | ShopView".</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R1; S1-R2; S1-R3; S1-R4</t>
+          <t>specs/sbr-sales-by-representative.md Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -540,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Page title and browser tab title read Sales By Representative</t>
+          <t>The navigation entry's padding fits the full Sales By Representative label without crowding or truncation</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -560,24 +561,24 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. You have opened the Sales By Representative report.</t>
+          <t>1. You are on the Reports navigation with the entry visible.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Read the page title at the top of the report.
-2. Read the browser tab's title.</t>
+          <t>1. Look closely at the "Sales By Representative" entry's label against the entry's left and right edges.
+2. Compare its padding with the neighbouring entries.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. The page title reads "Sales By Representative".
-2. The browser tab title reads "Sales By Representative - Report | ShopView".</t>
+          <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
+2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R5; S1-R6</t>
+          <t>specs/sbr-sales-by-representative.md Story 1 S1-R7; §1 naming note</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -586,12 +587,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>The navigation entry's padding fits the full Sales By Representative label without crowding or truncation</t>
+          <t>Every user who can see any other Performance report also sees Sales By Representative</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBR — Access &amp; Navigation</t>
+          <t>SBR — Permissions</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -601,29 +602,28 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Reports navigation with the entry visible.</t>
+          <t>1. A test user exists whose role can see another Performance-group report (create/assign a ZZAUTOTEST role if needed; restore afterwards).
+2. You are signed in as that user.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Look closely at the "Sales By Representative" entry's label against the entry's left and right edges.
-2. Compare its padding with the neighbouring entries.</t>
+          <t>1. Open the Reports navigation and read the Performance group.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
-2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.</t>
+          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R7; §1 naming note</t>
+          <t>specs/sbr-sales-by-representative.md Story 1 S1-R1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -632,7 +632,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Every user who can see any other Performance report also sees Sales By Representative</t>
+          <t>A user without Reports access sees no Reports navigation, no export menu, and cannot reach the Export Reports dialog</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,73 +651,72 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1. A test user exists whose role can see another Performance-group report (create/assign a ZZAUTOTEST role if needed; restore afterwards).
-2. You are signed in as that user.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports navigation and read the Performance group.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>A user without Reports access sees no Reports navigation, no export menu, and cannot reach the Export Reports dialog</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Permissions</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has no Reports access (use/create a ZZAUTOTEST role; restore afterwards).
 2. You are signed in as that user.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Look for the Reports navigation.
 2. Try to open the report by direct link (address copied from a permitted session).
 3. Try to reach the Export Reports dialog.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Rep Assignments download are not reachable.</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>A user without staff-administration access cannot reach the sales-rep deactivation flow</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Permissions</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user without staff-administration access.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to reach staff administration and open a staff member for editing.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1</t>
+          <t>specs/sbr-sales-by-representative.md Story 13 S13-N1</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -726,89 +725,91 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>A user without staff-administration access cannot reach the sales-rep deactivation flow</t>
+          <t>Date range picker is in the toolbar and offers the standard presets plus Custom</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SBR — Permissions</t>
+          <t>SBR — Date Range Filter</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user without staff-administration access.</t>
+          <t>1. You are on the Sales By Representative report.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to reach staff administration and open a staff member for editing.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-N1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Date range picker is in the toolbar and offers the standard presets plus Custom</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Date Range Filter</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Sales By Representative report.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Find the date range picker in the report toolbar.
 2. Open it and read the options.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. A date range picker is visible in the report toolbar.
 2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option (removed by the 2026-07-16 spec round).</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 2 S2-R1; S2-R2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Custom range uses the date-picker dialog and holds the user to a 366-day maximum span</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Date Range Filter</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Sales By Representative report.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Pick "Custom" and select a start and end date within 366 days; apply.
+2. Pick "Custom" again and try to select a start-to-end span of more than 366 days (start and end dates inclusive).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. A custom range within the cap applies normally via the date-picker dialog.
+2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 2 S2-R1; S2-R2</t>
+          <t>specs/sbr-sales-by-representative.md Story 2 S2-R3; S2-R6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -817,7 +818,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Custom range uses the date-picker dialog and holds the user to a 366-day maximum span</t>
+          <t>An invoice is placed in the range by its own invoice date with inclusive endpoints, and the range shows in both PDF headers</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -837,300 +838,117 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Sales By Representative report.</t>
+          <t>1. ZZAUTOTEST invoices exist dated exactly ON the start date and exactly ON the end date of a custom range, plus one dated just outside it.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Pick "Custom" and select a start and end date within 366 days; apply.
-2. Pick "Custom" again and try to select a start-to-end span of more than 366 days (start and end dates inclusive).</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. A custom range within the cap applies normally via the date-picker dialog.
-2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 2 S2-R3; S2-R6</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Date range defaults to This Month and changing it re-fetches the report with a loading indicator</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Date Range Filter</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1. Your browser has no remembered settings for this report (first visit or cleared storage).</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the report and read the date range picker.
-2. Change the range to Last Month and watch the table.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1. On first load the date range defaults to "This Month."
-2. Changing the range re-fetches and re-renders the report; the standard loading indicator (centered spinner over the data area) shows during the fetch.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 2 S2-R4; S2-R7; Story 16 S16-R4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>An invoice is placed in the range by its own invoice date with inclusive endpoints, and the range shows in both PDF headers</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Date Range Filter</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1. ZZAUTOTEST invoices exist dated exactly ON the start date and exactly ON the end date of a custom range, plus one dated just outside it.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Set a custom range whose start and end dates equal those two invoice dates.
 2. Check which invoices appear (expand the owning rep).
 3. Download both PDFs (Summary and Expanded View) and read their header strips.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 2 S2-R5; S2-R8; §3</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Product Type dropdown offers exactly three options with Parts &amp; Service as the default</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Product Type: three options, Parts &amp; Service default, each option filters right</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>SBR — Product Type Filter</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1. A rep has both a P (parts) and an S (service) invoice in the range (seed ZZAUTOTEST data via the WO Sales Rep field).
+2. No remembered settings for this report (first visit or cleared storage), so the default can be read.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the "Product Type" dropdown in the toolbar; read its default value, then open it and read the options.
+2. Select "Parts only," expand the rep, and read the invoice numbers.
+3. Select "Service only" and read them again.
+4. Select "Parts &amp; Service."</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. The dropdown offers exactly three options: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" as the default on first load.
+2. "Parts only" includes only invoices whose number starts with P.
+3. "Service only" includes only invoices whose number starts with S.
+4. "Parts &amp; Service" applies no product-type filter — both appear again.
+5. Each change re-fetches and re-renders the report.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6; S3-R7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Status dropdown offers exactly four options with All Statuses as the default</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Invoice Status Filter</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with no remembered settings.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Find the "Product Type" dropdown in the toolbar and read its default value.
-2. Open it and read the options.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. A "Product Type" dropdown is visible in the toolbar.
-2. It offers exactly three options: "Parts &amp; Service," "Parts only," "Service only."
-3. "Parts &amp; Service" is the default on first load.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 3 S3-R1; S3-R2; S3-R3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Parts only includes only P invoices, Service only includes only S invoices, and Parts &amp; Service applies no filter</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Product Type Filter</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1. A rep has both a P (parts) and an S (service) invoice in the range (seed ZZAUTOTEST data via the WO Sales Rep field).</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Select "Parts only," expand the rep, and read the invoice numbers.
-2. Select "Service only" and read them again.
-3. Select "Parts &amp; Service."</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1. "Parts only" includes only invoices whose number starts with P.
-2. "Service only" includes only invoices whose number starts with S.
-3. "Parts &amp; Service" applies no product-type filter — both appear again.
-4. Each change re-fetches and re-renders the report.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 3 S3-R4; S3-R5; S3-R6; S3-R7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Product Type is part of the contributor gate: a rep with no matching invoice disappears and every metric narrows</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Product Type Filter</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1. Rep A has ONLY service invoices in range; rep B has both types (seed ZZAUTOTEST data).</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Select "Parts only."
-2. Look for rep A's row.
-3. Read rep B's (N) count, summary totals, detail rows, and the grand Totals indicator.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. Rep A disappears — a rep appears only with at least one matching invoice after this filter.
-2. Rep B's summary totals, invoice detail rows, the grand Totals indicator, and the (N) count all reflect only the matching (P) invoices.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 3 S3-R8; S3-N1</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Invoice Status dropdown offers exactly four options with All Statuses as the default</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Invoice Status Filter</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with no remembered settings.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Find the "Invoice Status" dropdown in the toolbar and read its default value.
 2. Open it and read the options.
 3. Change the selection and watch the table.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. An "Invoice Status" dropdown is visible in the toolbar.
 2. It offers exactly four options: "All Statuses," "Unpaid," "Partially Paid," "Paid."
@@ -1138,48 +956,48 @@
 4. Changing the selection re-fetches and re-renders the report.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 4 S4-R1; S4-R2; S4-R3; S4-R5</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Status filtering matches on the mapped display value: five system states collapse into Paid, Partially Paid and Unpaid</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>SBR — Invoice Status Filter</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST invoices exist under one rep covering the payment situations: fully paid; overpaid; prepaid with zero balance owed; prepaid with a balance still owed; partially paid; unpaid.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Filter to "Paid" and read which invoices appear.
 2. Filter to "Partially Paid" and read again.
 3. Filter to "Unpaid" and read again.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
 2. "Partially Paid" includes the partially-paid AND the prepaid-with-a-balance-owed invoices.
@@ -1187,271 +1005,183 @@
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 4 S4-R4; §3 payment-status mapping</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Invoice Status is part of the contributor gate and narrows every metric</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Filters compose: a rep appears only with an invoice matching ALL active filters</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>SBR — Invoice Status Filter</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1. Rep A has only Paid invoices in range; rep B has a mix (seed ZZAUTOTEST data).</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1. Filter to "Unpaid."
-2. Look for rep A; read rep B's count, totals, detail rows, and the grand Totals indicator.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1. Rep A disappears (no matching invoice).
-2. Rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the Unpaid invoices.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 4 S4-R6; S4-N1</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Filters compose: only invoices matching ALL active filters contribute anywhere</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1. ZZAUTOTEST invoices exist that each fail exactly one of: date range, product type, invoice status, location — plus one invoice matching all four.
+2. For the per-filter legs: rep A has only service invoices and rep B both types; rep C has only Paid invoices and rep D a mix (seed ZZAUTOTEST data).</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Set all four filters (a range, "Parts only," "Paid," one location) and read the rep rows, counts, detail rows, and the grand Totals indicator.
+2. Product Type leg: select "Parts only"; look for rep A and read rep B's (N) count, summary totals, detail rows, and the grand Totals indicator.
+3. Invoice Status leg: filter to "Unpaid"; look for rep C and read rep D's figures.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
+2. A rep appears only if at least one invoice matches all active filters.
+3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
+4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 4 S4-R7; S4-R6; S4-N1; Story 3 S3-R8; S3-N1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Money columns always show invoiced amounts, never the outstanding balance</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>SBR — Invoice Status Filter</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1. ZZAUTOTEST invoices exist that each fail exactly one of: date range, product type, invoice status, location — plus one invoice matching all four.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1. Set all four filters (a range, "Parts only," "Paid," one location).
-2. Read the rep rows, counts, detail rows, and the grand Totals indicator.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1. Only the invoice matching ALL active filters contributes — every metric reflects the intersection.
-2. A rep appears only if at least one invoice matches all of them.
-3. Each invoice failing any single filter contributes nothing anywhere.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 4 S4-R7</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Money columns always show invoiced amounts, never the outstanding balance</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Invoice Status Filter</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. A partially-paid ZZAUTOTEST invoice exists with a known full Subtotal and a known partial payment.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Filter to "Partially Paid," expand the owning rep, and read that invoice's money columns.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 4 S4-R8</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Location filter is the rightmost toolbar control, a multi-select with an All Locations option</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>SBR — Location Filter</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report as a user with access to two or more locations.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar controls left to right.
 2. Open the location filter and read its options.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 21 S21-R1; Story 18 S18-R7.2</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Location filter defaults to the user's currently active location only</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Location selection cascades; an inaccessible location's data is never included</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SBR — Location Filter</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1. Your browser has no remembered settings for this report.
-2. You are working in a known active location (the application's location switcher).</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the report and read the location filter's selection.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1. The filter defaults to the currently active location only — the default view is scoped to the one location you are working in.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 21 S21-R2</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Location selection cascades; an inaccessible location's data is never included</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Location Filter</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. Rep A has invoices only at location X; rep B at locations X and Y (seed ZZAUTOTEST data).
 2. The signed-in user has access to X and Y but not to a third location Z which also has data.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Select only location Y.
 2. Look for rep A; read rep B's count, totals, and detail rows.
@@ -1459,7 +1189,7 @@
 4. With "All Locations" active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
@@ -1467,94 +1197,94 @@
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R3; S21-R4; S21-R5; §3 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>The Location filter is hidden for a user with access to only one location</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>SBR — Location Filter</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user assigned to exactly one location.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and look for the Location filter in the toolbar.
 2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Contributors only: a rep row appears if and only if the rep has at least one non-reversed invoice matching all active filters</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. Rep A has invoices in the current filtered view; rep B (sales-rep toggle on) has NONE; rep C has only a reversed invoice (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the summary rows.
 2. Look for reps B and C.
 3. Read the count in parentheses after rep A's name.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
@@ -1562,98 +1292,100 @@
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Row layout: 12 columns in order, chevron plus rep name in the Date cell, blank identifier cells, bold summary vs regular detail rows</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Row layout: 12 columns in order, blanks in position, bold summary rows</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep expanded.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Read a rep summary row cell by cell.
-3. Compare the font weight of a summary row and a detail row.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+3. Compare the font weight of a summary row and a detail row.
+4. Look for any cell whose content has shifted into a neighbouring column or wrapped; check the desktop Totals row's leading cells.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. The columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns).
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
-4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 5 S5-R2; S5-R3; S5-R6; S5-R8; Story 6 S6-R4; Story 18 S18-R4</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
+5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>A toggled-off or deleted contributor still appears with credit intact, tagged (Inactive), named from the latest invoice snapshot when deleted</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. Rep A has matching invoices; you then turn rep A's sales-rep toggle OFF (restore afterwards).
 2. If a rep whose staff record was DELETED but who has invoices in range exists (or can be produced), note it for step 3.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Refresh the report and find rep A's row.
 2. Read the name, tag, metrics, and position in the A→Z order; try expanding the row.
 3. If a deleted-rep contributor exists, read that row's name and sort position.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
@@ -1661,284 +1393,236 @@
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 5 S5-R9; §3 Key Decisions; §4 Snapshot</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Column alignment is a hard invariant: every row renders exactly the report's column count with blanks in position</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Expanding a rep loads its invoices on demand with a brief row-level loading indicator and full detail-row contents</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with a rep expanded and the grand Totals row visible.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Compare a summary row and a detail row column by column against the headers.
-2. Look for any cell whose content has shifted into a neighbouring column or wrapped.
-3. Look at the desktop Totals row's leading cells.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>1. Every rep summary row and every invoice detail row renders exactly the report's column count in the declared left-to-right order.
-2. A cell with nothing to show is rendered blank in its position — never shifted or wrapped; a drifted row is a defect.
-3. Both forms of the grand Totals indicator are exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 5 S5-R10; S5-N2; Story 18 S18-R6a</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Expanding a rep loads its invoices on demand with a brief row-level loading indicator and full detail-row contents</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Rep Rows &amp; Tree</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. A rep with several matching invoices is on the report.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron in the rep's Date cell and watch the row.
 2. Read a detail row left to right.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R1; S6-R2; S6-R3; S6-E1</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Header chevron expands every visible rep in one action and its glyph tracks the expand/collapse state</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. Several reps are on the report, all collapsed.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Look at the header-row chevron's glyph.
 2. Click it; watch the rep rows and the glyph.
 3. Click it again.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R5; S6-R6</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Each invoice appears under exactly one rep or the Unassigned row, never more than one</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. A known ZZAUTOTEST invoice set exists across two reps plus at least one unassigned invoice; Show Unassigned is on.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Expand every rep and the Unassigned row.
 2. Search the expanded rows for each seeded invoice number.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R7; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Expansion survives filter and sort changes within the session, resets on reload, and a removed rep returns collapsed</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are on the report; one of them stops matching under a stricter filter you can apply and re-remove.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Expand both reps, then change the sort and a filter that keeps both matching; check the expansion.
 2. Apply the stricter filter that removes rep B, then remove it again; check rep B.
 3. Reload the page and check all rows.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R8; S6-N1; Story 23 S23-R2</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Detail rows order newest first with a numeric invoice-number tie-break where P sorts before S</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. One rep has invoices allowing the tie-breaks: two invoices on different dates; two on the same date with numeric parts like 999 and 1000; and if producible a P and an S invoice with the same numeric part on the same day (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep and read the detail rows top to bottom.
 2. Change the rep-row column sort and re-read the detail order.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
@@ -1946,424 +1630,335 @@
 4. This order is independent of the rep-row column sort (which reorders summary rows only).</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R9; Story 11 S11-R2</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Status column sits between Customer and Inv. Hrs and every detail row shows the mapped badge text</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Status badge between Customer and Inv. Hrs; every detail row shows mapped text</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBR — Payment Status Badge</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist covering paid, overpaid, prepaid (zero balance), prepaid (balance owed), partially paid, and unpaid.
 2. The owning rep is expanded.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Locate the Status column relative to its neighbours.
-2. Read the badge on each seeded invoice's detail row.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+2. Read the badge on each seeded invoice's detail row.
+3. Look at a badge's vertical position in its cell, read the Status cell on a rep summary row, and check the status is readable from the badge text alone.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The Status column sits between the Customer column and the Inv. Hrs column.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
-3. The mapping matches §3: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 8 S8-R1; S8-R2; S8-N1; §3 payment-status mapping</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+3. The mapping matches §3: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
+4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Badge colors use the application's canonical payment-status tokens in both light and dark mode</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBR — Payment Status Badge</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows with all three badge values are visible; you can switch to dark mode.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Read the color treatment of each badge in light mode and compare with the badges on the application's invoice list.
 2. Switch to dark mode and compare again.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 8 S8-R3; Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Badges are vertically centered, blank on summary rows, and carry their text as the accessible label</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Payment Status Badge</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1. A rep is expanded with badges visible.</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1. Look at a badge's vertical position within its cell.
-2. Read the Status cell on a rep summary row.
-3. Check that the status is readable from the badge text alone (not only its color).</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1. The badge is vertically centered within its cell.
-2. On rep summary rows the Status cell is blank.
-3. The badge's text ("Paid"/"Partially Paid"/"Unpaid") is the accessible label — status is never conveyed by color alone.</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 8 S8-R4; S8-R5; S8-R6; Story 18 S18-R6</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim and the value is hours invoiced minus hours worked, rounded half-up to one decimal</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST work order exists with known billed labor-line hours and known technician clocked (timesheet) hours, invoiced under a rep.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Expand the rep and read the invoice's Inv. Hrs value; recalculate by hand.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 9 S9-R1; S9-R2; §3</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Inv. Hrs shows +green, -red, or 0.0 default on every row type, with rollups computed from unrounded deltas</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Inv. Hrs: +green, -red, 0.0 default on every row; rollups from unrounded deltas</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1. Invoices exist under one rep with a positive, a negative, and a break-even labor delta (seed ZZAUTOTEST data).</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1. Invoices exist under one rep with a positive, a negative, and a break-even labor delta (seed ZZAUTOTEST data).
+2. If producible, an invoice whose delta is tiny (e.g., +0.04) and one with a small negative delta (e.g., -0.5) also exist.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Read the three detail rows' Inv. Hrs values and colors.
 2. Read the rep summary row's and the Totals row's Inv. Hrs.
-3. Recalculate the rollup as the rounded sum of the unrounded per-invoice deltas.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+3. Recalculate the rollup as the rounded sum of the unrounded per-invoice deltas.
+4. Read the tiny-delta and small-negative invoices' Inv. Hrs.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
-3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 9 S9-R3; S9-R4; S9-R5; S9-R6</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
+4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>No-labor-no-time invoices show 0.0 but clocked-yet-unbilled work shows its negative delta, never suppressed</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice with no labor and no clocked time exists, AND an invoice whose work order has clocked technician hours but no billed labor line (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Read the parts-only invoice's Inv. Hrs cell.
 2. Read the clocked-but-unbilled invoice's Inv. Hrs cell.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 9 S9-N1</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Edge: a delta that rounds to zero shows 0.0 in the default color, and negatives always use an explicit minus with one decimal</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Margin % renders to one decimal with a % sign, shows an em dash when Subtotal is zero or below, and is recomputed on every rollup</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>1. If producible, an invoice whose delta is tiny (e.g., +0.04) and one with a small negative delta (e.g., -0.5) exist.</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the tiny-delta invoice's Inv. Hrs.
-2. Read the small-negative invoice's Inv. Hrs.</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>1. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green.
-2. Negative values always use an explicit minus and one decimal (e.g., -0.5).</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 9 S9-E1; S9-E2</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Margin % renders to one decimal with a % sign, shows an em dash when Subtotal is zero or below, and is recomputed on every rollup</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Inv. Hrs &amp; Calculations</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. A rep has two invoices with clearly different Margin % values; if producible, a row with Subtotal ≤ 0 also exists.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on both detail rows and on the rep's summary row; recompute the summary value as (total Margin ÷ total Subtotal) × 100.
 2. Read the Subtotal ≤ 0 row's Margin % cell.
 3. If a negative-margin row exists, read its format.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 Margin % definition; Story 10 S10-R5</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Money columns use the standardized labels and definitions: Subtotal is pre-tax Labor plus Parts Invoiced, Margin is the two margins combined</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known billed labor, billed parts, labor cost, parts cost, and tax.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Read the money column headers.
 2. Read that invoice's row values and recalculate each by hand.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
@@ -2371,182 +1966,185 @@
 4. The same values appear everywhere the numbers show (screen, and later the exports).</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 definitions; §4 Terminology</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Negative dollar values render in accounting parentheses on screen, in money columns only</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. A row with a negative money value exists (e.g., a net credit/return invoice, or a negative Labor Margin from cost exceeding billed labor — seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Read the negative money cell.
 2. Read a negative Inv. Hrs cell and a negative Margin % cell for comparison.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 Key Decisions (accounting parentheses)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Half-up rounding applies at each stated precision and a totals cell may differ from the eye-summed rows by one last-decimal unit — expected</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Half-up rounding at each precision; totals may differ by one last-decimal unit</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>1. Several invoices with odd cent/decimal values sit under one rep (seed ZZAUTOTEST data with values like $10.005).</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1. Several invoices whose money values come from calculations that produce fractions of a cent sit under one rep — seed ZZAUTOTEST invoices whose amounts come from hours × rate or percentage-based lines that do not land on a whole cent (money fields themselves only take two decimals, so the sub-cent amounts must come from the math, not be typed in).</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Read the displayed per-invoice values, sum them by hand, and compare with the rep summary and Totals cells.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 rounding rule</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Subtotal is the rightmost column, pinned to the right edge, bold everywhere, on the row's own background</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Subtotal: rightmost, pinned right, bold everywhere; header row sticky on scroll</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data, narrow enough to force horizontal scrolling.</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with data, narrow enough to force horizontal scrolling.
+2. Enough rows exist to also force vertical scrolling.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Confirm nothing renders to the right of Subtotal on any row type.
 2. Scroll horizontally and watch the Subtotal column on summary and detail rows.
-3. Inspect the Subtotal weight on the header, a summary row, a detail row, and the Totals indicator; check the pinned cell's background.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+3. Inspect the Subtotal weight on the header, a summary row, a detail row, and the Totals indicator; check the pinned cell's background.
+4. Scroll down through the rows and watch the header row; scroll right and watch the Subtotal header cell.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column on every row type.
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
 3. Subtotal values are bold across the header, every summary row, every detail row, and the grand Totals indicator.
-4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-N1; Story 18 S18-R7.5</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
+5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Desktop Totals row merges the four identifier columns, aggregates every metric over the full filtered set, and sticks to the bottom</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. Desktop viewport (1024px or wider); several reps with known amounts are on the report; at least one rep is left collapsed.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the table and find the Totals row.
 2. Read its first cell and the per-metric cells.
@@ -2554,7 +2152,7 @@
 4. Empty the results with a no-data filter and look for the indicator; also watch during a re-fetch.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
@@ -2563,48 +2161,48 @@
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5; S10-N1; Story 16 S16-R4</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Mobile shows a simplified external totals bar below the table with Totals left and the grand Subtotal right</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data in a viewport below 1024px.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Find the totals bar and read it.
 2. Swipe the table horizontally and watch the bar.
 3. Scroll the page vertically and watch the bar.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
@@ -2612,179 +2210,133 @@
 4. It uses the white card surface with a thin top border.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5 (mobile); Story 17 S17-R4</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>The column-header row is sticky to the top during vertical scroll and the Subtotal header is sticky in both axes</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Subtotal &amp; Totals</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>1. Enough rows exist to force vertical scrolling; the window is narrow enough to also force horizontal scrolling.</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Scroll down through the rows and watch the header row.
-2. Scroll right and watch the Subtotal header cell.</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1. The column-header row stays stuck to the top during vertical scroll.
-2. The Subtotal header cell stays visible in BOTH axes — stuck to the top while scrolling down and pinned right while scrolling sideways.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 10 S10-R6</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>All eight financial columns are sortable; the identifier columns are not and the Date header carries the chevron instead</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. Several reps with differing values are on the report.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Click each financial column header in turn: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Click the Date, Invoice, Customer, and Status headers.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R1; S11-R6</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Default order is plain A to Z by display name, case-insensitive, with no active/inactive tiers</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. No remembered sort exists (first visit or cleared storage); contributing reps include an "(Inactive)"-tagged rep and mixed-case names.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the rep order top to bottom.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R4; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>First click sorts ascending with an indicator, second click descending, no third cleared state, and no header path back to A to Z</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. Several reps are on the report in the A→Z default.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Click the Subtotal header once and read the order and the direction indicator.
 2. Click it again.
@@ -2792,7 +2344,7 @@
 4. Try to get back to the A→Z order using only the column headers.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
@@ -2800,323 +2352,237 @@
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R5; Story 23 S23-R5</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders rep summary rows only; detail rows stay under their rep and the Unassigned row stays pinned on top</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. Show Unassigned is on with a populated Unassigned row; at least one rep is expanded.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a financial column.
 2. Read the Unassigned row's position, the expanded rep's detail rows, and their order.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R2; Story 22 S22-R4</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Equal sorted values keep the A to Z order as tie-break and an em-dash Margin % sorts as zero</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. Two reps have equal values in a sortable column; if producible, one rep shows "—" in Margin % (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Sort by the column where the two reps tie and read their relative order.
 2. Sort by Margin % ascending and locate the "—" rep.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R7</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>With only one rep row the sort affordances are present but produce no observable change</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Sorting</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>1. Filters are set so exactly one rep row is visible.</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>1. Click several financial column headers.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1. The sort affordances are present and the direction indicator updates, but the single row's position does not change.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 11 S11-N1</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Invoice number on a detail row navigates the current tab to the underlying work order or parts sale</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Detail-row invoice number and customer name links navigate in the current tab</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. A rep row is expanded with at least one S and one P invoice visible.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Click a service invoice's number link and note the destination and tab.
-2. Go back, then click a parts invoice's number link.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+2. Go back, then click a parts invoice's number link.
+3. Click the customer name on a detail row.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number is a clickable link.
-2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Customer name on a detail row navigates the current tab to the customer's record</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
+3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2; S12-R3</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Browser back from a drilldown restores ALL report state including expansion and scroll, without a full reload</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>1. A rep row is expanded with detail rows visible.</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Click the customer name on a detail row.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>1. The customer name is a clickable link that navigates the current tab to the customer's record.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 12 S12-R3</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Browser back from a drilldown restores ALL report state including expansion and scroll, without a full reload</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Links &amp; Navigation</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. Non-default filters are set (date range, product type, invoice status, location, Show Unassigned on), two reps are expanded, and the table is scrolled partway down.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Click an invoice link, then press the browser back button; check every piece of state.
 2. Repeat via a customer-name link.
 3. Watch whether the report performs a full reload on back.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R3a; Story 23 S23-R2</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Link styling: theme-primary invoice links and body-colored customer links, hover/focus underline, never browser-purple, in both modes</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows are visible; at least one invoice and one customer link have been clicked earlier; you can switch to dark mode.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Inspect an invoice-number link at rest, on hover, on keyboard focus, and after a click.
 2. Inspect a customer-name link the same way.
 3. Switch to dark mode and repeat.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
@@ -3124,179 +2590,135 @@
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R4; S12-R5; S12-R6; S12-N3</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>An unavailable invoice or customer destination shows the standard not-found/access-denied state and back still returns</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with detail rows visible; in another session the target invoice is reversed/deleted (and, for the customer leg, a customer record is made unavailable if the app allows).</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Without refreshing, click the now-unavailable invoice's link; read the destination, then press back.
 2. If producible, repeat for an unavailable customer record.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-N1; S12-N2</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Deactivating a sales rep with no customer assignments applies silently with no dialog</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Deactivating a rep with assignments opens the Deactivate dialog with the counted, pluralized headline and reassurance line, trapping focus</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1. A ZZAUTOTEST staff member is active with the sales-rep toggle ON and NO customers assigned to them as sales rep.</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. Edit the staff member in staff administration and toggle their active status off.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1. The deactivation applies silently — no warning dialog is shown.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R2</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Deactivating a rep with assignments opens the Deactivate dialog with the counted, pluralized headline and reassurance line, trapping focus</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Staff Deactivation</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST rep "A" is active, toggle on, and assigned as sales rep to exactly 1 customer; ZZAUTOTEST rep "B" likewise to 3 customers.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Toggle rep B's active status off and read the dialog before confirming anything.
 2. Press Tab repeatedly and watch where focus goes; dismiss and watch where focus returns.
 3. Repeat step 1 for rep A (1 customer) and read the headline's noun.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales rep on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R3; S13-R4; S13-R12</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Type-YES gate: auto-focused input, case-insensitive whitespace-tolerant match, disabled-button tooltip, Enter submits</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Read the instruction text and check which element holds focus.
 2. Hover the disabled "Deactivate" button and read the tooltip.
@@ -3304,7 +2726,7 @@
 4. With a valid entry, press Enter.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
@@ -3312,41 +2734,41 @@
 4. Pressing Enter while valid submits.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R6; S13-R7</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Cancel and X dismiss the Deactivate dialog; Escape and clicking outside do not</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Click the "Cancel" button and watch the dialog; then re-open it.
 2. Click the "X" close icon and watch the dialog; then re-open it.
@@ -3355,7 +2777,7 @@
 5. After each action, check the staff member's active status.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
@@ -3364,47 +2786,47 @@
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Valid submit locks the dialog, then deactivates keeping assignments</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a ZZAUTOTEST rep with known customer assignments.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Type YES and submit; during the request try Cancel, X, and Escape.
 2. After success, check the staff member's status and each previously assigned customer's Sales Rep.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
@@ -3412,968 +2834,838 @@
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>After deactivation the sales-rep toggle is unchanged, the Assignments CSV shows Rep is active? = No, and report credit stays intact</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST rep with assignments AND matching invoices was just deactivated via the dialog flow.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Re-open the staff member and read the sales-rep toggle.
 2. Download the Sales Rep Assignments CSV and read the rep's rows.
 3. Open the report and find the rep's row.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The sales-rep toggle state is unchanged by the deactivation flow.
 2. In the Sales Rep Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-rep TOGGLE is off (a separate flag from staff-active status).</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>No dialog when the toggle is off, when the member is already inactive, or on reactivation — assignments resurface immediately</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>No dialog: toggle off, no assignments, already inactive, or reactivation</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>1. ZZAUTOTEST staff member X is active WITHOUT the sales-rep toggle; ZZAUTOTEST rep Y (with assignments) is currently inactive.</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1. ZZAUTOTEST staff member X is active WITHOUT the sales-rep toggle; ZZAUTOTEST rep Y (with assignments) is currently inactive; ZZAUTOTEST rep Z is active with the sales-rep toggle ON and NO customers assigned.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate X and watch for a dialog.
-2. Reactivate rep Y via the standard toggle and watch for a dialog; check Y's customer assignments afterwards.</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
+2. Reactivate rep Y via the standard toggle and watch for a dialog; check Y's customer assignments afterwards.
+3. Deactivate rep Z (sales-rep toggle on, no assignments) and watch for a dialog.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. For a staff member without the sales-rep toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
-3. After reactivation the assignments re-surface immediately with no extra action.</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-N2; S13-N3; S13-E3</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+3. After reactivation the assignments re-surface immediately with no extra action.
+4. Deactivating a sales rep with NO customer assignments applies silently — no warning dialog.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 13 S13-R2; S13-N2; S13-N3; S13-E3</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>A server-side deactivation failure shows the canonical error toast, leaves the status unchanged, and clears the input on the next open</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments; you can force the request to fail (go offline just before submitting).</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Type YES, force the failure condition, and submit.
 2. Read the toast; check the staff member's active status.
 3. Dismiss, re-open the dialog, and look at the confirmation input.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "Ooooops! An error occured" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-N5; §7</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>If the assignment pre-check fails, the warning dialog still opens — without the count headline — and never silently deactivates</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-rep toggle on.
 2. You can force the pre-deactivation assignment check to fail (for example, cut the network exactly when toggling active off) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Toggle the staff member's active status off while forcing the check to fail.
 2. Read the dialog that opens.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-N4</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned sits between the column selector and the date picker, is off by default, and while off unassigned invoices contribute nothing</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. No remembered settings; at least one matching invoice with NO assigned rep exists (seed via a WO with no Sales Rep whose customer also has no rep).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Find the "Show Unassigned" toggle in the toolbar and note its position and default state.
 2. With it off, look for an Unassigned row and check the grand Totals against the rep rows only.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 22 S22-R1; S22-R2; Story 18 S18-R7.2</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Turning Show Unassigned on adds a single Unassigned row pinned to the top and recomputes the grand Totals</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Show Unassigned adds one top-pinned Unassigned row that acts like a rep row</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. Matching unassigned invoices exist; the grand Totals with the toggle off are noted.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Turn "Show Unassigned" on and read the new row and its position.
 2. Read the grand Totals indicator.
-3. Turn the toggle off again.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
+3. Read the Unassigned row's columns and (N) count, click its chevron, and look for any "(Inactive)" tag.
+4. Turn the toggle off again.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
-3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R6</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>The Unassigned row behaves like a rep row — count, expandable, in the Totals — and never carries an (Inactive) tag</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
+4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>No empty Unassigned row is ever rendered, and toggling off while expanded removes the row which returns collapsed</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>1. Show Unassigned is on with a populated Unassigned row.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the Unassigned row's columns and (N) count.
-2. Click its chevron.
-3. Look for any "(Inactive)" tag.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>1. The Unassigned row shows the same metric columns and the (N) count like any rep summary row.
-2. It is expandable to its contributing invoices.
-3. It is included in the grand Totals indicator.
-4. It never carries an "(Inactive)" tag.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 22 S22-R5; Story 6 S6-R1</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>No empty Unassigned row is ever rendered, and toggling off while expanded removes the row which returns collapsed</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Show Unassigned</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: a filter set with NO matching unassigned invoices (but some rep rows).
 2. Scenario B: the Unassigned row is populated and expanded.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: turn Show Unassigned on and look for the row; then narrow so no reps match either and read the table.
 2. Scenario B: with the Unassigned row expanded, turn the toggle off, then back on.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 22 S22-N1; Story 6 S6-N2</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Column selector opens a dropdown of the seven metric columns with toggle switches, all visible on first visit</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Column selector: seven metric toggles; five always-on columns cannot be hidden</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. No remembered column preference exists (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Click the column selector button in the toolbar.
 2. Read the toggle list.
-3. Check the table's visible columns.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
+3. Check the table's visible columns.
+4. Look for Date, Invoice, Customer, Status, or Subtotal in the toggle list.
+5. Hide all seven metric columns and read the table and the grand Totals indicator.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
-2. On first visit all seven metric columns are visible.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R6</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>The five always-visible columns do not appear in the dropdown and cannot be hidden</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+2. On first visit all seven metric columns are visible.
+3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
+4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Toggling a column applies immediately across summary rows, detail rows and the grand Totals at once</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>1. The column selector dropdown is open.</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>1. Look for Date, Invoice, Customer, Status, or Subtotal in the toggle list.</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>1. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 20 S20-R3</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Toggling a column applies immediately across summary rows, detail rows and the grand Totals at once</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Column Selector</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. A rep is expanded and the Totals indicator is visible.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Toggle "Parts Margin" off and immediately check the summary rows, detail rows, and the Totals row.
 2. Toggle it back on.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R4; S20-R7</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Column visibility never affects the exports — all four downloads always include all metric columns</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. Several metric columns are hidden via the column selector.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Download all four exports (Summary PDF, Expanded View PDF, Summary CSV, Expanded View CSV).
 2. Check each file's columns.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R8</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Hiding the active sort column keeps the sort; showing it again reveals the sort indicator</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. The report is sorted by a metric column (e.g., Margin descending).</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Hide that column via the column selector and read the row order.
 2. Show the column again and look at its header.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R9</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>With all seven metric columns hidden the five always-on columns and the grand Totals still render — not an empty state</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Column Selector</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data.</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>1. Hide all seven metric columns.
-2. Read the table and the grand Totals indicator.</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>1. The table still renders the five always-on columns (Date, Invoice, Customer, Status, Subtotal) and the grand Totals indicator.
-2. No empty or error state is shown.</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 20 S20-N1</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>All filter and view settings are remembered per browser and restored before the first data fetch on the next visit</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Set a custom date range, "Parts only," "Paid," a specific location set, Show Unassigned on, hide two metric columns, and sort by Margin descending.
 2. Leave the report and return; also try a full page reload.
 3. Watch what data loads first.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R1; Story 20 S20-R5</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Expansion state and scroll position are not remembered and reset on reload</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are expanded and the table is scrolled partway.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Reload the page.
 2. Check the rows and the scroll position.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R2; §2 Out of Scope</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Restoration is defensive: a stale saved value falls back to its default and never causes an error or invalid request</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. Your saved settings include a location you are then un-assigned from (restore access afterwards).</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter, the data, and watch for any error.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R3</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>First visit or cleared browser storage yields the full set of defaults with no server-side profile</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>First visit or cleared storage yields all defaults; no server-side profile</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>1. You have distinctive saved settings, then clear the browser's site data (or use a fresh profile).</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. You have distinctive saved settings, then clear the browser's site data (or use a fresh profile).
+2. You are working in a known active location (the application's location switcher).</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read every setting.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your active location; Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1; Story 2 S2-R4; Story 21 S21-R2</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>The A to Z default is its own saved value: restoring a state with no financial sort returns to A to Z, not an arbitrary column</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You have never clicked a financial column header in this browser session/profile (the report is in the A→Z default).</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Change a few filters (no sort click), leave the report, and return.
 2. Read the row order and the headers.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R5; Story 11 S11-R4</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The ⋯ overflow menu lists exactly four download actions</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Sales By Representative report.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ (three-dot) button in the report toolbar — it is the first control in the toolbar's action cluster.
 2. Click it and read the menu entries top to bottom.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R1; Story 17 S17-R3 (position)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>All four downloads respect the active filters and the full result set — not the on-screen expansion — in the currently-active order</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps showing.
 2. Set a specific date range, Product Type, Invoice Status, and a location selection; turn Show Unassigned on.
@@ -4381,14 +3673,14 @@
 4. Leave at least one rep collapsed (do not expand it).</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Compare each file's rows against the on-screen result: which reps appear, which invoices are included, and the row order.
 3. Check where the Unassigned row sits in each file.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
@@ -4396,49 +3688,49 @@
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Summary PDF: A4 header strip, one rolled-up row per rep, bold Subtotal, colored Inv. Hrs, and a recomputed grand totals row</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, one of them a toggled-off ("(Inactive)") contributor if one can be arranged.
 2. A date range is selected.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (PDF)" from the ⋯ menu and open the file.
 2. Read the top of the first page, the column headers, one rep row, and the last row.
 3. Compare the totals row's Margin % against the child rows.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
@@ -4447,41 +3739,41 @@
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R3; S14-R5; Story 2 S2-R5; §3 Margin % definition</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF: one page-block per rep with its own header strip, per-invoice table, per-rep totals row, and no grand totals</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (PDF)" from the ⋯ menu and open the file.
 2. Check how each rep's section starts and what its table contains.
@@ -4489,7 +3781,7 @@
 4. Compare the order of one rep's invoices against the on-screen expanded order.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
@@ -4499,280 +3791,233 @@
 6. There is NO grand-totals row across all reps at the end of the document.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R6; S14-R8; Story 6 S6-R9</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF truncates invoice numbers longer than 18 characters; on screen they are never truncated</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. At least one invoice in the current view has an invoice number LONGER than 18 characters, and one has a number of 18 characters or fewer (seed data if needed).</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep on screen and read both invoice numbers.
 2. Download the Expanded View PDF and read the same two invoice numbers.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R7</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>PDF footer on every page, default-logo fallback, and deterministic PDF filenames</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. For the fallback check: the organization has NO configured logo (clear it in settings if permitted, and restore afterward).</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs and note each saved file's name.
 2. Scroll through every page of both PDFs and read the footer.
 3. With the organization logo not configured, download a PDF again and look at the header strip's logo region.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
 3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R4; S14-R3a; S14-R11</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag, and omit the on-screen (N) count</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. The current view includes at least one negative money value (for example, a net-credit/return invoice — seed one if needed) and, if arrangeable, one toggled-off "(Inactive)" contributor.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs.
 2. Find the negative money value in each and read how it is written.
 3. Read the rep names in both PDFs.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R9; S14-R10</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>PDF body font size adapts to the longest positive dollar value on the four-tier scale, with fixed column widths</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>PDF body font steps down as the longest dollar value grows; no overflow</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the Summary PDF for a view whose longest positive dollar value is 9 characters or fewer; note the body text size.
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the Summary PDF for a view whose longest positive dollar value is 9 characters or fewer; note the body text size (a relative comparison across files is enough).
 2. Repeat for views whose longest positive value is 10, 11, and 12-or-more characters (as far as seedable).
 3. In each file, check whether any value overflows or wraps its column.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>1. The body font follows the tier scale by the longest formatted positive dollar value in the document (totals included): 9 characters or fewer → 11px; 10 characters → 10px; 11 characters → 9px; 12 or more → 8px. 8px is the floor and 11px the ceiling.
-2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows.
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
+2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R12; S14-R13</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Font tier edge rules: a longer negative shifts one tier smaller (clamped at 8px); a document with no positive dollar value stays at 11px</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Summary CSV: filename, UTF-8 BOM, verbatim headers in order, one row per rep, and the # Invoices / # Customers counts</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>1. You can produce a view where a negative value's parenthesized rendering is LONGER than the largest positive value, and (separately) a view with no positive dollar value at all (for example, the empty export or an all-negative result).</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>1. Download a PDF for the view whose longest value is a parenthesized negative longer than any positive; note the body size against the positive value's own tier.
-2. Download a PDF for a view with zero matching invoices (or all-negative values); note the body size.</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>1. When a negative's parenthesized rendering is longer than the largest positive, the base tier shifts ONE step smaller than the positive value's tier, clamped at the 8px floor (already-8px stays 8px).
-2. With no positive dollar value in the document, the base tier is the 11px ceiling and the negative shift does not apply — the tier stays 11px.
-3. In all cases the fixed column widths prevent overflow.</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R14; S14-R12 (no-positive rule)</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Summary CSV: filename, UTF-8 BOM, verbatim headers in order, one row per rep, and the # Invoices / # Customers counts</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Exports</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing; one rep has invoices for the same customer more than once (to check de-duplication).</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
@@ -4780,7 +4025,7 @@
 4. For one rep, compare "# Invoices" with the on-screen (N) count, and "# Customers" with the number of DISTINCT customers across that rep's matching invoices.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
 2. The headers, in order, are exactly: Sales Rep, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
@@ -4789,95 +4034,95 @@
 5. The CSV has NO totals row.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R15; S14-R18</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Expanded CSV: filename, verbatim headers including the three hours columns, one row per invoice flattened across reps</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
 3. Compare the rows against the on-screen invoices (all reps, expanded).</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
 2. The headers, in order, are exactly: Sales Rep, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R16</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>CSV cell formatting: plain re-pivotable numbers, signed Inv. Hrs, Margin % empty when undefined, (Inactive) in the name, no (N)</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded both report CSVs from a view that includes a negative money value, a rep whose Margin % shows "—" on screen (Subtotal ≤ 0), and an "(Inactive)" contributor (seed what is missing).</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Open each CSV in a text editor (not a spreadsheet).
 2. Read a money cell, the negative value's cell, an Inv. Hrs cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Rep" cell.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
@@ -4886,41 +4131,41 @@
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers)</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>The Unassigned row appears in all four downloads when Show Unassigned is on, and in none of them when it is off</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set includes at least one invoice with no assigned sales rep (seed one if needed).</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Turn Show Unassigned ON and download all four files.
 2. Find the Unassigned entry in each file.
@@ -4928,149 +4173,149 @@
 4. Search each file for the unassigned invoices.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Rep" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Rep" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R19; Story 22 S22-R2; S22-R4</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>A failed download shows the canonical error toast, and a generating download shows a non-interactive loading state</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a PDF download and watch the menu action while the file is being generated.
 2. Force a failure on a download (PDF or CSV) and read the toast.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-N1; S14-N2; S14-E1; §7</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>An Expanded View PDF over the 10,000-row cap is refused with the specific too-large message — no truncated file</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. A filter set exists (or can be seeded) whose invoice detail rows exceed 10,000 — if this volume cannot be produced in the environment, mark Blocked-Env with the reason.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Apply the over-cap filter set.
 2. Choose "Download Expanded View (PDF)" and read the toast.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This export is too large to generate. Narrow the date range or filters and try again." (persists 120 seconds or until dismissed).
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E2; §7</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>An empty-data export still generates: zeroed Summary PDF totals, header-strip-only Expanded PDF, header-row-only CSVs</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set matches ZERO invoices (for example, a date range with no activity) — the report shows its empty state.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Open each and inspect its contents.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
@@ -5079,139 +4324,139 @@
 5. No special "empty" treatment or message appears inside the files.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E3</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>The Export Report dialog's Report Name dropdown includes "Sales Rep Assignments" at the bottom, hiding the date picker and showing the snapshot note</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Reports access.
 2. Note the current order of the Report Name dropdown entries before checking.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. In the Reports left sidebar, under the Accounting header, click the "Export Reports" entry — a dialog titled "Export Report" opens.
 2. Open the Report Name dropdown and read the list top to bottom.
 3. Select "Sales Rep Assignments" and look at the dialog body.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. "Sales Rep Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
 3. The dialog shows the note: "Snapshot of current sales rep assignments. Both active and inactive reps with assignments are listed."</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R1; S15-R2</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Exporting Sales Rep Assignments downloads sales-rep-assignments.csv with the verbatim headers and shows the success toast</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer in the organization has an assigned sales rep.
 2. The Export Report dialog is open with "Sales Rep Assignments" selected.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Click the Export action.
 2. Note the saved file's name and read the toast.
 3. Open the file in a text editor and read the header row.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as "sales-rep-assignments.csv".
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Rep, Rep is active?.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R3; S15-R4; §7</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>The Assignments CSV holds one row per customer with an assigned rep, sorted customer A→Z then rep A→Z; unassigned customers are excluded</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. The organization has several customers with assigned reps and at least one customer with NO assigned rep (seed as needed).</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Rep Assignments CSV.
 2. Count the rows against the customers with assigned reps.
@@ -5219,293 +4464,249 @@
 4. Read the row order.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. Every customer with an assigned sales rep produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R5; S15-R7; S15-R10</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>"Rep is active?" tracks the staff-active status (Yes/No), not the sales-rep toggle</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Arrange (and afterward restore): one assigned rep whose staff record is ACTIVE but whose sales-rep toggle is OFF, and one assigned rep whose staff record is INACTIVE but whose toggle is ON.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Rep Assignments CSV.
 2. Read the "Rep is active?" value on both reps' customer rows.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R6; Story 13 S13-R11</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Legacy robustness: a customer whose rep's staff record was deleted still exports one row from the customer-side stored name, marked No</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose assigned rep's staff record has been cleared or deleted while the customer still references it (seed and delete a throwaway ZZAUTOTEST rep if needed).</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Rep Assignments CSV.
 2. Find that customer's row and read its "Sales Rep" and "Rep is active?" cells.
 3. If two customers carry different stored name spellings for the same underlying rep, compare their rows.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Rep" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R8; S15-R9</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Assignments export failure and nothing-to-export paths use the Export dialog's own messages</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. For the empty path: no customer in the organization has an assigned rep (or use a state where the export yields zero rows).
 2. For the failure path: you can force a generation failure (for example, cut the network on Export) — if not forceable, mark that step Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, select "Sales Rep Assignments" in the Export Report dialog and click Export.
 2. Read the dialog warning and inspect any downloaded file.
 3. Force a generation failure and read the toast.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R11; S15-N2; §7</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>The empty state shows "No sales activity matches the current filters." with no grand Totals — including when no rep was ever credited</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Empty state: verbatim message, no grand Totals, toolbar stays interactive</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter set that matches no invoices for any rep (for example, a date range with no activity), with Show Unassigned OFF or with no matching unassigned invoices either.
 2. Read the data area and look for the grand Totals indicator.
-3. If checkable: view an organization/location state where NO staff member has ever been credited with an invoice, and compare the message.</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
+3. If checkable: view an organization/location state where NO staff member has ever been credited with an invoice, and compare the message.
+4. Look at the toolbar, then change the date range to a period WITH activity.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
 3. The same message appears when no staff member has ever been credited — there is no separate "no reps configured" message; the report is contributor-driven.
-4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-N1; §7</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>The toolbar stays visible and interactive in the empty state</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
+4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
+5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-R3; S16-N1; §7</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Loading shows a centered spinner over the data area, hides the Totals, keeps the toolbar interactive, and never flashes a blank table</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>1. The report is showing its empty state (no matching invoices).</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>1. Look at the toolbar.
-2. Change the date range to a period WITH activity.</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>1. In the empty state, the toolbar — the filters, the column selector, and the ⋯ exports — stays visible and interactive.
-2. Widening the date range from the empty state re-fetches and renders the matching reps normally.</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 16 S16-R3</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Loading shows a centered spinner over the data area, hides the Totals, keeps the toolbar interactive, and never flashes a blank table</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Loading, Empty &amp; Error States</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Reload the report and watch the data area during the initial load.
 2. Change a filter and watch the data area during the re-fetch.
 3. While loading, try to interact with the toolbar.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
@@ -5513,238 +4714,238 @@
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R4</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>A load failure shows the inline "Couldn't load the report. Please try again." message with a working Retry, keeping the filters</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Set several non-default filters.
 2. Force a load/re-fetch failure and read the data area.
 3. Restore the network and click "Retry".</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R5; §7</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; below 1024px the controls stack vertically with the ⋯ button wrapped above</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. Open the report on a phone-sized viewport (real device or browser device emulation, width under 1024px).</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Find and operate each toolbar control by touch: the ⋯ exports, the column selector, the Show Unassigned toggle, the date range picker, Product Type, Invoice Status, and Location.
 2. Look at how the controls are laid out.
 3. Widen the viewport to 1024px or more and compare.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R1; S17-R2; S17-R3</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>On a phone the table scrolls sideways with Subtotal pinned, the totals bar sits outside the scroll area, and the chevrons work on touch</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a phone-sized viewport (under 1024px) with at least one rep row.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the data table sideways and watch the Subtotal column.
 2. Look below the table for the totals bar and swipe the table again.
 3. Tap a rep row's chevron.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Touch targets are at least 44×44 px and touch users get no hover-only tooltips — the icons carry accessible names instead</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a touch device or touch emulation (under 1024px).</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Measure (device emulation ruler/inspector) the touch targets of a row chevron, the Show Unassigned toggle, the ⋯ button, and — via the staff deactivation dialog if opened — the dialog's X.
 2. Tap-and-hold the icon controls and watch for tooltips.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R6; S17-N1; Story 18 S18-R9</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Layout conformance: white toolbar with the specified padding and alignment, blue-grey page, separator line, edge-to-edge white table</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a desktop browser (light mode) with data showing.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar's surface, padding, and how the title and the rightmost control line up with the table columns.
 2. Look at the page background around the data area, the line between the toolbar and the column headers, and the table's side edges.
 3. Look at the header cells, the body cells, the pinned Subtotal cells, and the grand Totals indicator's surface.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a solid white background with padding 32px top / 24px bottom / 2rem left and right; the title's left edge aligns with the leftmost data column, and the rightmost toolbar control (the Location filter) aligns its right edge with the rightmost data column.
 2. The data area sits on the standard blue-grey page background with ZERO horizontal page padding — the toolbar and table run edge-to-edge against the side navigation.
@@ -5753,41 +4954,41 @@
 5. Row types are differentiated by font weight and color, not background color. These rules apply unconditionally whenever the report is rendered.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Dark mode: page, toolbar, table, and Totals switch to dark equivalents; badges and Inv. Hrs stay legible; PDFs stay light</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing, including at least one expanded rep (badges visible) and non-zero Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page, toolbar, header, body cells, and the grand Totals indicator.
@@ -5795,7 +4996,7 @@
 4. Download a PDF while in dark mode and open it.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
@@ -5803,47 +5004,47 @@
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Every icon-only control carries its specified accessible name</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the accessible name of: the ⋯ exports button, the column selector button, one rep row's chevron (collapsed, then expanded), and the header chevron.
 2. Open the staff deactivation dialog (Story 13 flow) and inspect its X close icon.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
@@ -5852,135 +5053,135 @@
 5. Dialog X = "Close".</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R9</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Chevrons and sortable headers are keyboard-operable and expose their expanded/sort state to assistive technology</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Tab to a rep row's chevron; press Enter, then Space.
 2. Tab to a financial column header; press Enter, then Space.
 3. Inspect what state each control exposes to assistive technology.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R10</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>The subdued grey of the (N) count and (Inactive) tag meets WCAG AA contrast, and no information is conveyed by color alone</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a rep row showing a (N) count and — if arrangeable — an "(Inactive)" tag; a contrast-checking tool is available.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Measure the contrast ratio of the subdued-grey (N) count and "(Inactive)" tag against the white body surface in light mode, and against the dark surface in dark mode.
 2. Review how Inv. Hrs, the status badges, and the links convey their meaning.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. The subdued grey meets at least WCAG AA contrast (4.5:1 or better) against the body surface in BOTH modes — the reduced font size does not drop it below that ratio.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R11; S18-R12</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>The Sales Rep selector shows in the left panel on standard Work Orders and Part Sale WOs, and is hidden on imported WOs and in History mode</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You have: an open standard Work Order, an open Part Sale WO, an imported Work Order, and a way to view a WO in History mode.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Open the standard Work Order and look at the left panel.
 2. Open the Part Sale WO and look at the left panel.
@@ -5988,7 +5189,7 @@
 4. View a WO in History mode and look for the field.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The left panel includes a "Sales Rep" selector on the standard Work Order.
 2. The left panel includes the same "Sales Rep" selector on the Part Sale WO.
@@ -5996,190 +5197,190 @@
 4. The selector is NOT present in History mode.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R1; S19-N1</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>The Sales Rep selector offers only reps whose sales-rep toggle is currently on, and carries the accessible name "Sales Rep"</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member has the sales-rep toggle ON and at least one has it OFF (arrange and restore afterward).</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Open a Work Order and open the "Sales Rep" selector.
 2. Search the option list for both staff members.
 3. Inspect the selector's accessible name.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
 3. The selector carries the accessible name "Sales Rep".</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>A new Work Order or Part Sale WO opens with Sales Rep unassigned, and a change saves immediately with no Save step</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member is offered as a sales rep.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Create a new Work Order (mark it ZZAUTOTEST) and read the Sales Rep field before touching it.
 2. Select a rep in the field, then navigate away WITHOUT any explicit save and reopen the WO.
 3. Repeat the unassigned-open check on a new Part Sale WO.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The new Work Order opens with the Sales Rep field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Rep persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R3; S19-R4</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>The Sales Rep selector is read-only when the Work Order status is Invoiced or Paid</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. One Work Order is in "Invoiced" status and one is in "Paid" status (drive throwaway ZZAUTOTEST WOs into these states if needed).</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Open the Invoiced WO and try to change the Sales Rep field.
 2. Open the Paid WO and try the same.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. On the Invoiced WO the Sales Rep selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R5</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Invoice crediting snapshot: WO rep, else the customer's rep, else unassigned — and a later WO change never rewrites past invoices</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. Three throwaway ZZAUTOTEST setups: (a) a WO WITH a Sales Rep assigned; (b) a WO with NO rep whose customer HAS an assigned rep; (c) a WO with NO rep whose customer has NO assigned rep.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Invoice all three WOs.
 2. On the report (Show Unassigned on, filters covering the invoices), find each invoice and note which row it sits under.
 3. Go back to WO (a), change its Sales Rep to a different rep, and re-check the already-created invoice on the report.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. Invoice (a) is credited to the WO's Sales Rep.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
@@ -6187,350 +5388,350 @@
 4. Changing WO (a)'s Sales Rep afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>The customer record shows a single Sales Rep row ("Unassigned" when none), and a toggled-off bound rep shows "(Inactive)" in the WO selector</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. One customer HAS an assigned sales rep and one customer has NONE.
 2. A Work Order exists whose bound Sales Rep can have their toggle turned off (arrange and restore afterward).</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Open the assigned customer's record and read the left-panel sidebar.
 2. Open the unassigned customer's record and read the same row.
 3. Turn the bound rep's sales-rep toggle OFF, reopen the Work Order, and read the Sales Rep selector; then open its option list.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The customer record's left-panel sidebar shows a single "Sales Rep" row with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R7; S19-E1</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>A rep's invoice detail rows are fetched from the server only on the first expand, and are paginated per rep</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows, one with a large invoice count if seedable.
 2. The browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note which requests deliver the summary rows.
 2. Expand one rep and watch the network panel; collapse and re-expand it.
 3. If a rep has many invoices, scroll/page through its expanded detail rows.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R2</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Sorting is performed server-side: a header click re-fetches the rep summary rows in the requested order</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several rep rows; the network panel is open.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Click a financial column header and watch the network panel.
 2. Click the same header again (descending) and watch again.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R5</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>The grand totals are server-computed over the full filtered result set and delivered with the summary payload</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Load the report with everything collapsed and inspect the summary response and the grand Totals indicator.
 2. Compare the grand totals against the full filtered result (for example, via the Summary CSV), not just the loaded rows.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>All four exports are generated server-side against the active filters and sort — a genuine failure yields a toast, never a malformed file</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Trigger each of the four downloads and observe the export requests and responses.
 2. Compare the delivered files against the active filters and sort.
 3. If forceable, fail one export server-side and check what (if anything) downloads.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R2a; S14-N2; S14-E3</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>The Expanded View PDF's 10,000-row cap is enforced server-side BEFORE generation — a refusal, not a truncated file</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. A filter set producing more than 10,000 invoice detail rows exists or can be seeded — otherwise mark Blocked-Env with the reason.
 2. The network panel is open.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download Expanded View (PDF)" against the over-cap filter set and observe the export request/response.
 2. Check whether any file arrives.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E2</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Toggling a sales rep's active status off first runs a server pre-check returning the assigned-customer count and an assignments flag</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-rep toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
 2. The network panel is open.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. In staff administration, toggle that staff member's active status off and watch the network panel BEFORE the dialog appears.
 2. Read the pre-check response and compare it with the dialog's "{N} customer{s}" headline.
 3. Cancel the dialog (leave the staff member active).</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales rep, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales rep on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R4</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -1194,12 +1194,13 @@
           <t>1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
 3. "All Locations" means all locations the user can access — location Z's data is never included.
-4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
+4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R3; S21-R4; S21-R5; §3 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R3; S21-R4; S21-R5; §3 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins)) + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -3647,7 +3648,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>All four downloads respect the active filters and the full result set — not the on-screen expansion — in the currently-active order</t>
+          <t>All four downloads respect filters, full result set, and active order</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3685,12 +3686,13 @@
           <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
 3. Rep rows appear in the report's currently-active order — the active column sort if one is set, otherwise the A→Z default.
-4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.</t>
+4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
+5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales By Representative" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales By Representative" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -987,7 +987,8 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. ZZAUTOTEST invoices exist under one rep covering the payment situations: fully paid; overpaid; prepaid with zero balance owed; prepaid with a balance still owed; partially paid; unpaid.</t>
+          <t>1. ZZAUTOTEST invoices exist under one rep covering the payment situations: fully paid; overpaid; prepaid with zero balance owed; prepaid with a balance still owed; partially paid; unpaid.
+2. Seed the prepaid-with-zero-balance situation the realistic way: the customer pays a DEPOSIT up front that fully covers the work, so the invoice is created with nothing left to pay.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2070,31 +2071,79 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>A clock-record edit after invoicing updates Inv. Hrs; billed money stays put</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Inv. Hrs &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1. A ZZAUTOTEST invoiced (not reversed, not void) work order exists with billed labor and clocked technician hours, and its invoice row is visible under its rep in the report.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Note the invoice row's Inv. Hrs value and its money columns.
+2. Edit a technician clock record on that work order (change its length), or delete one.
+3. Reload the report and re-read the same invoice row.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
+2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
+3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>SV-8626 (specs/sbr-sales-by-representative.md §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>Subtotal: rightmost, pinned right, bold everywhere; header row sticky on scroll</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, narrow enough to force horizontal scrolling.
 2. Enough rows exist to also force vertical scrolling.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Confirm nothing renders to the right of Subtotal on any row type.
 2. Scroll horizontally and watch the Subtotal column on summary and detail rows.
@@ -2102,7 +2151,7 @@
 4. Scroll down through the rows and watch the header row; scroll right and watch the Subtotal header cell.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column on every row type.
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
@@ -2111,41 +2160,41 @@
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Desktop Totals row merges the four identifier columns, aggregates every metric over the full filtered set, and sticks to the bottom</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. Desktop viewport (1024px or wider); several reps with known amounts are on the report; at least one rep is left collapsed.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the table and find the Totals row.
 2. Read its first cell and the per-metric cells.
@@ -2153,7 +2202,7 @@
 4. Empty the results with a no-data filter and look for the indicator; also watch during a re-fetch.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
@@ -2162,48 +2211,48 @@
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5; S10-N1; Story 16 S16-R4</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Mobile shows a simplified external totals bar below the table with Totals left and the grand Subtotal right</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data in a viewport below 1024px.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Find the totals bar and read it.
 2. Swipe the table horizontally and watch the bar.
 3. Scroll the page vertically and watch the bar.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
@@ -2211,133 +2260,133 @@
 4. It uses the white card surface with a thin top border.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5 (mobile); Story 17 S17-R4</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>All eight financial columns are sortable; the identifier columns are not and the Date header carries the chevron instead</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. Several reps with differing values are on the report.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Click each financial column header in turn: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Click the Date, Invoice, Customer, and Status headers.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R1; S11-R6</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Default order is plain A to Z by display name, case-insensitive, with no active/inactive tiers</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. No remembered sort exists (first visit or cleared storage); contributing reps include an "(Inactive)"-tagged rep and mixed-case names.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the rep order top to bottom.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R4; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>First click sorts ascending with an indicator, second click descending, no third cleared state, and no header path back to A to Z</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. Several reps are on the report in the A→Z default.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Click the Subtotal header once and read the order and the direction indicator.
 2. Click it again.
@@ -2345,7 +2394,7 @@
 4. Try to get back to the A→Z order using only the column headers.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
@@ -2353,237 +2402,237 @@
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R5; Story 23 S23-R5</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders rep summary rows only; detail rows stay under their rep and the Unassigned row stays pinned on top</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. Show Unassigned is on with a populated Unassigned row; at least one rep is expanded.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a financial column.
 2. Read the Unassigned row's position, the expanded rep's detail rows, and their order.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R2; Story 22 S22-R4</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Equal sorted values keep the A to Z order as tie-break and an em-dash Margin % sorts as zero</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Two reps have equal values in a sortable column; if producible, one rep shows "—" in Margin % (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Sort by the column where the two reps tie and read their relative order.
 2. Sort by Margin % ascending and locate the "—" rep.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R7</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Detail-row invoice number and customer name links navigate in the current tab</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. A rep row is expanded with at least one S and one P invoice visible.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Click a service invoice's number link and note the destination and tab.
 2. Go back, then click a parts invoice's number link.
 3. Click the customer name on a detail row.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2; S12-R3</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Browser back from a drilldown restores ALL report state including expansion and scroll, without a full reload</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Non-default filters are set (date range, product type, invoice status, location, Show Unassigned on), two reps are expanded, and the table is scrolled partway down.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Click an invoice link, then press the browser back button; check every piece of state.
 2. Repeat via a customer-name link.
 3. Watch whether the report performs a full reload on back.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R3a; Story 23 S23-R2</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Link styling: theme-primary invoice links and body-colored customer links, hover/focus underline, never browser-purple, in both modes</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows are visible; at least one invoice and one customer link have been clicked earlier; you can switch to dark mode.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Inspect an invoice-number link at rest, on hover, on keyboard focus, and after a click.
 2. Inspect a customer-name link the same way.
 3. Switch to dark mode and repeat.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
@@ -2591,135 +2640,135 @@
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R4; S12-R5; S12-R6; S12-N3</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>An unavailable invoice or customer destination shows the standard not-found/access-denied state and back still returns</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with detail rows visible; in another session the target invoice is reversed/deleted (and, for the customer leg, a customer record is made unavailable if the app allows).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Without refreshing, click the now-unavailable invoice's link; read the destination, then press back.
 2. If producible, repeat for an unavailable customer record.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-N1; S12-N2</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Deactivating a rep with assignments opens the Deactivate dialog with the counted, pluralized headline and reassurance line, trapping focus</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST rep "A" is active, toggle on, and assigned as sales rep to exactly 1 customer; ZZAUTOTEST rep "B" likewise to 3 customers.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Toggle rep B's active status off and read the dialog before confirming anything.
 2. Press Tab repeatedly and watch where focus goes; dismiss and watch where focus returns.
 3. Repeat step 1 for rep A (1 customer) and read the headline's noun.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales rep on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R3; S13-R4; S13-R12</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Type-YES gate: auto-focused input, case-insensitive whitespace-tolerant match, disabled-button tooltip, Enter submits</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Read the instruction text and check which element holds focus.
 2. Hover the disabled "Deactivate" button and read the tooltip.
@@ -2727,7 +2776,7 @@
 4. With a valid entry, press Enter.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
@@ -2735,41 +2784,41 @@
 4. Pressing Enter while valid submits.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R6; S13-R7</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Cancel and X dismiss the Deactivate dialog; Escape and clicking outside do not</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Click the "Cancel" button and watch the dialog; then re-open it.
 2. Click the "X" close icon and watch the dialog; then re-open it.
@@ -2778,7 +2827,7 @@
 5. After each action, check the staff member's active status.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
@@ -2787,47 +2836,47 @@
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Valid submit locks the dialog, then deactivates keeping assignments</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a ZZAUTOTEST rep with known customer assignments.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Type YES and submit; during the request try Cancel, X, and Escape.
 2. After success, check the staff member's status and each previously assigned customer's Sales Rep.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
@@ -2835,96 +2884,96 @@
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>After deactivation the sales-rep toggle is unchanged, the Assignments CSV shows Rep is active? = No, and report credit stays intact</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST rep with assignments AND matching invoices was just deactivated via the dialog flow.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Re-open the staff member and read the sales-rep toggle.
 2. Download the Sales Rep Assignments CSV and read the rep's rows.
 3. Open the report and find the rep's row.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The sales-rep toggle state is unchanged by the deactivation flow.
 2. In the Sales Rep Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-rep TOGGLE is off (a separate flag from staff-active status).</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>No dialog: toggle off, no assignments, already inactive, or reactivation</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST staff member X is active WITHOUT the sales-rep toggle; ZZAUTOTEST rep Y (with assignments) is currently inactive; ZZAUTOTEST rep Z is active with the sales-rep toggle ON and NO customers assigned.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate X and watch for a dialog.
 2. Reactivate rep Y via the standard toggle and watch for a dialog; check Y's customer assignments afterwards.
 3. Deactivate rep Z (sales-rep toggle on, no assignments) and watch for a dialog.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. For a staff member without the sales-rep toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
@@ -2932,182 +2981,182 @@
 4. Deactivating a sales rep with NO customer assignments applies silently — no warning dialog.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R2; S13-N2; S13-N3; S13-E3</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>A server-side deactivation failure shows the canonical error toast, leaves the status unchanged, and clears the input on the next open</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments; you can force the request to fail (go offline just before submitting).</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Type YES, force the failure condition, and submit.
 2. Read the toast; check the staff member's active status.
 3. Dismiss, re-open the dialog, and look at the confirmation input.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "Ooooops! An error occured" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-N5; §7</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>If the assignment pre-check fails, the warning dialog still opens — without the count headline — and never silently deactivates</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-rep toggle on.
 2. You can force the pre-deactivation assignment check to fail (for example, cut the network exactly when toggling active off) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Toggle the staff member's active status off while forcing the check to fail.
 2. Read the dialog that opens.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-N4</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned sits between the column selector and the date picker, is off by default, and while off unassigned invoices contribute nothing</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. No remembered settings; at least one matching invoice with NO assigned rep exists (seed via a WO with no Sales Rep whose customer also has no rep).</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Find the "Show Unassigned" toggle in the toolbar and note its position and default state.
 2. With it off, look for an Unassigned row and check the grand Totals against the rep rows only.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 22 S22-R1; S22-R2; Story 18 S18-R7.2</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned adds one top-pinned Unassigned row that acts like a rep row</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. Matching unassigned invoices exist; the grand Totals with the toggle off are noted.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Turn "Show Unassigned" on and read the new row and its position.
 2. Read the grand Totals indicator.
@@ -3115,7 +3164,7 @@
 4. Turn the toggle off again.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
@@ -3123,88 +3172,88 @@
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>No empty Unassigned row is ever rendered, and toggling off while expanded removes the row which returns collapsed</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: a filter set with NO matching unassigned invoices (but some rep rows).
 2. Scenario B: the Unassigned row is populated and expanded.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: turn Show Unassigned on and look for the row; then narrow so no reps match either and read the table.
 2. Scenario B: with the Unassigned row expanded, turn the toggle off, then back on.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 22 S22-N1; Story 6 S6-N2</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Column selector: seven metric toggles; five always-on columns cannot be hidden</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. No remembered column preference exists (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Click the column selector button in the toolbar.
 2. Read the toggle list.
@@ -3213,7 +3262,7 @@
 5. Hide all seven metric columns and read the table and the grand Totals indicator.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
@@ -3221,452 +3270,452 @@
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Toggling a column applies immediately across summary rows, detail rows and the grand Totals at once</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. A rep is expanded and the Totals indicator is visible.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Toggle "Parts Margin" off and immediately check the summary rows, detail rows, and the Totals row.
 2. Toggle it back on.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R4; S20-R7</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Column visibility never affects the exports — all four downloads always include all metric columns</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. Several metric columns are hidden via the column selector.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download all four exports (Summary PDF, Expanded View PDF, Summary CSV, Expanded View CSV).
 2. Check each file's columns.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R8</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Hiding the active sort column keeps the sort; showing it again reveals the sort indicator</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. The report is sorted by a metric column (e.g., Margin descending).</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Hide that column via the column selector and read the row order.
 2. Show the column again and look at its header.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R9</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>All filter and view settings are remembered per browser and restored before the first data fetch on the next visit</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Set a custom date range, "Parts only," "Paid," a specific location set, Show Unassigned on, hide two metric columns, and sort by Margin descending.
 2. Leave the report and return; also try a full page reload.
 3. Watch what data loads first.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R1; Story 20 S20-R5</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Expansion state and scroll position are not remembered and reset on reload</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are expanded and the table is scrolled partway.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Reload the page.
 2. Check the rows and the scroll position.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R2; §2 Out of Scope</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Restoration is defensive: a stale saved value falls back to its default and never causes an error or invalid request</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. Your saved settings include a location you are then un-assigned from (restore access afterwards).</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter, the data, and watch for any error.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R3</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>First visit or cleared storage yields all defaults; no server-side profile</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You have distinctive saved settings, then clear the browser's site data (or use a fresh profile).
 2. You are working in a known active location (the application's location switcher).</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read every setting.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1; Story 2 S2-R4; Story 21 S21-R2</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The A to Z default is its own saved value: restoring a state with no financial sort returns to A to Z, not an arbitrary column</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You have never clicked a financial column header in this browser session/profile (the report is in the A→Z default).</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Change a few filters (no sort click), leave the report, and return.
 2. Read the row order and the headers.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R5; Story 11 S11-R4</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The ⋯ overflow menu lists exactly four download actions</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Sales By Representative report.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ (three-dot) button in the report toolbar — it is the first control in the toolbar's action cluster.
 2. Click it and read the menu entries top to bottom.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R1; Story 17 S17-R3 (position)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>All four downloads respect filters, full result set, and active order</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps showing.
 2. Set a specific date range, Product Type, Invoice Status, and a location selection; turn Show Unassigned on.
@@ -3674,14 +3723,14 @@
 4. Leave at least one rep collapsed (do not expand it).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Compare each file's rows against the on-screen result: which reps appear, which invoices are included, and the row order.
 3. Check where the Unassigned row sits in each file.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
@@ -3690,49 +3739,49 @@
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Summary PDF: A4 header strip, one rolled-up row per rep, bold Subtotal, colored Inv. Hrs, and a recomputed grand totals row</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, one of them a toggled-off ("(Inactive)") contributor if one can be arranged.
 2. A date range is selected.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (PDF)" from the ⋯ menu and open the file.
 2. Read the top of the first page, the column headers, one rep row, and the last row.
 3. Compare the totals row's Margin % against the child rows.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
@@ -3741,41 +3790,41 @@
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R3; S14-R5; Story 2 S2-R5; §3 Margin % definition</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF: one page-block per rep with its own header strip, per-invoice table, per-rep totals row, and no grand totals</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (PDF)" from the ⋯ menu and open the file.
 2. Check how each rep's section starts and what its table contains.
@@ -3783,7 +3832,7 @@
 4. Compare the order of one rep's invoices against the on-screen expanded order.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
@@ -3793,233 +3842,233 @@
 6. There is NO grand-totals row across all reps at the end of the document.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R6; S14-R8; Story 6 S6-R9</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF truncates invoice numbers longer than 18 characters; on screen they are never truncated</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. At least one invoice in the current view has an invoice number LONGER than 18 characters, and one has a number of 18 characters or fewer (seed data if needed).</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep on screen and read both invoice numbers.
 2. Download the Expanded View PDF and read the same two invoice numbers.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R7</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>PDF footer on every page, default-logo fallback, and deterministic PDF filenames</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. For the fallback check: the organization has NO configured logo (clear it in settings if permitted, and restore afterward).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs and note each saved file's name.
 2. Scroll through every page of both PDFs and read the footer.
 3. With the organization logo not configured, download a PDF again and look at the header strip's logo region.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
 3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R4; S14-R3a; S14-R11</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag, and omit the on-screen (N) count</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. The current view includes at least one negative money value (for example, a net-credit/return invoice — seed one if needed) and, if arrangeable, one toggled-off "(Inactive)" contributor.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs.
 2. Find the negative money value in each and read how it is written.
 3. Read the rep names in both PDFs.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R9; S14-R10</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>PDF body font steps down as the longest dollar value grows; no overflow</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Download the Summary PDF for a view whose longest positive dollar value is 9 characters or fewer; note the body text size (a relative comparison across files is enough).
 2. Repeat for views whose longest positive value is 10, 11, and 12-or-more characters (as far as seedable).
 3. In each file, check whether any value overflows or wraps its column.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R12; S14-R13</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Summary CSV: filename, UTF-8 BOM, verbatim headers in order, one row per rep, and the # Invoices / # Customers counts</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing; one rep has invoices for the same customer more than once (to check de-duplication).</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
@@ -4027,7 +4076,7 @@
 4. For one rep, compare "# Invoices" with the on-screen (N) count, and "# Customers" with the number of DISTINCT customers across that rep's matching invoices.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
 2. The headers, in order, are exactly: Sales Rep, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
@@ -4036,95 +4085,95 @@
 5. The CSV has NO totals row.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R15; S14-R18</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Expanded CSV: filename, verbatim headers including the three hours columns, one row per invoice flattened across reps</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
 3. Compare the rows against the on-screen invoices (all reps, expanded).</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
 2. The headers, in order, are exactly: Sales Rep, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R16</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>CSV cell formatting: plain re-pivotable numbers, signed Inv. Hrs, Margin % empty when undefined, (Inactive) in the name, no (N)</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded both report CSVs from a view that includes a negative money value, a rep whose Margin % shows "—" on screen (Subtotal ≤ 0), and an "(Inactive)" contributor (seed what is missing).</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Open each CSV in a text editor (not a spreadsheet).
 2. Read a money cell, the negative value's cell, an Inv. Hrs cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Rep" cell.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
@@ -4133,41 +4182,41 @@
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>The Unassigned row appears in all four downloads when Show Unassigned is on, and in none of them when it is off</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set includes at least one invoice with no assigned sales rep (seed one if needed).</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Turn Show Unassigned ON and download all four files.
 2. Find the Unassigned entry in each file.
@@ -4175,149 +4224,149 @@
 4. Search each file for the unassigned invoices.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Rep" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Rep" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R19; Story 22 S22-R2; S22-R4</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>A failed download shows the canonical error toast, and a generating download shows a non-interactive loading state</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a PDF download and watch the menu action while the file is being generated.
 2. Force a failure on a download (PDF or CSV) and read the toast.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-N1; S14-N2; S14-E1; §7</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>An Expanded View PDF over the 10,000-row cap is refused with the specific too-large message — no truncated file</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. A filter set exists (or can be seeded) whose invoice detail rows exceed 10,000 — if this volume cannot be produced in the environment, mark Blocked-Env with the reason.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Apply the over-cap filter set.
 2. Choose "Download Expanded View (PDF)" and read the toast.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This export is too large to generate. Narrow the date range or filters and try again." (persists 120 seconds or until dismissed).
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E2; §7</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>An empty-data export still generates: zeroed Summary PDF totals, header-strip-only Expanded PDF, header-row-only CSVs</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set matches ZERO invoices (for example, a date range with no activity) — the report shows its empty state.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Open each and inspect its contents.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
@@ -4326,139 +4375,139 @@
 5. No special "empty" treatment or message appears inside the files.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E3</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>The Export Report dialog's Report Name dropdown includes "Sales Rep Assignments" at the bottom, hiding the date picker and showing the snapshot note</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Reports access.
 2. Note the current order of the Report Name dropdown entries before checking.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. In the Reports left sidebar, under the Accounting header, click the "Export Reports" entry — a dialog titled "Export Report" opens.
 2. Open the Report Name dropdown and read the list top to bottom.
 3. Select "Sales Rep Assignments" and look at the dialog body.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. "Sales Rep Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
 3. The dialog shows the note: "Snapshot of current sales rep assignments. Both active and inactive reps with assignments are listed."</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R1; S15-R2</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Exporting Sales Rep Assignments downloads sales-rep-assignments.csv with the verbatim headers and shows the success toast</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer in the organization has an assigned sales rep.
 2. The Export Report dialog is open with "Sales Rep Assignments" selected.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Click the Export action.
 2. Note the saved file's name and read the toast.
 3. Open the file in a text editor and read the header row.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as "sales-rep-assignments.csv".
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Rep, Rep is active?.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R3; S15-R4; §7</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>The Assignments CSV holds one row per customer with an assigned rep, sorted customer A→Z then rep A→Z; unassigned customers are excluded</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. The organization has several customers with assigned reps and at least one customer with NO assigned rep (seed as needed).</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Rep Assignments CSV.
 2. Count the rows against the customers with assigned reps.
@@ -4466,191 +4515,191 @@
 4. Read the row order.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. Every customer with an assigned sales rep produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R5; S15-R7; S15-R10</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>"Rep is active?" tracks the staff-active status (Yes/No), not the sales-rep toggle</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Arrange (and afterward restore): one assigned rep whose staff record is ACTIVE but whose sales-rep toggle is OFF, and one assigned rep whose staff record is INACTIVE but whose toggle is ON.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Rep Assignments CSV.
 2. Read the "Rep is active?" value on both reps' customer rows.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R6; Story 13 S13-R11</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Legacy robustness: a customer whose rep's staff record was deleted still exports one row from the customer-side stored name, marked No</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose assigned rep's staff record has been cleared or deleted while the customer still references it (seed and delete a throwaway ZZAUTOTEST rep if needed).</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Rep Assignments CSV.
 2. Find that customer's row and read its "Sales Rep" and "Rep is active?" cells.
 3. If two customers carry different stored name spellings for the same underlying rep, compare their rows.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Rep" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R8; S15-R9</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Assignments export failure and nothing-to-export paths use the Export dialog's own messages</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. For the empty path: no customer in the organization has an assigned rep (or use a state where the export yields zero rows).
 2. For the failure path: you can force a generation failure (for example, cut the network on Export) — if not forceable, mark that step Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, select "Sales Rep Assignments" in the Export Report dialog and click Export.
 2. Read the dialog warning and inspect any downloaded file.
 3. Force a generation failure and read the toast.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 15 S15-R11; S15-N2; §7</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Empty state: verbatim message, no grand Totals, toolbar stays interactive</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter set that matches no invoices for any rep (for example, a date range with no activity), with Show Unassigned OFF or with no matching unassigned invoices either.
 2. Read the data area and look for the grand Totals indicator.
@@ -4658,7 +4707,7 @@
 4. Look at the toolbar, then change the date range to a period WITH activity.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
@@ -4667,48 +4716,48 @@
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-R3; S16-N1; §7</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Loading shows a centered spinner over the data area, hides the Totals, keeps the toolbar interactive, and never flashes a blank table</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Reload the report and watch the data area during the initial load.
 2. Change a filter and watch the data area during the re-fetch.
 3. While loading, try to interact with the toolbar.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
@@ -4716,238 +4765,238 @@
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R4</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>A load failure shows the inline "Couldn't load the report. Please try again." message with a working Retry, keeping the filters</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Set several non-default filters.
 2. Force a load/re-fetch failure and read the data area.
 3. Restore the network and click "Retry".</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R5; §7</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; below 1024px the controls stack vertically with the ⋯ button wrapped above</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. Open the report on a phone-sized viewport (real device or browser device emulation, width under 1024px).</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Find and operate each toolbar control by touch: the ⋯ exports, the column selector, the Show Unassigned toggle, the date range picker, Product Type, Invoice Status, and Location.
 2. Look at how the controls are laid out.
 3. Widen the viewport to 1024px or more and compare.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R1; S17-R2; S17-R3</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>On a phone the table scrolls sideways with Subtotal pinned, the totals bar sits outside the scroll area, and the chevrons work on touch</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a phone-sized viewport (under 1024px) with at least one rep row.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the data table sideways and watch the Subtotal column.
 2. Look below the table for the totals bar and swipe the table again.
 3. Tap a rep row's chevron.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Touch targets are at least 44×44 px and touch users get no hover-only tooltips — the icons carry accessible names instead</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a touch device or touch emulation (under 1024px).</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Measure (device emulation ruler/inspector) the touch targets of a row chevron, the Show Unassigned toggle, the ⋯ button, and — via the staff deactivation dialog if opened — the dialog's X.
 2. Tap-and-hold the icon controls and watch for tooltips.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R6; S17-N1; Story 18 S18-R9</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Layout conformance: white toolbar with the specified padding and alignment, blue-grey page, separator line, edge-to-edge white table</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a desktop browser (light mode) with data showing.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar's surface, padding, and how the title and the rightmost control line up with the table columns.
 2. Look at the page background around the data area, the line between the toolbar and the column headers, and the table's side edges.
 3. Look at the header cells, the body cells, the pinned Subtotal cells, and the grand Totals indicator's surface.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a solid white background with padding 32px top / 24px bottom / 2rem left and right; the title's left edge aligns with the leftmost data column, and the rightmost toolbar control (the Location filter) aligns its right edge with the rightmost data column.
 2. The data area sits on the standard blue-grey page background with ZERO horizontal page padding — the toolbar and table run edge-to-edge against the side navigation.
@@ -4956,41 +5005,41 @@
 5. Row types are differentiated by font weight and color, not background color. These rules apply unconditionally whenever the report is rendered.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Dark mode: page, toolbar, table, and Totals switch to dark equivalents; badges and Inv. Hrs stay legible; PDFs stay light</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing, including at least one expanded rep (badges visible) and non-zero Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page, toolbar, header, body cells, and the grand Totals indicator.
@@ -4998,7 +5047,7 @@
 4. Download a PDF while in dark mode and open it.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
@@ -5006,47 +5055,47 @@
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Every icon-only control carries its specified accessible name</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the accessible name of: the ⋯ exports button, the column selector button, one rep row's chevron (collapsed, then expanded), and the header chevron.
 2. Open the staff deactivation dialog (Story 13 flow) and inspect its X close icon.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
@@ -5055,135 +5104,135 @@
 5. Dialog X = "Close".</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R9</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Chevrons and sortable headers are keyboard-operable and expose their expanded/sort state to assistive technology</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Tab to a rep row's chevron; press Enter, then Space.
 2. Tab to a financial column header; press Enter, then Space.
 3. Inspect what state each control exposes to assistive technology.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R10</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>The subdued grey of the (N) count and (Inactive) tag meets WCAG AA contrast, and no information is conveyed by color alone</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a rep row showing a (N) count and — if arrangeable — an "(Inactive)" tag; a contrast-checking tool is available.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Measure the contrast ratio of the subdued-grey (N) count and "(Inactive)" tag against the white body surface in light mode, and against the dark surface in dark mode.
 2. Review how Inv. Hrs, the status badges, and the links convey their meaning.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The subdued grey meets at least WCAG AA contrast (4.5:1 or better) against the body surface in BOTH modes — the reduced font size does not drop it below that ratio.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R11; S18-R12</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>The Sales Rep selector shows in the left panel on standard Work Orders and Part Sale WOs, and is hidden on imported WOs and in History mode</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You have: an open standard Work Order, an open Part Sale WO, an imported Work Order, and a way to view a WO in History mode.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Open the standard Work Order and look at the left panel.
 2. Open the Part Sale WO and look at the left panel.
@@ -5191,7 +5240,7 @@
 4. View a WO in History mode and look for the field.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The left panel includes a "Sales Rep" selector on the standard Work Order.
 2. The left panel includes the same "Sales Rep" selector on the Part Sale WO.
@@ -5199,190 +5248,190 @@
 4. The selector is NOT present in History mode.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R1; S19-N1</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>The Sales Rep selector offers only reps whose sales-rep toggle is currently on, and carries the accessible name "Sales Rep"</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member has the sales-rep toggle ON and at least one has it OFF (arrange and restore afterward).</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Open a Work Order and open the "Sales Rep" selector.
 2. Search the option list for both staff members.
 3. Inspect the selector's accessible name.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
 3. The selector carries the accessible name "Sales Rep".</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>A new Work Order or Part Sale WO opens with Sales Rep unassigned, and a change saves immediately with no Save step</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member is offered as a sales rep.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Create a new Work Order (mark it ZZAUTOTEST) and read the Sales Rep field before touching it.
 2. Select a rep in the field, then navigate away WITHOUT any explicit save and reopen the WO.
 3. Repeat the unassigned-open check on a new Part Sale WO.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. The new Work Order opens with the Sales Rep field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Rep persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R3; S19-R4</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>The Sales Rep selector is read-only when the Work Order status is Invoiced or Paid</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. One Work Order is in "Invoiced" status and one is in "Paid" status (drive throwaway ZZAUTOTEST WOs into these states if needed).</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Open the Invoiced WO and try to change the Sales Rep field.
 2. Open the Paid WO and try the same.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. On the Invoiced WO the Sales Rep selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R5</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Invoice crediting snapshot: WO rep, else the customer's rep, else unassigned — and a later WO change never rewrites past invoices</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. Three throwaway ZZAUTOTEST setups: (a) a WO WITH a Sales Rep assigned; (b) a WO with NO rep whose customer HAS an assigned rep; (c) a WO with NO rep whose customer has NO assigned rep.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Invoice all three WOs.
 2. On the report (Show Unassigned on, filters covering the invoices), find each invoice and note which row it sits under.
 3. Go back to WO (a), change its Sales Rep to a different rep, and re-check the already-created invoice on the report.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. Invoice (a) is credited to the WO's Sales Rep.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
@@ -5390,350 +5439,350 @@
 4. Changing WO (a)'s Sales Rep afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>The customer record shows a single Sales Rep row ("Unassigned" when none), and a toggled-off bound rep shows "(Inactive)" in the WO selector</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. One customer HAS an assigned sales rep and one customer has NONE.
 2. A Work Order exists whose bound Sales Rep can have their toggle turned off (arrange and restore afterward).</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Open the assigned customer's record and read the left-panel sidebar.
 2. Open the unassigned customer's record and read the same row.
 3. Turn the bound rep's sales-rep toggle OFF, reopen the Work Order, and read the Sales Rep selector; then open its option list.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The customer record's left-panel sidebar shows a single "Sales Rep" row with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 19 S19-R7; S19-E1</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>A rep's invoice detail rows are fetched from the server only on the first expand, and are paginated per rep</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows, one with a large invoice count if seedable.
 2. The browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note which requests deliver the summary rows.
 2. Expand one rep and watch the network panel; collapse and re-expand it.
 3. If a rep has many invoices, scroll/page through its expanded detail rows.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R2</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Sorting is performed server-side: a header click re-fetches the rep summary rows in the requested order</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several rep rows; the network panel is open.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Click a financial column header and watch the network panel.
 2. Click the same header again (descending) and watch again.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R5</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>The grand totals are server-computed over the full filtered result set and delivered with the summary payload</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Load the report with everything collapsed and inspect the summary response and the grand Totals indicator.
 2. Compare the grand totals against the full filtered result (for example, via the Summary CSV), not just the loaded rows.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>All four exports are generated server-side against the active filters and sort — a genuine failure yields a toast, never a malformed file</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Trigger each of the four downloads and observe the export requests and responses.
 2. Compare the delivered files against the active filters and sort.
 3. If forceable, fail one export server-side and check what (if anything) downloads.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R2a; S14-N2; S14-E3</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>The Expanded View PDF's 10,000-row cap is enforced server-side BEFORE generation — a refusal, not a truncated file</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. A filter set producing more than 10,000 invoice detail rows exists or can be seeded — otherwise mark Blocked-Env with the reason.
 2. The network panel is open.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download Expanded View (PDF)" against the over-cap filter set and observe the export request/response.
 2. Check whether any file arrives.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E2</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Toggling a sales rep's active status off first runs a server pre-check returning the assigned-customer count and an assignments flag</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-rep toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
 2. The network panel is open.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. In staff administration, toggle that staff member's active status off and watch the network panel BEFORE the dialog appears.
 2. Read the pre-check response and compare it with the dialog's "{N} customer{s}" headline.
 3. Cancel the dialog (leave the staff member active).</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales rep, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales rep on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R4</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sales By Representative at the bottom of Performance group; titles correct</t>
+          <t>Sales By Representative under Performance, below existing links; titles correct</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group, at the BOTTOM of the group — the label is the full word "Representative," not a "Rep" shorthand.
+          <t>1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
 2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
 3. Selecting the entry opens the report in the main content area.
 4. The page title reads "Sales By Representative".
@@ -532,7 +532,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6</t>
+          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6 — 'at the bottom' re-based to below-the-named-anchors [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05; order among the four new reports not important)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -5259,7 +5259,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>The Sales Rep selector offers only reps whose sales-rep toggle is currently on, and carries the accessible name "Sales Rep"</t>
+          <t>Sales Rep selector offers only reps whose sales-rep toggle is on</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>1. At least one staff member has the sales-rep toggle ON and at least one has it OFF (arrange and restore afterward).</t>
+          <t>1. At least one staff member has the sales-rep toggle ON and at least one has it OFF. To arrange this: open Settings, go to Staff, edit the staff member, and use the sales-rep toggle there (restore both afterward).</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8</t>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>The customer record shows a single Sales Rep row ("Unassigned" when none), and a toggled-off bound rep shows "(Inactive)" in the WO selector</t>
+          <t>Customer record shows a "Sales Representative" row; "Unassigned" when none</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5483,14 +5483,14 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1. The customer record's left-panel sidebar shows a single "Sales Rep" row with the customer's assigned rep.
+          <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Rep" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R7; S19-E1</t>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R7; S19-E1 — customer-card row label RE-RULED to the full 'Sales Representative' per the PRD companion video 2026-07-30 10:53-11:12, superseding the spec's 'Sales Rep'; video authoritative, newest-wins)</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>A user without Reports access sees no Reports navigation, no export menu, and cannot reach the Export Reports dialog</t>
+          <t>Without Reports access: no navigation, no export menu, no Export dialog</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -667,12 +667,12 @@
         <is>
           <t>1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
 2. The report (and its ⋯ export menu) is not reachable.
-3. The Export Reports dialog and the Sales Rep Assignments download are not reachable.</t>
+3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1</t>
+          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. A rep has both a P (parts) and an S (service) invoice in the range (seed ZZAUTOTEST data via the WO Sales Rep field).
+          <t>1. A rep has both a P (parts) and an S (service) invoice in the range (seed ZZAUTOTEST data via the WO Sales Representative field).
 2. No remembered settings for this report (first visit or cleared storage), so the default can be read.</t>
         </is>
       </c>
@@ -909,7 +909,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6; S3-R7</t>
+          <t>SV-8621 (specs/sbr-sales-by-representative.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6; S3-R7)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8638 (SBR spec S21-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S21-N1 "still sees the filter" note is stale, spec edit pending)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1256,37 +1256,97 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>The Location column shows only with more than one location; rep rows Multiple</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Location Filter</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Sales By Representative report as a user with access to two or more locations.
+2. One rep has invoices at a single location and another rep has invoices at two different locations.
+3. Show Unassigned is turned on and at least one unassigned invoice exists.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Select two or more locations and read the column headers.
+2. Read the Location cell on the single-location rep's summary row.
+3. Read the Location cell on the rep whose invoices span two locations.
+4. Expand that rep and read an invoice detail row's Location cell.
+5. Read the Location cell on the Unassigned summary row.
+6. Check that the pinned Subtotal column is still the rightmost column.
+7. Narrow to a single location and read the headers again.
+8. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
+2. A rep summary row whose invoices are all at one location shows that location's name.
+3. A rep summary row whose invoices span more than one location shows "Multiple".
+4. An invoice detail row shows that invoice's own exact location — never "Multiple".
+5. The Unassigned summary row follows the same rule as any rep summary row.
+6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
+7. With a single location in scope the Location column is hidden.
+8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>SV-8638 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13 — per-row Location column, "Multiple" verbatim on a rep row spanning locations, position after Status, constant-width filter)</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Contributors only: a rep row appears if and only if the rep has at least one non-reversed invoice matching all active filters</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. Rep A has invoices in the current filtered view; rep B (sales-rep toggle on) has NONE; rep C has only a reversed invoice (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the summary rows.
 2. Look for reps B and C.
 3. Read the count in parentheses after rep A's name.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
@@ -1294,41 +1354,41 @@
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Row layout: 12 columns in order, blanks in position, bold summary rows</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep expanded.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Read a rep summary row cell by cell.
@@ -1336,7 +1396,7 @@
 4. Look for any cell whose content has shifted into a neighbouring column or wrapped; check the desktop Totals row's leading cells.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. The columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns).
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
@@ -1345,49 +1405,49 @@
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>A toggled-off or deleted contributor still appears with credit intact, tagged (Inactive), named from the latest invoice snapshot when deleted</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. Rep A has matching invoices; you then turn rep A's sales-rep toggle OFF (restore afterwards).
 2. If a rep whose staff record was DELETED but who has invoices in range exists (or can be produced), note it for step 3.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Refresh the report and find rep A's row.
 2. Read the name, tag, metrics, and position in the A→Z order; try expanding the row.
 3. If a deleted-rep contributor exists, read that row's name and sort position.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
@@ -1395,236 +1455,236 @@
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 5 S5-R9; §3 Key Decisions; §4 Snapshot</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Expanding a rep loads its invoices on demand with a brief row-level loading indicator and full detail-row contents</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. A rep with several matching invoices is on the report.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron in the rep's Date cell and watch the row.
 2. Read a detail row left to right.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R1; S6-R2; S6-R3; S6-E1</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Header chevron expands every visible rep in one action and its glyph tracks the expand/collapse state</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. Several reps are on the report, all collapsed.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Look at the header-row chevron's glyph.
 2. Click it; watch the rep rows and the glyph.
 3. Click it again.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R5; S6-R6</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Each invoice appears under exactly one rep or the Unassigned row, never more than one</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. A known ZZAUTOTEST invoice set exists across two reps plus at least one unassigned invoice; Show Unassigned is on.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Expand every rep and the Unassigned row.
 2. Search the expanded rows for each seeded invoice number.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R7; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Expansion survives filter and sort changes within the session, resets on reload, and a removed rep returns collapsed</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are on the report; one of them stops matching under a stricter filter you can apply and re-remove.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Expand both reps, then change the sort and a filter that keeps both matching; check the expansion.
 2. Apply the stricter filter that removes rep B, then remove it again; check rep B.
 3. Reload the page and check all rows.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R8; S6-N1; Story 23 S23-R2</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Detail rows order newest first with a numeric invoice-number tie-break where P sorts before S</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. One rep has invoices allowing the tie-breaks: two invoices on different dates; two on the same date with numeric parts like 999 and 1000; and if producible a P and an S invoice with the same numeric part on the same day (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep and read the detail rows top to bottom.
 2. Change the rep-row column sort and re-read the detail order.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
@@ -1632,49 +1692,49 @@
 4. This order is independent of the rep-row column sort (which reorders summary rows only).</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R9; Story 11 S11-R2</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Status badge between Customer and Inv. Hrs; every detail row shows mapped text</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBR — Payment Status Badge</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist covering paid, overpaid, prepaid (zero balance), prepaid (balance owed), partially paid, and unpaid.
 2. The owning rep is expanded.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Locate the Status column relative to its neighbours.
 2. Read the badge on each seeded invoice's detail row.
 3. Look at a badge's vertical position in its cell, read the Status cell on a rep summary row, and check the status is readable from the badge text alone.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The Status column sits between the Customer column and the Inv. Hrs column.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
@@ -1682,135 +1742,135 @@
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Badge colors use the application's canonical payment-status tokens in both light and dark mode</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBR — Payment Status Badge</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows with all three badge values are visible; you can switch to dark mode.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Read the color treatment of each badge in light mode and compare with the badges on the application's invoice list.
 2. Switch to dark mode and compare again.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 8 S8-R3; Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim and the value is hours invoiced minus hours worked, rounded half-up to one decimal</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST work order exists with known billed labor-line hours and known technician clocked (timesheet) hours, invoiced under a rep.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Expand the rep and read the invoice's Inv. Hrs value; recalculate by hand.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 9 S9-R1; S9-R2; §3</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs: +green, -red, 0.0 default on every row; rollups from unrounded deltas</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist under one rep with a positive, a negative, and a break-even labor delta (seed ZZAUTOTEST data).
 2. If producible, an invoice whose delta is tiny (e.g., +0.04) and one with a small negative delta (e.g., -0.5) also exist.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Read the three detail rows' Inv. Hrs values and colors.
 2. Read the rep summary row's and the Totals row's Inv. Hrs.
@@ -1818,7 +1878,7 @@
 4. Read the tiny-delta and small-negative invoices' Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
@@ -1826,141 +1886,141 @@
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>No-labor-no-time invoices show 0.0 but clocked-yet-unbilled work shows its negative delta, never suppressed</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice with no labor and no clocked time exists, AND an invoice whose work order has clocked technician hours but no billed labor line (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Read the parts-only invoice's Inv. Hrs cell.
 2. Read the clocked-but-unbilled invoice's Inv. Hrs cell.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 9 S9-N1</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Margin % renders to one decimal with a % sign, shows an em dash when Subtotal is zero or below, and is recomputed on every rollup</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. A rep has two invoices with clearly different Margin % values; if producible, a row with Subtotal ≤ 0 also exists.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on both detail rows and on the rep's summary row; recompute the summary value as (total Margin ÷ total Subtotal) × 100.
 2. Read the Subtotal ≤ 0 row's Margin % cell.
 3. If a negative-margin row exists, read its format.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 Margin % definition; Story 10 S10-R5</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Money columns use the standardized labels and definitions: Subtotal is pre-tax Labor plus Parts Invoiced, Margin is the two margins combined</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known billed labor, billed parts, labor cost, parts cost, and tax.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Read the money column headers.
 2. Read that invoice's row values and recalculate each by hand.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
@@ -1968,182 +2028,182 @@
 4. The same values appear everywhere the numbers show (screen, and later the exports).</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 definitions; §4 Terminology</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Negative dollar values render in accounting parentheses on screen, in money columns only</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. A row with a negative money value exists (e.g., a net credit/return invoice, or a negative Labor Margin from cost exceeding billed labor — seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Read the negative money cell.
 2. Read a negative Inv. Hrs cell and a negative Margin % cell for comparison.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 Key Decisions (accounting parentheses)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Half-up rounding at each precision; totals may differ by one last-decimal unit</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. Several invoices whose money values come from calculations that produce fractions of a cent sit under one rep — seed ZZAUTOTEST invoices whose amounts come from hours × rate or percentage-based lines that do not land on a whole cent (money fields themselves only take two decimals, so the sub-cent amounts must come from the math, not be typed in).</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Read the displayed per-invoice values, sum them by hand, and compare with the rep summary and Totals cells.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md §3 rounding rule</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>A clock-record edit after invoicing updates Inv. Hrs; billed money stays put</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoiced (not reversed, not void) work order exists with billed labor and clocked technician hours, and its invoice row is visible under its rep in the report.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Note the invoice row's Inv. Hrs value and its money columns.
 2. Edit a technician clock record on that work order (change its length), or delete one.
 3. Reload the report and re-read the same invoice row.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8626 (specs/sbr-sales-by-representative.md §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Subtotal: rightmost, pinned right, bold everywhere; header row sticky on scroll</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, narrow enough to force horizontal scrolling.
 2. Enough rows exist to also force vertical scrolling.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Confirm nothing renders to the right of Subtotal on any row type.
 2. Scroll horizontally and watch the Subtotal column on summary and detail rows.
@@ -2151,7 +2211,7 @@
 4. Scroll down through the rows and watch the header row; scroll right and watch the Subtotal header cell.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column on every row type.
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
@@ -2160,41 +2220,41 @@
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Desktop Totals row merges the four identifier columns, aggregates every metric over the full filtered set, and sticks to the bottom</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. Desktop viewport (1024px or wider); several reps with known amounts are on the report; at least one rep is left collapsed.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the table and find the Totals row.
 2. Read its first cell and the per-metric cells.
@@ -2202,7 +2262,7 @@
 4. Empty the results with a no-data filter and look for the indicator; also watch during a re-fetch.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
@@ -2211,48 +2271,48 @@
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5; S10-N1; Story 16 S16-R4</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Mobile shows a simplified external totals bar below the table with Totals left and the grand Subtotal right</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data in a viewport below 1024px.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Find the totals bar and read it.
 2. Swipe the table horizontally and watch the bar.
 3. Scroll the page vertically and watch the bar.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
@@ -2260,133 +2320,133 @@
 4. It uses the white card surface with a thin top border.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5 (mobile); Story 17 S17-R4</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>All eight financial columns are sortable; the identifier columns are not and the Date header carries the chevron instead</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. Several reps with differing values are on the report.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Click each financial column header in turn: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Click the Date, Invoice, Customer, and Status headers.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R1; S11-R6</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Default order is plain A to Z by display name, case-insensitive, with no active/inactive tiers</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. No remembered sort exists (first visit or cleared storage); contributing reps include an "(Inactive)"-tagged rep and mixed-case names.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the rep order top to bottom.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R4; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>First click sorts ascending with an indicator, second click descending, no third cleared state, and no header path back to A to Z</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. Several reps are on the report in the A→Z default.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Click the Subtotal header once and read the order and the direction indicator.
 2. Click it again.
@@ -2394,7 +2454,7 @@
 4. Try to get back to the A→Z order using only the column headers.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
@@ -2402,237 +2462,237 @@
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R5; Story 23 S23-R5</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders rep summary rows only; detail rows stay under their rep and the Unassigned row stays pinned on top</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Show Unassigned is on with a populated Unassigned row; at least one rep is expanded.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a financial column.
 2. Read the Unassigned row's position, the expanded rep's detail rows, and their order.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R2; Story 22 S22-R4</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Equal sorted values keep the A to Z order as tie-break and an em-dash Margin % sorts as zero</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. Two reps have equal values in a sortable column; if producible, one rep shows "—" in Margin % (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Sort by the column where the two reps tie and read their relative order.
 2. Sort by Margin % ascending and locate the "—" rep.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R7</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Detail-row invoice number and customer name links navigate in the current tab</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. A rep row is expanded with at least one S and one P invoice visible.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Click a service invoice's number link and note the destination and tab.
 2. Go back, then click a parts invoice's number link.
 3. Click the customer name on a detail row.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2; S12-R3</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Browser back from a drilldown restores ALL report state including expansion and scroll, without a full reload</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Non-default filters are set (date range, product type, invoice status, location, Show Unassigned on), two reps are expanded, and the table is scrolled partway down.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Click an invoice link, then press the browser back button; check every piece of state.
 2. Repeat via a customer-name link.
 3. Watch whether the report performs a full reload on back.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R3a; Story 23 S23-R2</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Link styling: theme-primary invoice links and body-colored customer links, hover/focus underline, never browser-purple, in both modes</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows are visible; at least one invoice and one customer link have been clicked earlier; you can switch to dark mode.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Inspect an invoice-number link at rest, on hover, on keyboard focus, and after a click.
 2. Inspect a customer-name link the same way.
 3. Switch to dark mode and repeat.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
@@ -2640,135 +2700,135 @@
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-R4; S12-R5; S12-R6; S12-N3</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>An unavailable invoice or customer destination shows the standard not-found/access-denied state and back still returns</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with detail rows visible; in another session the target invoice is reversed/deleted (and, for the customer leg, a customer record is made unavailable if the app allows).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Without refreshing, click the now-unavailable invoice's link; read the destination, then press back.
 2. If producible, repeat for an unavailable customer record.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 12 S12-N1; S12-N2</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Deactivating a rep with assignments opens the Deactivate dialog with the counted, pluralized headline and reassurance line, trapping focus</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Deactivate dialog: counted pluralized headline, reassurance, focus trap</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1. ZZAUTOTEST rep "A" is active, toggle on, and assigned as sales rep to exactly 1 customer; ZZAUTOTEST rep "B" likewise to 3 customers.</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>1. ZZAUTOTEST rep "A" is active, toggle on, and assigned as sales representative to exactly 1 customer; ZZAUTOTEST rep "B" likewise to 3 customers.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Toggle rep B's active status off and read the dialog before confirming anything.
 2. Press Tab repeatedly and watch where focus goes; dismiss and watch where focus returns.
 3. Repeat step 1 for rep A (1 customer) and read the headline's noun.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
-2. The body shows "{Staff Name} is the sales rep on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
+2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R3; S13-R4; S13-R12</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R3; S13-R4; S13-R12)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Type-YES gate: auto-focused input, case-insensitive whitespace-tolerant match, disabled-button tooltip, Enter submits</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Read the instruction text and check which element holds focus.
 2. Hover the disabled "Deactivate" button and read the tooltip.
@@ -2776,7 +2836,7 @@
 4. With a valid entry, press Enter.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
@@ -2784,41 +2844,41 @@
 4. Pressing Enter while valid submits.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-R6; S13-R7</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Cancel and X dismiss the Deactivate dialog; Escape and clicking outside do not</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Click the "Cancel" button and watch the dialog; then re-open it.
 2. Click the "X" close icon and watch the dialog; then re-open it.
@@ -2827,7 +2887,7 @@
 5. After each action, check the staff member's active status.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
@@ -2836,47 +2896,47 @@
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Valid submit locks the dialog, then deactivates keeping assignments</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a ZZAUTOTEST rep with known customer assignments.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Type YES and submit; during the request try Cancel, X, and Escape.
-2. After success, check the staff member's status and each previously assigned customer's Sales Rep.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+2. After success, check the staff member's status and each previously assigned customer's Sales Representative.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
@@ -2884,57 +2944,9 @@
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>After deactivation the sales-rep toggle is unchanged, the Assignments CSV shows Rep is active? = No, and report credit stays intact</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Staff Deactivation</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1. A ZZAUTOTEST rep with assignments AND matching invoices was just deactivated via the dialog flow.</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Re-open the staff member and read the sales-rep toggle.
-2. Download the Sales Rep Assignments CSV and read the rep's rows.
-3. Open the report and find the rep's row.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>1. The sales-rep toggle state is unchanged by the deactivation flow.
-2. In the Sales Rep Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
-3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-rep TOGGLE is off (a separate flag from staff-active status).</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2943,220 +2955,268 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>After deactivation: toggle unchanged, CSV shows No, report credit intact</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Staff Deactivation</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. A ZZAUTOTEST rep with assignments AND matching invoices was just deactivated via the dialog flow.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Re-open the staff member and read the sales-representative toggle.
+2. Download the Sales Representative Assignments CSV and read the rep's rows.
+3. Open the report and find the rep's row.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. The sales-representative toggle state is unchanged by the deactivation flow.
+2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
+3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
           <t>No dialog: toggle off, no assignments, already inactive, or reactivation</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>1. ZZAUTOTEST staff member X is active WITHOUT the sales-rep toggle; ZZAUTOTEST rep Y (with assignments) is currently inactive; ZZAUTOTEST rep Z is active with the sales-rep toggle ON and NO customers assigned.</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. ZZAUTOTEST staff member X is active WITHOUT the sales-representative toggle; ZZAUTOTEST rep Y (with assignments) is currently inactive; ZZAUTOTEST rep Z is active with the sales-representative toggle ON and NO customers assigned.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate X and watch for a dialog.
 2. Reactivate rep Y via the standard toggle and watch for a dialog; check Y's customer assignments afterwards.
-3. Deactivate rep Z (sales-rep toggle on, no assignments) and watch for a dialog.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1. For a staff member without the sales-rep toggle, the precondition check is skipped and no warning is shown.
+3. Deactivate rep Z (sales-representative toggle on, no assignments) and watch for a dialog.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
 3. After reactivation the assignments re-surface immediately with no extra action.
-4. Deactivating a sales rep with NO customer assignments applies silently — no warning dialog.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R2; S13-N2; S13-N3; S13-E3</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R2; S13-N2; S13-N3; S13-E3)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>A server-side deactivation failure shows the canonical error toast, leaves the status unchanged, and clears the input on the next open</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments; you can force the request to fail (go offline just before submitting).</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Type YES, force the failure condition, and submit.
 2. Read the toast; check the staff member's active status.
 3. Dismiss, re-open the dialog, and look at the confirmation input.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "Ooooops! An error occured" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-N5; §7</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>If the assignment pre-check fails, the warning dialog still opens — without the count headline — and never silently deactivates</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-rep toggle on.
 2. You can force the pre-deactivation assignment check to fail (for example, cut the network exactly when toggling active off) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Toggle the staff member's active status off while forcing the check to fail.
 2. Read the dialog that opens.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 13 S13-N4</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Show Unassigned sits between the column selector and the date picker, is off by default, and while off unassigned invoices contribute nothing</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Show Unassigned sits between the column selector and the date picker, off</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. No remembered settings; at least one matching invoice with NO assigned rep exists (seed via a WO with no Sales Rep whose customer also has no rep).</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. No remembered settings; at least one matching invoice with NO assigned rep exists (seed via a WO with no Sales Representative whose customer also has no rep).</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Find the "Show Unassigned" toggle in the toolbar and note its position and default state.
 2. With it off, look for an Unassigned row and check the grand Totals against the rep rows only.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 22 S22-R1; S22-R2; Story 18 S18-R7.2</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-R1; S22-R2; Story 18 S18-R7.2)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned adds one top-pinned Unassigned row that acts like a rep row</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. Matching unassigned invoices exist; the grand Totals with the toggle off are noted.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Turn "Show Unassigned" on and read the new row and its position.
 2. Read the grand Totals indicator.
@@ -3164,7 +3224,7 @@
 4. Turn the toggle off again.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
@@ -3172,88 +3232,88 @@
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>No empty Unassigned row is ever rendered, and toggling off while expanded removes the row which returns collapsed</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: a filter set with NO matching unassigned invoices (but some rep rows).
 2. Scenario B: the Unassigned row is populated and expanded.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: turn Show Unassigned on and look for the row; then narrow so no reps match either and read the table.
 2. Scenario B: with the Unassigned row expanded, turn the toggle off, then back on.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 22 S22-N1; Story 6 S6-N2</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Column selector: seven metric toggles; five always-on columns cannot be hidden</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. No remembered column preference exists (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Click the column selector button in the toolbar.
 2. Read the toggle list.
@@ -3262,7 +3322,7 @@
 5. Hide all seven metric columns and read the table and the grand Totals indicator.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
@@ -3270,452 +3330,452 @@
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Toggling a column applies immediately across summary rows, detail rows and the grand Totals at once</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. A rep is expanded and the Totals indicator is visible.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Toggle "Parts Margin" off and immediately check the summary rows, detail rows, and the Totals row.
 2. Toggle it back on.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R4; S20-R7</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Column visibility never affects the exports — all four downloads always include all metric columns</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. Several metric columns are hidden via the column selector.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download all four exports (Summary PDF, Expanded View PDF, Summary CSV, Expanded View CSV).
 2. Check each file's columns.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R8</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Hiding the active sort column keeps the sort; showing it again reveals the sort indicator</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. The report is sorted by a metric column (e.g., Margin descending).</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Hide that column via the column selector and read the row order.
 2. Show the column again and look at its header.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 20 S20-R9</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>All filter and view settings are remembered per browser and restored before the first data fetch on the next visit</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Set a custom date range, "Parts only," "Paid," a specific location set, Show Unassigned on, hide two metric columns, and sort by Margin descending.
 2. Leave the report and return; also try a full page reload.
 3. Watch what data loads first.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R1; Story 20 S20-R5</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Expansion state and scroll position are not remembered and reset on reload</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are expanded and the table is scrolled partway.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Reload the page.
 2. Check the rows and the scroll position.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R2; §2 Out of Scope</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Restoration is defensive: a stale saved value falls back to its default and never causes an error or invalid request</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. Your saved settings include a location you are then un-assigned from (restore access afterwards).</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter, the data, and watch for any error.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R3</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>First visit or cleared storage yields all defaults; no server-side profile</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You have distinctive saved settings, then clear the browser's site data (or use a fresh profile).
 2. You are working in a known active location (the application's location switcher).</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read every setting.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1; Story 2 S2-R4; Story 21 S21-R2</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The A to Z default is its own saved value: restoring a state with no financial sort returns to A to Z, not an arbitrary column</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You have never clicked a financial column header in this browser session/profile (the report is in the A→Z default).</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Change a few filters (no sort click), leave the report, and return.
 2. Read the row order and the headers.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 23 S23-R5; Story 11 S11-R4</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The ⋯ overflow menu lists exactly four download actions</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Sales By Representative report.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ (three-dot) button in the report toolbar — it is the first control in the toolbar's action cluster.
 2. Click it and read the menu entries top to bottom.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R1; Story 17 S17-R3 (position)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>All four downloads respect filters, full result set, and active order</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps showing.
 2. Set a specific date range, Product Type, Invoice Status, and a location selection; turn Show Unassigned on.
@@ -3723,14 +3783,14 @@
 4. Leave at least one rep collapsed (do not expand it).</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Compare each file's rows against the on-screen result: which reps appear, which invoices are included, and the row order.
 3. Check where the Unassigned row sits in each file.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
@@ -3739,49 +3799,49 @@
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Summary PDF: A4 header strip, one rolled-up row per rep, bold Subtotal, colored Inv. Hrs, and a recomputed grand totals row</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, one of them a toggled-off ("(Inactive)") contributor if one can be arranged.
 2. A date range is selected.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (PDF)" from the ⋯ menu and open the file.
 2. Read the top of the first page, the column headers, one rep row, and the last row.
 3. Compare the totals row's Margin % against the child rows.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
@@ -3790,41 +3850,41 @@
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R3; S14-R5; Story 2 S2-R5; §3 Margin % definition</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF: one page-block per rep with its own header strip, per-invoice table, per-rep totals row, and no grand totals</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (PDF)" from the ⋯ menu and open the file.
 2. Check how each rep's section starts and what its table contains.
@@ -3832,7 +3892,7 @@
 4. Compare the order of one rep's invoices against the on-screen expanded order.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
@@ -3842,233 +3902,233 @@
 6. There is NO grand-totals row across all reps at the end of the document.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R6; S14-R8; Story 6 S6-R9</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF truncates invoice numbers longer than 18 characters; on screen they are never truncated</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. At least one invoice in the current view has an invoice number LONGER than 18 characters, and one has a number of 18 characters or fewer (seed data if needed).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep on screen and read both invoice numbers.
 2. Download the Expanded View PDF and read the same two invoice numbers.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R7</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>PDF footer on every page, default-logo fallback, and deterministic PDF filenames</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. For the fallback check: the organization has NO configured logo (clear it in settings if permitted, and restore afterward).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs and note each saved file's name.
 2. Scroll through every page of both PDFs and read the footer.
 3. With the organization logo not configured, download a PDF again and look at the header strip's logo region.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
 3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R4; S14-R3a; S14-R11</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag, and omit the on-screen (N) count</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. The current view includes at least one negative money value (for example, a net-credit/return invoice — seed one if needed) and, if arrangeable, one toggled-off "(Inactive)" contributor.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs.
 2. Find the negative money value in each and read how it is written.
 3. Read the rep names in both PDFs.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R9; S14-R10</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>PDF body font steps down as the longest dollar value grows; no overflow</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Download the Summary PDF for a view whose longest positive dollar value is 9 characters or fewer; note the body text size (a relative comparison across files is enough).
 2. Repeat for views whose longest positive value is 10, 11, and 12-or-more characters (as far as seedable).
 3. In each file, check whether any value overflows or wraps its column.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R12; S14-R13</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Summary CSV: filename, UTF-8 BOM, verbatim headers in order, one row per rep, and the # Invoices / # Customers counts</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Summary CSV: file name, UTF-8 BOM, verbatim headers, one row per rep</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing; one rep has invoices for the same customer more than once (to check de-duplication).</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
@@ -4076,147 +4136,150 @@
 4. For one rep, compare "# Invoices" with the on-screen (N) count, and "# Customers" with the number of DISTINCT customers across that rep's matching invoices.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
-2. The headers, in order, are exactly: Sales Rep, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. The headers, in order, are exactly: Sales Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
-5. The CSV has NO totals row.</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R15; S14-R18</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Expanded CSV: filename, verbatim headers including the three hours columns, one row per invoice flattened across reps</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
+5. The CSV has NO totals row.
+6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R15; S14-R18)</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Expanded CSV: file name, verbatim headers, one row per invoice</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
 3. Compare the rows against the on-screen invoices (all reps, expanded).</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
-2. The headers, in order, are exactly: Sales Rep, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
-3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R16</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>CSV cell formatting: plain re-pivotable numbers, signed Inv. Hrs, Margin % empty when undefined, (Inactive) in the name, no (N)</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
+2. The headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R16)</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>CSV cells: plain numbers, signed Inv. Hrs, empty Margin %, (Inactive)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded both report CSVs from a view that includes a negative money value, a rep whose Margin % shows "—" on screen (Subtotal ≤ 0), and an "(Inactive)" contributor (seed what is missing).</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Open each CSV in a text editor (not a spreadsheet).
-2. Read a money cell, the negative value's cell, an Inv. Hrs cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Rep" cell.</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
+2. Read a money cell, the negative value's cell, an Inv. Hrs cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Representative" cell.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
 3. Margin % is a plain number to one decimal (for example, 45.2) with no % sign, and the cell is EMPTY where Margin % is undefined (Subtotal ≤ 0).
-4. The "Sales Rep" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
-5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers)</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>The Unassigned row appears in all four downloads when Show Unassigned is on, and in none of them when it is off</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
+5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
+6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>The Unassigned row appears in all four downloads only when the toggle is on</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>1. The current filter set includes at least one invoice with no assigned sales rep (seed one if needed).</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1. The current filter set includes at least one invoice with no assigned sales representative (seed one if needed).</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Turn Show Unassigned ON and download all four files.
 2. Find the Unassigned entry in each file.
@@ -4224,149 +4287,150 @@
 4. Search each file for the unassigned invoices.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Rep" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Rep" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
-3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R19; Story 22 S22-R2; S22-R4</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>A failed download shows the canonical error toast, and a generating download shows a non-interactive loading state</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a PDF download and watch the menu action while the file is being generated.
 2. Force a failure on a download (PDF or CSV) and read the toast.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-N1; S14-N2; S14-E1; §7</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>An Expanded View PDF over the 10,000-row cap is refused with the specific too-large message — no truncated file</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Over-cap Expanded View PDF is refused with the too-large message</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. A filter set exists (or can be seeded) whose invoice detail rows exceed 10,000 — if this volume cannot be produced in the environment, mark Blocked-Env with the reason.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Apply the over-cap filter set.
 2. Choose "Download Expanded View (PDF)" and read the toast.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. No file is produced — the server declines rather than generating a truncated file.
-2. An error toast reads exactly: "This export is too large to generate. Narrow the date range or filters and try again." (persists 120 seconds or until dismissed).
+2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-E2; §7</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E2; §7)</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>An empty-data export still generates: zeroed Summary PDF totals, header-strip-only Expanded PDF, header-row-only CSVs</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set matches ZERO invoices (for example, a date range with no activity) — the report shows its empty state.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Open each and inspect its contents.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
@@ -4375,251 +4439,205 @@
 5. No special "empty" treatment or message appears inside the files.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E3</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>The Export Report dialog's Report Name dropdown includes "Sales Rep Assignments" at the bottom, hiding the date picker and showing the snapshot note</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Report Name dropdown lists Sales Representative Assignments at the bottom</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Reports access.
 2. Note the current order of the Report Name dropdown entries before checking.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. In the Reports left sidebar, under the Accounting header, click the "Export Reports" entry — a dialog titled "Export Report" opens.
 2. Open the Report Name dropdown and read the list top to bottom.
-3. Select "Sales Rep Assignments" and look at the dialog body.</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1. "Sales Rep Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
+3. Select "Sales Representative Assignments" and look at the dialog body.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
-3. The dialog shows the note: "Snapshot of current sales rep assignments. Both active and inactive reps with assignments are listed."</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 15 S15-R1; S15-R2</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Exporting Sales Rep Assignments downloads sales-rep-assignments.csv with the verbatim headers and shows the success toast</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
+3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R1; S15-R2)</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative Assignments CSV: file name, headers, success toast</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>1. At least one customer in the organization has an assigned sales rep.
-2. The Export Report dialog is open with "Sales Rep Assignments" selected.</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>1. At least one customer in the organization has an assigned sales representative.
+2. The Export Report dialog is open with "Sales Representative Assignments" selected.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Click the Export action.
 2. Note the saved file's name and read the toast.
 3. Open the file in a text editor and read the header row.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>1. The file downloads as "sales-rep-assignments.csv".
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1. The file downloads as "sales-representative-assignments.csv (the short form "rep" is gone from the file name — confirm the exact final file name in the build)".
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
-3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Rep, Rep is active?.</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 15 S15-R3; S15-R4; §7</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>The Assignments CSV holds one row per customer with an assigned rep, sorted customer A→Z then rep A→Z; unassigned customers are excluded</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
+3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R3; S15-R4; §7)</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Assignments CSV: one row per assigned customer, sorted customer then rep</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. The organization has several customers with assigned reps and at least one customer with NO assigned rep (seed as needed).</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the Sales Rep Assignments CSV.
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the Sales Representative Assignments CSV.
 2. Count the rows against the customers with assigned reps.
 3. Search for the no-rep customer.
 4. Read the row order.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>1. Every customer with an assigned sales rep produces exactly ONE row (single-rep model: one rep per customer).
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 15 S15-R5; S15-R7; S15-R10</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>"Rep is active?" tracks the staff-active status (Yes/No), not the sales-rep toggle</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R5; S15-R7; S15-R10)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>"Rep is active?" tracks the staff-active status, not the toggle</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>1. Arrange (and afterward restore): one assigned rep whose staff record is ACTIVE but whose sales-rep toggle is OFF, and one assigned rep whose staff record is INACTIVE but whose toggle is ON.</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the Sales Rep Assignments CSV.
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1. Arrange (and afterward restore): one assigned rep whose staff record is ACTIVE but whose sales-representative toggle is OFF, and one assigned rep whose staff record is INACTIVE but whose toggle is ON.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the Sales Representative Assignments CSV.
 2. Read the "Rep is active?" value on both reps' customer rows.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 15 S15-R6; Story 13 S13-R11</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Legacy robustness: a customer whose rep's staff record was deleted still exports one row from the customer-side stored name, marked No</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Sales Rep Assignments Export</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>1. A customer exists whose assigned rep's staff record has been cleared or deleted while the customer still references it (seed and delete a throwaway ZZAUTOTEST rep if needed).</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the Sales Rep Assignments CSV.
-2. Find that customer's row and read its "Sales Rep" and "Rep is active?" cells.
-3. If two customers carry different stored name spellings for the same underlying rep, compare their rows.</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>1. The customer still produces a row — the export never silently drops it.
-2. The "Sales Rep" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
-3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.</t>
-        </is>
-      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 15 S15-R8; S15-R9</t>
+          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R6; Story 13 S13-R11)</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4628,7 +4646,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Assignments export failure and nothing-to-export paths use the Export dialog's own messages</t>
+          <t>A deleted rep record still exports one row from the stored name, marked No</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4638,68 +4656,117 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1. A customer exists whose assigned rep's staff record has been cleared or deleted while the customer still references it (seed and delete a throwaway ZZAUTOTEST rep if needed).</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the Sales Representative Assignments CSV.
+2. Find that customer's row and read its "Sales Representative" and "Rep is active?" cells.
+3. If two customers carry different stored name spellings for the same underlying rep, compare their rows.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1. The customer still produces a row — the export never silently drops it.
+2. The "Sales Representative" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
+3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R8; S15-R9)</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Assignments export failure and nothing-to-export use the dialog's messages</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Sales Rep Assignments Export</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. For the empty path: no customer in the organization has an assigned rep (or use a state where the export yields zero rows).
 2. For the failure path: you can force a generation failure (for example, cut the network on Export) — if not forceable, mark that step Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>1. With zero assigned customers, select "Sales Rep Assignments" in the Export Report dialog and click Export.
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. With zero assigned customers, select "Sales Representative Assignments" in the Export Report dialog and click Export.
 2. Read the dialog warning and inspect any downloaded file.
 3. Force a generation failure and read the toast.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 15 S15-R11; S15-N2; §7</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R11; S15-N2; §7)</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Empty state: verbatim message, no grand Totals, toolbar stays interactive</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter set that matches no invoices for any rep (for example, a date range with no activity), with Show Unassigned OFF or with no matching unassigned invoices either.
 2. Read the data area and look for the grand Totals indicator.
@@ -4707,7 +4774,7 @@
 4. Look at the toolbar, then change the date range to a period WITH activity.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
@@ -4716,48 +4783,48 @@
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-R3; S16-N1; §7</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Loading shows a centered spinner over the data area, hides the Totals, keeps the toolbar interactive, and never flashes a blank table</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Reload the report and watch the data area during the initial load.
 2. Change a filter and watch the data area during the re-fetch.
 3. While loading, try to interact with the toolbar.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
@@ -4765,238 +4832,238 @@
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R4</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>A load failure shows the inline "Couldn't load the report. Please try again." message with a working Retry, keeping the filters</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Set several non-default filters.
 2. Force a load/re-fetch failure and read the data area.
 3. Restore the network and click "Retry".</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 16 S16-R5; §7</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; below 1024px the controls stack vertically with the ⋯ button wrapped above</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. Open the report on a phone-sized viewport (real device or browser device emulation, width under 1024px).</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Find and operate each toolbar control by touch: the ⋯ exports, the column selector, the Show Unassigned toggle, the date range picker, Product Type, Invoice Status, and Location.
 2. Look at how the controls are laid out.
 3. Widen the viewport to 1024px or more and compare.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R1; S17-R2; S17-R3</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>On a phone the table scrolls sideways with Subtotal pinned, the totals bar sits outside the scroll area, and the chevrons work on touch</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a phone-sized viewport (under 1024px) with at least one rep row.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the data table sideways and watch the Subtotal column.
 2. Look below the table for the totals bar and swipe the table again.
 3. Tap a rep row's chevron.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Touch targets are at least 44×44 px and touch users get no hover-only tooltips — the icons carry accessible names instead</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a touch device or touch emulation (under 1024px).</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Measure (device emulation ruler/inspector) the touch targets of a row chevron, the Show Unassigned toggle, the ⋯ button, and — via the staff deactivation dialog if opened — the dialog's X.
 2. Tap-and-hold the icon controls and watch for tooltips.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 17 S17-R6; S17-N1; Story 18 S18-R9</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Layout conformance: white toolbar with the specified padding and alignment, blue-grey page, separator line, edge-to-edge white table</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a desktop browser (light mode) with data showing.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar's surface, padding, and how the title and the rightmost control line up with the table columns.
 2. Look at the page background around the data area, the line between the toolbar and the column headers, and the table's side edges.
 3. Look at the header cells, the body cells, the pinned Subtotal cells, and the grand Totals indicator's surface.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a solid white background with padding 32px top / 24px bottom / 2rem left and right; the title's left edge aligns with the leftmost data column, and the rightmost toolbar control (the Location filter) aligns its right edge with the rightmost data column.
 2. The data area sits on the standard blue-grey page background with ZERO horizontal page padding — the toolbar and table run edge-to-edge against the side navigation.
@@ -5005,41 +5072,41 @@
 5. Row types are differentiated by font weight and color, not background color. These rules apply unconditionally whenever the report is rendered.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Dark mode: page, toolbar, table, and Totals switch to dark equivalents; badges and Inv. Hrs stay legible; PDFs stay light</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing, including at least one expanded rep (badges visible) and non-zero Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page, toolbar, header, body cells, and the grand Totals indicator.
@@ -5047,7 +5114,7 @@
 4. Download a PDF while in dark mode and open it.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
@@ -5055,47 +5122,47 @@
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Every icon-only control carries its specified accessible name</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the accessible name of: the ⋯ exports button, the column selector button, one rep row's chevron (collapsed, then expanded), and the header chevron.
 2. Open the staff deactivation dialog (Story 13 flow) and inspect its X close icon.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
@@ -5104,135 +5171,135 @@
 5. Dialog X = "Close".</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R9</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Chevrons and sortable headers are keyboard-operable and expose their expanded/sort state to assistive technology</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Tab to a rep row's chevron; press Enter, then Space.
 2. Tab to a financial column header; press Enter, then Space.
 3. Inspect what state each control exposes to assistive technology.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R10</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>The subdued grey of the (N) count and (Inactive) tag meets WCAG AA contrast, and no information is conveyed by color alone</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a rep row showing a (N) count and — if arrangeable — an "(Inactive)" tag; a contrast-checking tool is available.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Measure the contrast ratio of the subdued-grey (N) count and "(Inactive)" tag against the white body surface in light mode, and against the dark surface in dark mode.
 2. Review how Inv. Hrs, the status badges, and the links convey their meaning.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The subdued grey meets at least WCAG AA contrast (4.5:1 or better) against the body surface in BOTH modes — the reduced font size does not drop it below that ratio.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 18 S18-R11; S18-R12</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>The Sales Rep selector shows in the left panel on standard Work Orders and Part Sale WOs, and is hidden on imported WOs and in History mode</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative selector shows on WO and Part Sale, not on imported</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You have: an open standard Work Order, an open Part Sale WO, an imported Work Order, and a way to view a WO in History mode.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Open the standard Work Order and look at the left panel.
 2. Open the Part Sale WO and look at the left panel.
@@ -5240,159 +5307,115 @@
 4. View a WO in History mode and look for the field.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>1. The left panel includes a "Sales Rep" selector on the standard Work Order.
-2. The left panel includes the same "Sales Rep" selector on the Part Sale WO.
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1. The left panel includes a "Sales Representative" selector on the standard Work Order.
+2. The left panel includes the same "Sales Representative" selector on the Part Sale WO.
 3. The selector is NOT present on the imported Work Order.
-4. The selector is NOT present in History mode.</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R1; S19-N1</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep selector offers only reps whose sales-rep toggle is on</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
+4. The selector is NOT present in History mode.
+5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R1; S19-N1)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Selector offers only reps whose sales-representative toggle is on</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>1. At least one staff member has the sales-rep toggle ON and at least one has it OFF. To arrange this: open Settings, go to Staff, edit the staff member, and use the sales-rep toggle there (restore both afterward).</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a Work Order and open the "Sales Rep" selector.
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1. At least one staff member has the sales-representative toggle ON and at least one has it OFF. To arrange this: open Settings, go to Staff, edit the staff member, and use the sales-representative toggle there (restore both afterward).</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a Work Order and open the "Sales Representative" selector.
 2. Search the option list for both staff members.
 3. Inspect the selector's accessible name.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
-3. The selector carries the accessible name "Sales Rep".</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
+3. The selector carries the accessible name "Sales Representative".
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>A new Work Order or Part Sale WO opens with Sales Rep unassigned, and a change saves immediately with no Save step</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>A new WO opens with Sales Representative unassigned; a change saves at once</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>1. At least one staff member is offered as a sales rep.</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>1. Create a new Work Order (mark it ZZAUTOTEST) and read the Sales Rep field before touching it.
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>1. At least one staff member is offered as a sales representative.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1. Create a new Work Order (mark it ZZAUTOTEST) and read the Sales Representative field before touching it.
 2. Select a rep in the field, then navigate away WITHOUT any explicit save and reopen the WO.
 3. Repeat the unassigned-open check on a new Part Sale WO.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>1. The new Work Order opens with the Sales Rep field UNASSIGNED — it is not pre-filled at creation.
-2. Changing the Sales Rep persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
+2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R3; S19-R4</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>The Sales Rep selector is read-only when the Work Order status is Invoiced or Paid</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Work Order Sales Rep</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>1. One Work Order is in "Invoiced" status and one is in "Paid" status (drive throwaway ZZAUTOTEST WOs into these states if needed).</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Invoiced WO and try to change the Sales Rep field.
-2. Open the Paid WO and try the same.</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>1. On the Invoiced WO the Sales Rep selector is read-only (non-interactive) — the assignment cannot be changed.
-2. On the Paid WO the selector is also read-only.</t>
-        </is>
-      </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R5</t>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R3; S19-R4)</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5401,7 +5424,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Invoice crediting snapshot: WO rep, else the customer's rep, else unassigned — and a later WO change never rewrites past invoices</t>
+          <t>The Sales Representative selector is read-only when Invoiced or Paid</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5416,373 +5439,421 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>1. One Work Order is in "Invoiced" status and one is in "Paid" status (drive throwaway ZZAUTOTEST WOs into these states if needed).</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Invoiced WO and try to change the Sales Representative field.
+2. Open the Paid WO and try the same.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
+2. On the Paid WO the selector is also read-only.
+3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R5)</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Invoice credit snapshot: WO rep, else customer rep, else unassigned</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Work Order Sales Rep</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>1. Three throwaway ZZAUTOTEST setups: (a) a WO WITH a Sales Rep assigned; (b) a WO with NO rep whose customer HAS an assigned rep; (c) a WO with NO rep whose customer has NO assigned rep.</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>1. Three throwaway ZZAUTOTEST setups: (a) a WO WITH a Sales Representative assigned; (b) a WO with NO rep whose customer HAS an assigned rep; (c) a WO with NO rep whose customer has NO assigned rep.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Invoice all three WOs.
 2. On the report (Show Unassigned on, filters covering the invoices), find each invoice and note which row it sits under.
-3. Go back to WO (a), change its Sales Rep to a different rep, and re-check the already-created invoice on the report.</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>1. Invoice (a) is credited to the WO's Sales Rep.
+3. Go back to WO (a), change its Sales Representative to a different rep, and re-check the already-created invoice on the report.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1. Invoice (a) is credited to the WO's Sales Representative.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
-4. Changing WO (a)'s Sales Rep afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3)</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Customer record shows a "Sales Representative" row; "Unassigned" when none</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>1. One customer HAS an assigned sales rep and one customer has NONE.
-2. A Work Order exists whose bound Sales Rep can have their toggle turned off (arrange and restore afterward).</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1. One customer HAS an assigned sales representative and one customer has NONE.
+2. A Work Order exists whose bound Sales Representative can have their toggle turned off (arrange and restore afterward).</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the assigned customer's record and read the left-panel sidebar.
 2. Open the unassigned customer's record and read the same row.
-3. Turn the bound rep's sales-rep toggle OFF, reopen the Work Order, and read the Sales Rep selector; then open its option list.</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Rep" label here) with the customer's assigned rep.
+3. Turn the bound rep's sales-representative toggle OFF, reopen the Work Order, and read the Sales Representative selector; then open its option list.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
-3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R7; S19-E1 — customer-card row label RE-RULED to the full 'Sales Representative' per the PRD companion video 2026-07-30 10:53-11:12, superseding the spec's 'Sales Rep'; video authoritative, newest-wins)</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>SV-8636 (SBR spec Story 19 S19-R7; S19-E1 — customer-card label RE-RULED to the full "Sales Representative" per the PRD companion video 2026-07-30 + Chris Ward answer 2026-07-31 Q5=A; the spec text still says "Sales Rep")</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>A rep's invoice detail rows are fetched from the server only on the first expand, and are paginated per rep</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows, one with a large invoice count if seedable.
 2. The browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note which requests deliver the summary rows.
 2. Expand one rep and watch the network panel; collapse and re-expand it.
 3. If a rep has many invoices, scroll/page through its expanded detail rows.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 6 S6-R2</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Sorting is performed server-side: a header click re-fetches the rep summary rows in the requested order</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several rep rows; the network panel is open.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Click a financial column header and watch the network panel.
 2. Click the same header again (descending) and watch again.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 11 S11-R5</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>The grand totals are server-computed over the full filtered result set and delivered with the summary payload</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Load the report with everything collapsed and inspect the summary response and the grand Totals indicator.
 2. Compare the grand totals against the full filtered result (for example, via the Summary CSV), not just the loaded rows.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 10 S10-R5</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>All four exports are generated server-side against the active filters and sort — a genuine failure yields a toast, never a malformed file</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Trigger each of the four downloads and observe the export requests and responses.
 2. Compare the delivered files against the active filters and sort.
 3. If forceable, fail one export server-side and check what (if anything) downloads.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-R2a; S14-N2; S14-E3</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>The Expanded View PDF's 10,000-row cap is enforced server-side BEFORE generation — a refusal, not a truncated file</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. A filter set producing more than 10,000 invoice detail rows exists or can be seeded — otherwise mark Blocked-Env with the reason.
 2. The network panel is open.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download Expanded View (PDF)" against the over-cap filter set and observe the export request/response.
 2. Check whether any file arrives.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>specs/sbr-sales-by-representative.md Story 14 S14-E2</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Toggling a sales rep's active status off first runs a server pre-check returning the assigned-customer count and an assignments flag</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Deactivating a rep first runs a server pre-check returning the count</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>1. A staff member is active with the sales-rep toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1. A staff member is active with the sales-representative toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
 2. The network panel is open.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. In staff administration, toggle that staff member's active status off and watch the network panel BEFORE the dialog appears.
 2. Read the pre-check response and compare it with the dialog's "{N} customer{s}" headline.
 3. Cancel the dialog (leave the staff member active).</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales rep, plus a flag indicating whether any assignments exist.
-2. The dialog's "{Staff Name} is the sales rep on {N} customer{s}." headline matches the returned count.
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
+2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R4</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R4)</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6 — 'at the bottom' re-based to below-the-named-anchors [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05; order among the four new reports not important)</t>
+          <t>SV-8619 (SBR spec Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6 — 'at the bottom' = below the four named anchor reports per PRD video 2026-07-30 01:18-02:05; order among the four new reports not important)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>The navigation entry's padding fits the full Sales By Representative label without crowding or truncation</t>
+          <t>The nav entry fits the full Sales By Representative label; no truncation</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R7; §1 naming note</t>
+          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R7; §1 naming note)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Every user who can see any other Performance report also sees Sales By Representative</t>
+          <t>Sales By Representative is visible to anyone who sees another Performance report</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R1</t>
+          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R1)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -681,7 +681,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A user without staff-administration access cannot reach the sales-rep deactivation flow</t>
+          <t>Without staff-administration access the deactivation flow is unreachable</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-N1</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -763,7 +763,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 2 S2-R1; S2-R2</t>
+          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R1; S2-R2)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -772,7 +772,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Custom range uses the date-picker dialog and holds the user to a 366-day maximum span</t>
+          <t>A Custom range uses the date-picker and holds a 366-day maximum span</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 2 S2-R3; S2-R6</t>
+          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R3; S2-R6)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>An invoice is placed in the range by its own invoice date with inclusive endpoints, and the range shows in both PDF headers</t>
+          <t>An invoice sits in the range by its own invoice date; endpoints included</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 2 S2-R5; S2-R8; §3</t>
+          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R5; S2-R8; §3)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -918,7 +918,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Invoice Status dropdown offers exactly four options with All Statuses as the default</t>
+          <t>Invoice Status offers exactly four options; All Statuses is the default</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 4 S4-R1; S4-R2; S4-R3; S4-R5</t>
+          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R1; S4-R2; S4-R3; S4-R5)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -967,7 +967,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Status filtering matches on the mapped display value: five system states collapse into Paid, Partially Paid and Unpaid</t>
+          <t>Status filtering matches on the mapped display value</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 4 S4-R4; §3 payment-status mapping</t>
+          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R4; §3 payment-status mapping)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 4 S4-R7; S4-R6; S4-N1; Story 3 S3-R8; S3-N1</t>
+          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R7; S4-R6; S4-N1; Story 3 S3-R8; S3-N1)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 4 S4-R8</t>
+          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R8)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Location filter is the rightmost toolbar control, a multi-select with an All Locations option</t>
+          <t>Location filter is the rightmost control with an All Locations option</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 21 S21-R1; Story 18 S18-R7.2</t>
+          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R1; Story 18 S18-R7.2)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R3; S21-R4; S21-R5; §3 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins)) + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins)</t>
+          <t>SV-8638 (SBR spec Story 21 S21-R3; S21-R4; S21-R5; §3 — per-row location identifier in All-Locations view ADDED per kickoff video P10 [ruling 2026-07-28 video-overrides-spec]) + on-screen location-scope indicator per Chris Ward 2026-07-29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>The Location filter is hidden for a user with access to only one location</t>
+          <t>Sales By Representative: Location filter hidden for a one-location user</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (SBR spec S21-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S21-N1 "still sees the filter" note is stale, spec edit pending)</t>
+          <t>SV-8638 (SBR spec S21-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S21-N1 "still sees the filter" note is stale; spec edit pending)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13 — per-row Location column, "Multiple" verbatim on a rep row spanning locations, position after Status, constant-width filter)</t>
+          <t>SV-8638 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13 — per-row Location column; "Multiple" verbatim on a rep row spanning locations; position after Status; constant-width filter)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Contributors only: a rep row appears if and only if the rep has at least one non-reversed invoice matching all active filters</t>
+          <t>A rep row appears only when the rep has a matching non-reversed invoice</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions</t>
+          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a</t>
+          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>A toggled-off or deleted contributor still appears with credit intact, tagged (Inactive), named from the latest invoice snapshot when deleted</t>
+          <t>A toggled-off or deleted contributor still appears; tagged (Inactive)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 5 S5-R9; §3 Key Decisions; §4 Snapshot</t>
+          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R9; §3 Key Decisions; §4 Snapshot)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Expanding a rep loads its invoices on demand with a brief row-level loading indicator and full detail-row contents</t>
+          <t>Expanding a rep loads its invoices on demand with a row-level spinner</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 6 S6-R1; S6-R2; S6-R3; S6-E1</t>
+          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R1; S6-R2; S6-R3; S6-E1)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Header chevron expands every visible rep in one action and its glyph tracks the expand/collapse state</t>
+          <t>The header chevron expands every visible rep and its glyph tracks state</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 6 S6-R5; S6-R6</t>
+          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Each invoice appears under exactly one rep or the Unassigned row, never more than one</t>
+          <t>Each invoice appears under exactly one rep or the Unassigned row</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 6 S6-R7; §3 Key Decisions</t>
+          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R7; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1607,7 +1607,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Expansion survives filter and sort changes within the session, resets on reload, and a removed rep returns collapsed</t>
+          <t>Expansion survives filter and sort changes within the session, resets on reload</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 6 S6-R8; S6-N1; Story 23 S23-R2</t>
+          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R8; S6-N1; Story 23 S23-R2)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Detail rows order newest first with a numeric invoice-number tie-break where P sorts before S</t>
+          <t>Detail rows run newest first with a numeric invoice-number tie-break</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 6 S6-R9; Story 11 S11-R2</t>
+          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R9; Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1738,13 +1738,13 @@
         <is>
           <t>1. The Status column sits between the Customer column and the Inv. Hrs column.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
-3. The mapping matches §3: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
+3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6</t>
+          <t>SV-8625 (specs/sbr-sales-by-representative.md Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Badge colors use the application's canonical payment-status tokens in both light and dark mode</t>
+          <t>Badge colors use the canonical payment-status tokens in light and dark</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 8 S8-R3; Story 18 S18-R8</t>
+          <t>SV-8625 (specs/sbr-sales-by-representative.md Story 8 S8-R3; Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs heading is verbatim and the value is hours invoiced minus hours worked, rounded half-up to one decimal</t>
+          <t>Inv. Hrs is hours invoiced minus hours worked; half-up to one decimal</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 9 S9-R1; S9-R2; §3</t>
+          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-R1; S9-R2; §3)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2</t>
+          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>No-labor-no-time invoices show 0.0 but clocked-yet-unbilled work shows its negative delta, never suppressed</t>
+          <t>No-labor-no-time invoices show 0.0; clocked-unbilled work shows negative</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 9 S9-N1</t>
+          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-N1)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Margin % renders to one decimal with a % sign, shows an em dash when Subtotal is zero or below, and is recomputed on every rollup</t>
+          <t>Margin % to one decimal; em dash when Subtotal &lt;= 0; recomputed on rollups</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md §3 Margin % definition; Story 10 S10-R5</t>
+          <t>SV-8627 (specs/sbr-sales-by-representative.md §3 Margin % definition; Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Money columns use the standardized labels and definitions: Subtotal is pre-tax Labor plus Parts Invoiced, Margin is the two margins combined</t>
+          <t>Money columns use the standardized labels and definitions</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md §3 definitions; §4 Terminology</t>
+          <t>SV-8582 (SBR spec §3 definitions; §4 Terminology — money-column labels and the Subtotal/Margin definitions; CROSS-CUTTING across every SBR row level with no single owning story)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2039,7 +2039,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Negative dollar values render in accounting parentheses on screen, in money columns only</t>
+          <t>Negative dollar values render in accounting parentheses; money columns only</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md §3 Key Decisions (accounting parentheses)</t>
+          <t>SV-8593 (SBR spec §3 Key Decisions accounting parentheses — owned by the shared A5 report-shell formatter module: verbatim 'accounting-parens negatives')</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md §3 rounding rule</t>
+          <t>SV-8582 (SBR spec §3 half-up rounding rule + round of unrounded rollups; CROSS-CUTTING display rule with no single owning story)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5</t>
+          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Desktop Totals row merges the four identifier columns, aggregates every metric over the full filtered set, and sticks to the bottom</t>
+          <t>Desktop Totals row merges the identifier columns and sticks to the bottom</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 10 S10-R5; S10-N1; Story 16 S16-R4</t>
+          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5; S10-N1; Story 16 S16-R4)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Mobile shows a simplified external totals bar below the table with Totals left and the grand Subtotal right</t>
+          <t>Mobile shows a simplified totals bar below the table; Subtotal at right</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 10 S10-R5 (mobile); Story 17 S17-R4</t>
+          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5 (mobile); Story 17 S17-R4)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>All eight financial columns are sortable; the identifier columns are not and the Date header carries the chevron instead</t>
+          <t>All eight financial columns are sortable</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 11 S11-R1; S11-R6</t>
+          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R1; S11-R6)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2378,7 +2378,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Default order is plain A to Z by display name, case-insensitive, with no active/inactive tiers</t>
+          <t>Default order is plain A to Z by display name, case-insensitive</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 11 S11-R4; §3 Key Decisions</t>
+          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>First click sorts ascending with an indicator, second click descending, no third cleared state, and no header path back to A to Z</t>
+          <t>First header click sorts ascending; second descending; no third state</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 11 S11-R5; Story 23 S23-R5</t>
+          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R5; Story 23 S23-R5)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2473,7 +2473,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Sorting reorders rep summary rows only; detail rows stay under their rep and the Unassigned row stays pinned on top</t>
+          <t>Sorting reorders rep rows only; Unassigned stays pinned on top</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 11 S11-R2; Story 22 S22-R4</t>
+          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R2; Story 22 S22-R4)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Equal sorted values keep the A to Z order as tie-break and an em-dash Margin % sorts as zero</t>
+          <t>Ties keep the A to Z order and an em-dash Margin % sorts as zero</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 11 S11-R7</t>
+          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2; S12-R3</t>
+          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2; S12-R3)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Browser back from a drilldown restores ALL report state including expansion and scroll, without a full reload</t>
+          <t>Browser back from a drilldown restores expansion and scroll; no reload</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 12 S12-R3a; Story 23 S23-R2</t>
+          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R3a; Story 23 S23-R2)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Link styling: theme-primary invoice links and body-colored customer links, hover/focus underline, never browser-purple, in both modes</t>
+          <t>Invoice links use theme-primary; customer links use the body color</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 12 S12-R4; S12-R5; S12-R6; S12-N3</t>
+          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R4; S12-R5; S12-R6; S12-N3)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2711,7 +2711,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>An unavailable invoice or customer destination shows the standard not-found/access-denied state and back still returns</t>
+          <t>An unavailable link destination shows the standard not-found state</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 12 S12-N1; S12-N2</t>
+          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-N1; S12-N2)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Type-YES gate: auto-focused input, case-insensitive whitespace-tolerant match, disabled-button tooltip, Enter submits</t>
+          <t>Type-YES gate: auto-focus; case-insensitive match; Enter submits</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R6; S13-R7</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R6; S13-R7)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>A server-side deactivation failure shows the canonical error toast, leaves the status unchanged, and clears the input on the next open</t>
+          <t>A deactivation failure shows the error toast and leaves the status alone</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-N5; §7</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N5; §7)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>If the assignment pre-check fails, the warning dialog still opens — without the count headline — and never silently deactivates</t>
+          <t>If the assignment pre-check fails, the warning dialog still opens</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-N4</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N4)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1</t>
+          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>No empty Unassigned row is ever rendered, and toggling off while expanded removes the row which returns collapsed</t>
+          <t>No empty Unassigned row is ever rendered</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 22 S22-N1; Story 6 S6-N2</t>
+          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-N1; Story 6 S6-N2)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1</t>
+          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3341,7 +3341,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Toggling a column applies immediately across summary rows, detail rows and the grand Totals at once</t>
+          <t>Toggling a column applies at once to summary; detail and Totals rows</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 20 S20-R4; S20-R7</t>
+          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R4; S20-R7)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3387,7 +3387,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Column visibility never affects the exports — all four downloads always include all metric columns</t>
+          <t>Column visibility never affects the exports</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 20 S20-R8</t>
+          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R8)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3432,7 +3432,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Hiding the active sort column keeps the sort; showing it again reveals the sort indicator</t>
+          <t>Hiding the active sort column keeps the sort</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 20 S20-R9</t>
+          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R9)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3478,7 +3478,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>All filter and view settings are remembered per browser and restored before the first data fetch on the next visit</t>
+          <t>All filter and view settings are restored before the first data fetch</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 23 S23-R1; Story 20 S20-R5</t>
+          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R1; Story 20 S20-R5)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 23 S23-R2; §2 Out of Scope</t>
+          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R2; §2 Out of Scope)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3571,7 +3571,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Restoration is defensive: a stale saved value falls back to its default and never causes an error or invalid request</t>
+          <t>A stale saved value falls back to its default and never errors</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 23 S23-R3</t>
+          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R3)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1; Story 2 S2-R4; Story 21 S21-R2</t>
+          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1; Story 2 S2-R4; Story 21 S21-R2)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3664,7 +3664,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>The A to Z default is its own saved value: restoring a state with no financial sort returns to A to Z, not an arbitrary column</t>
+          <t>The A to Z default is its own saved value</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 23 S23-R5; Story 11 S11-R4</t>
+          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R5; Story 11 S11-R4)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R1; Story 17 S17-R3 (position)</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R1; Story 17 S17-R3 (position))</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
+          <t>SV-8631 (SBR spec Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4 + Locations: line in every export per Chris Ward msg 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Summary PDF: A4 header strip, one rolled-up row per rep, bold Subtotal, colored Inv. Hrs, and a recomputed grand totals row</t>
+          <t>Summary PDF: one rolled-up row per rep with a recomputed grand totals row</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R3; S14-R5; Story 2 S2-R5; §3 Margin % definition</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R3; S14-R5; Story 2 S2-R5; §3 Margin % definition)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3861,7 +3861,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Expanded View PDF: one page-block per rep with its own header strip, per-invoice table, per-rep totals row, and no grand totals</t>
+          <t>Expanded View PDF: one page-block per rep with its own totals; no grand</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R6; S14-R8; Story 6 S6-R9</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R6; S14-R8; Story 6 S6-R9)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3913,7 +3913,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Expanded View PDF truncates invoice numbers longer than 18 characters; on screen they are never truncated</t>
+          <t>Expanded View PDF truncates invoice numbers longer than 18 characters</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R7</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R7)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R4; S14-R3a; S14-R11</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R4; S14-R3a; S14-R11)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag, and omit the on-screen (N) count</t>
+          <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R9; S14-R10</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R9; S14-R10)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R12; S14-R13</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4306,7 +4306,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>A failed download shows the canonical error toast, and a generating download shows a non-interactive loading state</t>
+          <t>A failed download shows the canonical error toast</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-N1; S14-N2; S14-E1; §7</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4401,7 +4401,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>An empty-data export still generates: zeroed Summary PDF totals, header-strip-only Expanded PDF, header-row-only CSVs</t>
+          <t>An empty-data export still generates with zeroed Summary PDF totals</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-E3</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E3)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-R3; S16-N1; §7</t>
+          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-R3; S16-N1; §7)</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4794,7 +4794,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Loading shows a centered spinner over the data area, hides the Totals, keeps the toolbar interactive, and never flashes a blank table</t>
+          <t>Loading shows a centered spinner over the data area and hides the Totals</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 16 S16-R4</t>
+          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R4)</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4843,7 +4843,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>A load failure shows the inline "Couldn't load the report. Please try again." message with a working Retry, keeping the filters</t>
+          <t>A load failure shows the inline could-not-load message with a Retry</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 16 S16-R5; §7</t>
+          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R5; §7)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4891,7 +4891,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>On a phone every toolbar control works on touch; below 1024px the controls stack vertically with the ⋯ button wrapped above</t>
+          <t>On a phone every toolbar control works on touch</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 17 S17-R1; S17-R2; S17-R3</t>
+          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R1; S17-R2; S17-R3)</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4939,7 +4939,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>On a phone the table scrolls sideways with Subtotal pinned, the totals bar sits outside the scroll area, and the chevrons work on touch</t>
+          <t>On a phone the table scrolls sideways with Subtotal pinned outside it</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile)</t>
+          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile))</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4987,7 +4987,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Touch targets are at least 44×44 px and touch users get no hover-only tooltips — the icons carry accessible names instead</t>
+          <t>Touch targets are at least 44×44 px and touch users get no hover-only tooltips</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 17 S17-R6; S17-N1; Story 18 S18-R9</t>
+          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R6; S17-N1; Story 18 S18-R9)</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Layout conformance: white toolbar with the specified padding and alignment, blue-grey page, separator line, edge-to-edge white table</t>
+          <t>Layout: white toolbar; blue-grey page; separator; edge-to-edge white table</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1</t>
+          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1)</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Dark mode: page, toolbar, table, and Totals switch to dark equivalents; badges and Inv. Hrs stay legible; PDFs stay light</t>
+          <t>Dark mode: page, toolbar, table; Totals switch to dark equivalents</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 18 S18-R8</t>
+          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 18 S18-R9</t>
+          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R9)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5182,7 +5182,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Chevrons and sortable headers are keyboard-operable and expose their expanded/sort state to assistive technology</t>
+          <t>Chevrons and sortable headers are keyboard-operable and expose their state</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 18 S18-R10</t>
+          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R10)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -5230,7 +5230,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>The subdued grey of the (N) count and (Inactive) tag meets WCAG AA contrast, and no information is conveyed by color alone</t>
+          <t>The subdued grey of the (N) count and (Inactive) tag meets WCAG AA contrast</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 18 S18-R11; S18-R12</t>
+          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R11; S18-R12)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -5570,7 +5570,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>A rep's invoice detail rows are fetched from the server only on the first expand, and are paginated per rep</t>
+          <t>A rep's invoice detail rows are fetched from the server only on the first expand</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 6 S6-R2</t>
+          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R2)</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5619,7 +5619,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Sorting is performed server-side: a header click re-fetches the rep summary rows in the requested order</t>
+          <t>Sorting is performed server-side and returns the first page</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 11 S11-R5</t>
+          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5666,7 +5666,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>The grand totals are server-computed over the full filtered result set and delivered with the summary payload</t>
+          <t>Grand totals are server-computed over the full filtered set</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 10 S10-R5</t>
+          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5713,7 +5713,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>All four exports are generated server-side against the active filters and sort — a genuine failure yields a toast, never a malformed file</t>
+          <t>All four exports are generated server-side against the active filters and sort</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-R2a; S14-N2; S14-E3</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R2a; S14-N2; S14-E3)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5761,7 +5761,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>The Expanded View PDF's 10,000-row cap is enforced server-side BEFORE generation — a refusal, not a truncated file</t>
+          <t>The Expanded View PDF's 10,000-row cap is enforced server-side BEFORE generation</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 14 S14-E2</t>
+          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E2)</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -1290,7 +1290,8 @@
 5. Read the Location cell on the Unassigned summary row.
 6. Check that the pinned Subtotal column is still the rightmost column.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
+9. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1302,12 +1303,13 @@
 5. The Unassigned summary row follows the same rule as any rep summary row.
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+9. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13 — per-row Location column; "Multiple" verbatim on a rep row spanning locations; position after Status; constant-width filter)</t>
+          <t>SV-8638; SV-8631 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13; S14-R20 — per-row Location column; "Multiple" on a rep row spanning locations; position after Status; constant-width filter; S14-R20 = the same column in all four exports)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1398,7 +1400,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. The columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns).
+          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
@@ -1407,7 +1409,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a)</t>
+          <t>SV-8623; SV-8638 (SBR spec v15 2026-07-29 Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a + Story 21 S21-R7 — plus the Location column after Status)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -3655,7 +3657,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1; Story 2 S2-R4; Story 21 S21-R2)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R4; S23-N1; Story 2 S2-R4; S2-R7; Story 21 S21-R2)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3845,14 +3847,14 @@
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
-3. The columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
+3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added with the identifying columns ahead of Inv. Hrs, and a rep who spans more than one location reads "Multiple" (this file has no Status column for it to follow — confirm its exact position in the build).
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R3; S14-R5; Story 2 S2-R5; §3 Margin % definition)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3; S14-R5; S14-R20; Story 2 S2-R5; §3 Margin % definition — Summary PDF; plus the automatic Location column in all four exports)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3895,7 +3897,7 @@
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
-2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
+2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, only when more than one location is in scope, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
@@ -3904,7 +3906,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R6; S14-R8; Story 6 S6-R9)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R6; S14-R8; S14-R20; Story 6 S6-R9 — Expanded PDF page-block per rep; plus the automatic Location column after Status)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4139,16 +4141,17 @@
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
-2. The headers, in order, are exactly: Sales Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. With a single location in scope the headers, in order, are exactly: Sales Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
-6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R15; S14-R18)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R15; S14-R18; S14-R20 — Summary CSV headers; plus the automatic Location column in all four exports; S14-R15's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4190,14 +4193,15 @@
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
-2. The headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. With a single location in scope the headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R16)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R16; S14-R20 — Expanded CSV headers; plus the automatic Location column after Status; S14-R16's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4785,7 +4789,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-R3; S16-N1; §7)</t>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R1; S16-R2; S16-R3; S16-N1; Story 2 S2-N1; Story 21 S21-N2; §7)</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales By Representative" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sales By Representative" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -909,7 +909,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8621 (specs/sbr-sales-by-representative.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6; S3-R7)</t>
+          <t>SV-8621 (SBR spec v15 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6; S3-R7 — S3-R2 CLOSES the list itself ("exactly three options"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R1; S4-R2; S4-R3; S4-R5)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R1; S4-R2; S4-R3; S4-R5 — S4-R2 CLOSES the list itself ("exactly four options"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8582 (SBR spec §3 definitions; §4 Terminology — money-column labels and the Subtotal/Margin definitions; CROSS-CUTTING across every SBR row level with no single owning story)</t>
+          <t>SV-8623; SV-8582 (SBR spec v15 2026-07-29 S5-R2 = the authoritative 12-column left-to-right order; §3 definitions; §4 Terminology — S5-R2 CLOSES the money-label list; Location sits after Status [S21-R7] and is not a money column)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5 (mobile); Story 17 S17-R4)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5 (mobile branch) + Story 17 S17-R4 — S10-R5 CLOSES it in the spec's own words: "Totals" left and the grand Subtotal right "(no other metrics)")</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -3329,12 +3329,13 @@
           <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
-4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.</t>
+4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
+5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1 — S20-R2/S20-R3 CLOSE the seven toggles and the five always-on columns; Location is automatic and in neither list [S21-R7])</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3750,7 +3751,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R1; Story 17 S17-R3 (position))</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R1 + Story 17 S17-R3 (position) — S14-R1 CLOSES it in the spec's own words ("lists exactly four actions"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3803,7 +3804,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4 + Locations: line in every export per Chris Ward msg 2026-07-29 [newest-wins])</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2; S14-R2a; S14-R20 + Story 21 S21-R6 + Story 22 S22-R4 — all four downloads honour the filters; the full result set and the active order; S14-R20 = the "Locations:" line in every export)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -4002,7 +4003,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R4; S14-R3a; S14-R11)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3a; S14-R4; S14-R11 — S14-R11 CLOSES both PDF filenames verbatim ("deterministic") and S14-R4 closes the footer string; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4396,7 +4397,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E2; §7)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2; §7 — 10k-row export cap; no truncated file; toast persists 120s; the toast STRING is the ONE suite-wide message ruled by Chris Ward 2026-07-31 Q2=A [newest-wins]; his SBR spec edit is pending)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4540,12 +4541,13 @@
           <t>1. The file downloads as "sales-representative-assignments.csv (the short form "rep" is gone from the file name — confirm the exact final file name in the build)".
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R3; S15-R4; §7)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R3; S15-R4; §7 — S15-R4 CLOSES the three headers; "Sales Rep"→"Sales Representative" per Chris Ward 2026-07-31 Q5 [newest-wins]; NOT one of the four report exports so S14-R20 adds no Location)</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -5254,24 +5256,25 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with a rep row showing a (N) count and — if arrangeable — an "(Inactive)" tag; a contrast-checking tool is available.</t>
+          <t>1. You are on the report with a rep row showing a (N) count and - if arrangeable - an "(Inactive)" tag.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>1. Measure the contrast ratio of the subdued-grey (N) count and "(Inactive)" tag against the white body surface in light mode, and against the dark surface in dark mode.
+          <t>1. Read the subdued-grey (N) count and the "(Inactive)" tag in light mode, then switch to dark mode and read them again.
 2. Review how Inv. Hrs, the status badges, and the links convey their meaning.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1. The subdued grey meets at least WCAG AA contrast (4.5:1 or better) against the body surface in BOTH modes — the reduced font size does not drop it below that ratio.
-2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.</t>
+          <t>1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
+2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R11; S18-R12)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R11; S18-R12 — subdued-grey (N) count and "(Inactive)" tag at ≥ 4.5:1 WCAG AA in both modes; nothing conveyed by colour alone; the ratio is a design-token property so the check is by-eye)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -797,8 +797,8 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Pick "Custom" and select a start and end date within 366 days; apply.
-2. Pick "Custom" again and try to select a start-to-end span of more than 366 days (start and end dates inclusive).</t>
+          <t>1. Open the date range picker and select a start and end date within 366 days on the calendar shown inside it; apply.
+2. Open it again and try to select a start-to-end span of more than 366 days (start and end dates inclusive).</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5464,7 +5464,8 @@
         <is>
           <t>1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.
-3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -527,7 +527,9 @@
 2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
 3. Selecting the entry opens the report in the main content area.
 4. The page title reads "Sales By Representative".
-5. The browser tab title reads "Sales By Representative - Report | ShopView".</t>
+5. The browser tab title reads "Sales By Representative - Report | ShopView".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -573,12 +575,14 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
-2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.</t>
+2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R7).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R7; §1 naming note)</t>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R7; §1 naming note)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -618,12 +622,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.</t>
+          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R1)</t>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R1)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -667,12 +673,14 @@
         <is>
           <t>1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
 2. The report (and its ⋯ export menu) is not reachable.
-3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.</t>
+3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1)</t>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -711,12 +719,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.</t>
+          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N1)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -758,12 +768,14 @@
         <is>
           <t>1. A date range picker is visible in the report toolbar.
 2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
-3. There is no "All Time" option (removed by the 2026-07-16 spec round).</t>
+3. There is no "All Time" option (removed by the 2026-07-16 spec round).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R1; S2-R2)</t>
+          <t>SV-8620 (SBR spec v15 2026-07-29 Story 2 S2-R1; S2-R2)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -804,12 +816,14 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. A custom range within the cap applies normally via the date-picker dialog.
-2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.</t>
+2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R3; S2-R6)</t>
+          <t>SV-8620 (SBR spec v15 2026-07-29 Story 2 S2-R3; S2-R6)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -852,12 +866,14 @@
         <is>
           <t>1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
 2. The date used is the invoice's own date — the value shown in the Date column.
-3. The chosen date range is reflected in both PDF exports' header strips.</t>
+3. The chosen date range is reflected in both PDF exports' header strips.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R5; S2-R8; §3)</t>
+          <t>SV-8620 (SBR spec v15 2026-07-29 Story 2 S2-R5; S2-R8; §3)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -904,7 +920,9 @@
 2. "Parts only" includes only invoices whose number starts with P.
 3. "Service only" includes only invoices whose number starts with S.
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
-5. Each change re-fetches and re-renders the report.</t>
+5. Each change re-fetches and re-renders the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -953,7 +971,9 @@
           <t>1. An "Invoice Status" dropdown is visible in the toolbar.
 2. It offers exactly four options: "All Statuses," "Unpaid," "Partially Paid," "Paid."
 3. "All Statuses" is the default on first load.
-4. Changing the selection re-fetches and re-renders the report.</t>
+4. Changing the selection re-fetches and re-renders the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1003,12 +1023,14 @@
           <t>1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
 2. "Partially Paid" includes the partially-paid AND the prepaid-with-a-balance-owed invoices.
 3. "Unpaid" includes only the unpaid invoice.
-4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.</t>
+4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R4).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R4; §3 payment-status mapping)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R4; §3 payment-status mapping)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1053,12 +1075,14 @@
           <t>1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
 2. A rep appears only if at least one invoice matches all active filters.
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
-4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.</t>
+4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R7; S4-R6; S4-N1; Story 3 S3-R8; S3-N1)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R7; S4-R6; S4-N1; Story 3 S3-R8; S3-N1)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1098,12 +1122,14 @@
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
-2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.</t>
+2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R8).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R8)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R8)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1144,12 +1170,14 @@
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. The location filter is the rightmost control in the toolbar.
-2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.</t>
+2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R1; Story 18 S18-R7.2)</t>
+          <t>SV-8638 (SBR spec v15 2026-07-29 Story 21 S21-R1; Story 18 S18-R7.2)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1196,7 +1224,9 @@
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
 3. "All Locations" means all locations the user can access — location Z's data is never included.
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1242,7 +1272,9 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1290,8 +1322,7 @@
 5. Read the Location cell on the Unassigned summary row.
 6. Check that the pinned Subtotal column is still the rightmost column.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
-9. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
+8. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1303,8 +1334,9 @@
 5. The Unassigned summary row follows the same rule as any rep summary row.
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-9. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.</t>
+8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1353,12 +1385,14 @@
           <t>1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
-4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.</t>
+4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions)</t>
+          <t>SV-8623 (SBR spec v15 2026-07-29 Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1404,7 +1438,9 @@
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
-5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.</t>
+5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1454,12 +1490,14 @@
           <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
-4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.</t>
+4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R9).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R9; §3 Key Decisions; §4 Snapshot)</t>
+          <t>SV-8623 (SBR spec v15 2026-07-29 Story 5 S5-R9; §3 Key Decisions; §4 Snapshot)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1501,12 +1539,14 @@
         <is>
           <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
-3. A rep with a single matching invoice can still be expanded — one detail row is shown.</t>
+3. A rep with a single matching invoice can still be expanded — one detail row is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R1; S6-R2; S6-R3; S6-E1)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R1; S6-R2; S6-R3; S6-E1)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1549,12 +1589,14 @@
         <is>
           <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
-3. A second activation collapses them all.</t>
+3. A second activation collapses them all.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R5; S6-R6)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1595,12 +1637,14 @@
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
-2. The sum of all (N) counts equals the number of matching invoices.</t>
+2. The sum of all (N) counts equals the number of matching invoices.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R7).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R7; §3 Key Decisions)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R7; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1643,12 +1687,14 @@
         <is>
           <t>1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
-3. A full page reload resets all expansion.</t>
+3. A full page reload resets all expansion.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R8; S6-N1; Story 23 S23-R2)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R8; S6-N1; Story 23 S23-R2)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1691,12 +1737,14 @@
           <t>1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
-4. This order is independent of the rep-row column sort (which reorders summary rows only).</t>
+4. This order is independent of the rep-row column sort (which reorders summary rows only).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R9; Story 11 S11-R2)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R9; Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1738,15 +1786,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The Status column sits between the Customer column and the Inv. Hrs column.
+          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
-4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.</t>
+4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8625 (specs/sbr-sales-by-representative.md Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6)</t>
+          <t>SV-8625 (SBR spec v15 2026-07-29 Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1788,12 +1838,14 @@
         <is>
           <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
-3. The treatment stays legible and consistent in both light and dark mode.</t>
+3. The treatment stays legible and consistent in both light and dark mode.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8625 (specs/sbr-sales-by-representative.md Story 8 S8-R3; Story 18 S18-R8)</t>
+          <t>SV-8625 (SBR spec v15 2026-07-29 Story 8 S8-R3; Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1834,12 +1886,14 @@
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
-2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.</t>
+2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-R1; S9-R2; §3)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R1; S9-R2; §3)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1885,12 +1939,14 @@
           <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
-4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).</t>
+4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1931,12 +1987,14 @@
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
-2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.</t>
+2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-N1).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-N1)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-N1)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1979,12 +2037,14 @@
         <is>
           <t>1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
-3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.</t>
+3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md §3 Margin % definition; Story 10 S10-R5)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 §3 Margin % definition; Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2027,7 +2087,9 @@
           <t>1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
-4. The same values appear everywhere the numbers show (screen, and later the exports).</t>
+4. The same values appear everywhere the numbers show (screen, and later the exports).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2073,7 +2135,9 @@
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
-2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.</t>
+2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2119,7 +2183,9 @@
         <is>
           <t>1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
-3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.</t>
+3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 half).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2167,12 +2233,14 @@
         <is>
           <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
-3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.</t>
+3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R2).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2219,12 +2287,14 @@
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
 3. Subtotal values are bold across the header, every summary row, every detail row, and the grand Totals indicator.
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
-5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).</t>
+5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2270,12 +2340,14 @@
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
 3. The grand totals cover the FULL filtered result set — every matching non-reversed invoice across every rep, independent of which reps are expanded or loaded.
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
-5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.</t>
+5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5; S10-N1; Story 16 S16-R4)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5; S10-N1; Story 16 S16-R4)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2319,7 +2391,9 @@
           <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
-4. It uses the white card surface with a thin top border.</t>
+4. It uses the white card surface with a thin top border.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2366,12 +2440,14 @@
         <is>
           <t>1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
-3. The Date header carries the expand/collapse-all chevron, not a sort affordance.</t>
+3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R1; S11-R6)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R1; S11-R6)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2411,12 +2487,14 @@
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Rows render in A→Z order by display name, case-insensitive.
-2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.</t>
+2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R4).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R4; §3 Key Decisions)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2461,12 +2539,14 @@
           <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
 3. There is no third "cleared" state — the third click returns to ascending.
-4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.</t>
+4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R5; Story 23 S23-R5)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R5; Story 23 S23-R5)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2508,12 +2588,14 @@
         <is>
           <t>1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
-3. The Unassigned row stays pinned to the top regardless of sort.</t>
+3. The Unassigned row stays pinned to the top regardless of sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R2; Story 22 S22-R4)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R2; Story 22 S22-R4)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2554,12 +2636,14 @@
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
-2. A Margin % cell rendered "—" (undefined) sorts as zero.</t>
+2. A Margin % cell rendered "—" (undefined) sorts as zero.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R7).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R7)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2602,12 +2686,14 @@
         <is>
           <t>1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
-3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.</t>
+3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2; S12-R3)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R1; S12-R2; S12-R3)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2650,12 +2736,14 @@
         <is>
           <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
-3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.</t>
+3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R3a; Story 23 S23-R2)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R3a; Story 23 S23-R2)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2699,12 +2787,14 @@
           <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
 3. Both hold in light and dark mode and across return visits.
-4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.</t>
+4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R4; S12-R5; S12-R6; S12-N3)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R4; S12-R5; S12-R6; S12-N3)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2745,12 +2835,14 @@
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
-2. Pressing back still returns to the report.</t>
+2. Pressing back still returns to the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-N1; S12-N2)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-N1; S12-N2)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2793,12 +2885,14 @@
         <is>
           <t>1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
-3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.</t>
+3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R3; S13-R4; S13-R12)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R3; S13-R4; S13-R12)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2843,12 +2937,14 @@
           <t>1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
-4. Pressing Enter while valid submits.</t>
+4. Pressing Enter while valid submits.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R6; S13-R7)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R6; S13-R7)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2895,12 +2991,14 @@
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
 3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
 4. Clicking outside the dialog does NOT close it.
-5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.</t>
+5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R8).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R8)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R8)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2943,12 +3041,14 @@
           <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
-4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.</t>
+4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2991,12 +3091,14 @@
         <is>
           <t>1. The sales-representative toggle state is unchanged by the deactivation flow.
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
-3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).</t>
+3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3040,12 +3142,14 @@
           <t>1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
 3. After reactivation the assignments re-surface immediately with no extra action.
-4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.</t>
+4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R2; S13-N2; S13-N3; S13-E3)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R2; S13-N2; S13-N3; S13-E3)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3088,12 +3192,14 @@
         <is>
           <t>1. An error toast is shown: "Ooooops! An error occured" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
-3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.</t>
+3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N5).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N5; §7)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N5; §7)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3135,12 +3241,14 @@
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
-2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.</t>
+2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N4).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N4)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N4)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3181,12 +3289,14 @@
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
-2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.</t>
+2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-R1; S22-R2; Story 18 S18-R7.2)</t>
+          <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R1; S22-R2; Story 18 S18-R7.2)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3231,12 +3341,14 @@
           <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
-4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.</t>
+4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1)</t>
+          <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3278,12 +3390,14 @@
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
-2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.</t>
+2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-N1; Story 6 S6-N2)</t>
+          <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-N1; Story 6 S6-N2)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3330,7 +3444,9 @@
 2. On first visit all seven metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
-5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.</t>
+5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3376,12 +3492,14 @@
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The toggle takes effect immediately — no confirm step.
-2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.</t>
+2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R4; S20-R7)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R4; S20-R7)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3421,12 +3539,14 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.</t>
+          <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R8).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R8)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R8)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3467,12 +3587,14 @@
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
-2. Showing the column again reveals the sort indicator on it.</t>
+2. Showing the column again reveals the sort indicator on it.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R9).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R9)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R9)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3514,12 +3636,14 @@
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
-2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.</t>
+2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R1; Story 20 S20-R5)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R1; Story 20 S20-R5)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3560,12 +3684,14 @@
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. All rows render collapsed and the scroll position resets.
-2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.</t>
+2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R2).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R2; §2 Out of Scope)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R2; §2 Out of Scope)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3607,12 +3733,14 @@
         <is>
           <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
-3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.</t>
+3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R3).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R3)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R3)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3653,7 +3781,9 @@
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
-2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.</t>
+2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3699,12 +3829,14 @@
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The report restores to the A→Z default order by rep display name.
-2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.</t>
+2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R5; Story 11 S11-R4)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R5; Story 11 S11-R4)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3746,7 +3878,9 @@
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
-2. No other entries appear in the menu.</t>
+2. No other entries appear in the menu.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3799,7 +3933,9 @@
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
 3. Rep rows appear in the report's currently-active order — the active column sort if one is set, otherwise the A→Z default.
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
-5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3850,7 +3986,9 @@
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
 3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added with the identifying columns ahead of Inv. Hrs, and a rep who spans more than one location reads "Multiple" (this file has no Status column for it to follow — confirm its exact position in the build).
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
-5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.</t>
+5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3902,7 +4040,9 @@
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
-6. There is NO grand-totals row across all reps at the end of the document.</t>
+6. There is NO grand-totals row across all reps at the end of the document.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3949,12 +4089,14 @@
         <is>
           <t>1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
-3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.</t>
+3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R7).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R7)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R7)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3998,7 +4140,9 @@
         <is>
           <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
-3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.</t>
+3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4046,12 +4190,14 @@
         <is>
           <t>1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
-3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.</t>
+3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R9; S14-R10)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R9; S14-R10)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4080,7 +4226,8 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).</t>
+          <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).
+2. This test reads what is inside a downloaded PDF. Open the file in any PDF viewer and use the viewer's own text search (Ctrl+F) to find the text named below — that is enough. There is nothing to install.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4094,12 +4241,14 @@
         <is>
           <t>1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
-3. Both PDF formats adapt the same way.</t>
+3. Both PDF formats adapt the same way.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R12; S14-R13)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4147,7 +4296,9 @@
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)</t>
+7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4197,7 +4348,9 @@
 2. With a single location in scope the headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".</t>
+5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4247,12 +4400,14 @@
 3. Margin % is a plain number to one decimal (for example, 45.2) with no % sign, and the cell is EMPTY where Margin % is undefined (Subtotal ≤ 0).
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
-6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R17).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4297,12 +4452,14 @@
           <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4332,7 +4489,8 @@
       <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
-2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.</t>
+2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.
+3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4345,12 +4503,14 @@
         <is>
           <t>1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
-3. A genuine failure downloads nothing — never a malformed file.</t>
+3. A genuine failure downloads nothing — never a malformed file.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4392,7 +4552,10 @@
         <is>
           <t>1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
-3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).</t>
+3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4441,12 +4604,14 @@
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
 3. The Expanded View PDF renders just the header strip with no per-rep blocks (it has no grand-totals row).
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
-5. No special "empty" treatment or message appears inside the files.</t>
+5. No special "empty" treatment or message appears inside the files.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E3).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E3)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E3)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4491,12 +4656,14 @@
           <t>1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R1; S15-R2)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R1; S15-R2)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4538,11 +4705,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as "sales-representative-assignments.csv (the short form "rep" is gone from the file name — confirm the exact final file name in the build)".
+          <t>1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.</t>
+5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4591,12 +4760,14 @@
         <is>
           <t>1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
-3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).</t>
+3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R5; S15-R7; S15-R10)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R5; S15-R7; S15-R10)</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4638,12 +4809,14 @@
         <is>
           <t>1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
-3. The value is always "Yes" or "No" (never "Deactivated" or another word).</t>
+3. The value is always "Yes" or "No" (never "Deactivated" or another word).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R6; Story 13 S13-R11)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R6; Story 13 S13-R11)</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4687,12 +4860,14 @@
           <t>1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Representative" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R8; S15-R9)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R8; S15-R9)</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4735,12 +4910,14 @@
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
-2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.</t>
+2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R11; S15-N2; §7)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R11; S15-N2; §7)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4786,7 +4963,9 @@
 2. The grand Totals indicator is NOT shown.
 3. The same message appears when no staff member has ever been credited — there is no separate "no reps configured" message; the report is contributor-driven.
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
-5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.</t>
+5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -4820,7 +4999,8 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).</t>
+          <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4835,12 +5015,14 @@
           <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
 3. The toolbar stays interactive so filters can be changed mid-load.
-4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.</t>
+4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R4).</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R4)</t>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R4)</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4869,7 +5051,8 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.</t>
+          <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4883,12 +5066,14 @@
         <is>
           <t>1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
-3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.</t>
+3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R5).</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R5; §7)</t>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R5; §7)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4931,12 +5116,14 @@
         <is>
           <t>1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
-3. At 1024px and above the desktop layout applies.</t>
+3. At 1024px and above the desktop layout applies.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R1; S17-R2; S17-R3)</t>
+          <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R1; S17-R2; S17-R3)</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4979,12 +5166,14 @@
         <is>
           <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
-3. The chevron expands/collapses the rep on touch.</t>
+3. The chevron expands/collapses the rep on touch.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile))</t>
+          <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile))</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -5013,7 +5202,8 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1. The report is open on a touch device or touch emulation (under 1024px).</t>
+          <t>1. The report is open on a touch device or touch emulation (under 1024px).
+2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5025,12 +5215,14 @@
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
-2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.</t>
+2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R6; S17-N1; Story 18 S18-R9)</t>
+          <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R6; S17-N1; Story 18 S18-R9)</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5064,23 +5256,28 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the toolbar's surface, padding, and how the title and the rightmost control line up with the table columns.
+          <t>1. Look at the toolbar strip, at the space between its controls and the edges of the strip, and at how the title and the rightmost control line up with the table columns.
 2. Look at the page background around the data area, the line between the toolbar and the column headers, and the table's side edges.
-3. Look at the header cells, the body cells, the pinned Subtotal cells, and the grand Totals indicator's surface.</t>
+3. Look at the header cells, the body cells, the pinned Subtotal cells, and the grand Totals indicator's surface.
+4. Open another report in the suite (for example Parts Velocity) side by side and compare.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a solid white background with padding 32px top / 24px bottom / 2rem left and right; the title's left edge aligns with the leftmost data column, and the rightmost toolbar control (the Location filter) aligns its right edge with the rightmost data column.
-2. The data area sits on the standard blue-grey page background with ZERO horizontal page padding — the toolbar and table run edge-to-edge against the side navigation.
+          <t>1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
+2. The data area sits on the standard blue-grey page background and runs edge-to-edge against the side navigation — there is no strip of empty space down either side.
 3. A thin horizontal separator line sits between the toolbar and the column headers.
 4. Column-header cells and all body cells render on white; the pinned Subtotal column matches the row background (not a contrasting strip); the grand Totals indicator renders on the white card surface with a thin top border.
-5. Row types are differentiated by font weight and color, not background color. These rules apply unconditionally whenever the report is rendered.</t>
+5. Row types are told apart by how heavy and what colour their text is, not by a different background colour.
+6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
+7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1)</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -5125,12 +5322,14 @@
           <t>1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
-4. PDFs always render in light-mode colors, even when downloaded from dark mode.</t>
+4. PDFs always render in light-mode colors, even when downloaded from dark mode.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R8).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R8)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -5159,7 +5358,8 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.</t>
+          <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5174,12 +5374,14 @@
 2. Column selector = "Show or hide columns".
 3. Per-row chevron = "Expand {rep name}" when collapsed / "Collapse {rep name}" when expanded.
 4. Header chevron = "Expand all reps" / "Collapse all reps".
-5. Dialog X = "Close".</t>
+5. Dialog X = "Close".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R9).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R9)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R9)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5208,7 +5410,8 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.</t>
+          <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5222,12 +5425,14 @@
         <is>
           <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
-3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.</t>
+3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R10).</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R10)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R10)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -5269,7 +5474,9 @@
         <is>
           <t>1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
-3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)</t>
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5320,12 +5527,14 @@
 2. The left panel includes the same "Sales Representative" selector on the Part Sale WO.
 3. The selector is NOT present on the imported Work Order.
 4. The selector is NOT present in History mode.
-5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R1; S19-N1)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R1; S19-N1)</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5369,12 +5578,14 @@
           <t>1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
 3. The selector carries the accessible name "Sales Representative".
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5417,12 +5628,14 @@
         <is>
           <t>1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
-3. A new Part Sale WO also opens with the field unassigned.</t>
+3. A new Part Sale WO also opens with the field unassigned.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R3; S19-R4)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R3; S19-R4)</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5465,12 +5678,14 @@
           <t>1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.</t>
+4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R5).</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R5)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R5)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5514,12 +5729,14 @@
           <t>1. Invoice (a) is credited to the WO's Sales Representative.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
-4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.</t>
+4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3)</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5564,7 +5781,9 @@
           <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5599,7 +5818,8 @@
       <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows, one with a large invoice count if seedable.
-2. The browser's network panel is open.</t>
+2. The browser's network panel is open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5613,12 +5833,14 @@
         <is>
           <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
-3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.</t>
+3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R2).</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R2)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R2)</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5647,7 +5869,8 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with several rep rows; the network panel is open.</t>
+          <t>1. You are on the report with several rep rows; the network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5660,12 +5883,14 @@
         <is>
           <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
-3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.</t>
+3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5).</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R5)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5694,7 +5919,8 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.</t>
+          <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5707,12 +5933,14 @@
         <is>
           <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
-3. The on-screen grand Totals match the export's aggregate for the same filter set.</t>
+3. The on-screen grand Totals match the export's aggregate for the same filter set.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5741,7 +5969,8 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.</t>
+          <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5755,12 +5984,14 @@
         <is>
           <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
-3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).</t>
+3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R2a; S14-N2; S14-E3)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2a; S14-N2; S14-E3)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5790,7 +6021,8 @@
       <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. A filter set producing more than 10,000 invoice detail rows exists or can be seeded — otherwise mark Blocked-Env with the reason.
-2. The network panel is open.</t>
+2. The network panel is open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5803,12 +6035,15 @@
         <is>
           <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
-3. A filter set just below the cap still generates a complete (possibly very large) PDF.</t>
+3. A filter set just below the cap still generates a complete (possibly very large) PDF.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2).</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E2)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2)</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5838,7 +6073,8 @@
       <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-representative toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
-2. The network panel is open.</t>
+2. The network panel is open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5852,12 +6088,14 @@
         <is>
           <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
-3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.</t>
+3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R4)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R4)</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -2987,7 +2987,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon.
+          <t>1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
 3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
 4. Clicking outside the dialog does NOT close it.
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. An error toast is shown: "Ooooops! An error occured" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
+          <t>1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -770,6 +770,8 @@
 2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option (removed by the 2026-07-16 spec round).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -1274,6 +1276,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1336,6 +1340,8 @@
 7. With a single location in scope the Location column is hidden.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
@@ -3988,6 +3994,8 @@
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
@@ -4042,6 +4050,8 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
@@ -4298,6 +4308,8 @@
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -4350,6 +4362,8 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -5529,6 +5543,8 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
@@ -5783,6 +5799,8 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -770,8 +770,6 @@
 2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option (removed by the 2026-07-16 spec round).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -1276,8 +1274,6 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1340,8 +1336,6 @@
 7. With a single location in scope the Location column is hidden.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
@@ -3994,8 +3988,6 @@
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
@@ -4050,8 +4042,6 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
@@ -4308,8 +4298,6 @@
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -4362,8 +4350,6 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -5543,8 +5529,6 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
@@ -5799,8 +5783,6 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -529,7 +529,7 @@
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
           <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
 2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
         <is>
           <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
         <is>
           <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
           <t>1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
           <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
           <t>1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1393,7 +1393,7 @@
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
           <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1745,7 +1745,7 @@
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
           <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
           <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
           <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 half).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
           <t>1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2999,7 +2999,7 @@
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
           <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
           <t>1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
         <is>
           <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
           <t>1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
           <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
           <t>1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4052,7 +4052,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
 3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4364,7 +4364,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4415,8 +4415,10 @@
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R17).</t>
+On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4468,7 +4470,7 @@
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4519,7 +4521,7 @@
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4569,7 +4571,7 @@
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4620,7 +4622,7 @@
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4672,7 +4674,7 @@
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4725,7 +4727,7 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4776,7 +4778,7 @@
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4825,7 +4827,7 @@
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4876,7 +4878,7 @@
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4926,7 +4928,7 @@
           <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4979,7 +4981,7 @@
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5031,7 +5033,7 @@
 3. The toolbar stays interactive so filters can be changed mid-load.
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5082,7 +5084,7 @@
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5132,7 +5134,7 @@
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5182,7 +5184,7 @@
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5231,7 +5233,7 @@
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5286,7 +5288,7 @@
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5338,7 +5340,7 @@
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5390,7 +5392,7 @@
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5441,7 +5443,7 @@
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5490,7 +5492,7 @@
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5545,7 +5547,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5596,7 +5598,7 @@
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5646,7 +5648,7 @@
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5696,7 +5698,7 @@
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5747,7 +5749,7 @@
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5801,7 +5803,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5853,7 +5855,7 @@
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5903,7 +5905,7 @@
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5953,7 +5955,7 @@
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6004,7 +6006,7 @@
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6056,7 +6058,7 @@
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6108,7 +6110,7 @@
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -767,12 +767,10 @@
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. A date range picker is visible in the report toolbar.
-2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
-3. There is no "All Time" option (removed by the 2026-07-16 spec round).
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
+2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
+3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1276,9 +1274,7 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1339,10 +1335,12 @@
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
 7. With a single location in scope the Location column is hidden.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
+Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
+Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+---
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3990,13 +3988,11 @@
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
-3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added with the identifying columns ahead of Inv. Hrs, and a rep who spans more than one location reads "Multiple" (this file has no Status column for it to follow — confirm its exact position in the build).
+3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, and it has not yet been confirmed on a build.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4050,9 +4046,7 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4150,9 +4144,10 @@
         <is>
           <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
-3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11).</t>
+3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The PDF still generates normally either way.
+---
+Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4301,16 +4296,14 @@
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
-2. With a single location in scope the headers, in order, are exactly: Sales Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal. On this build only nine of them arrive - Representative, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal - because # Invoices, # Customers, Hrs Worked and Hrs Invoiced are missing by mistake. Record what you see; the four missing columns are with the developers.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
-6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
+7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4357,14 +4350,12 @@
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
-2. With a single location in scope the headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S14-R16, S14-R20) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -523,13 +523,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
+          <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
 2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
 3. Selecting the entry opens the report in the main content area.
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -574,10 +576,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
+          <t xml:space="preserve">1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
 2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -622,9 +626,11 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).</t>
+          <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -671,11 +677,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
+          <t xml:space="preserve">1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -719,9 +727,11 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).</t>
+          <t xml:space="preserve">1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -766,11 +776,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. A date range picker is visible in the report toolbar.
+          <t xml:space="preserve">1. A date range picker is visible in the report toolbar.
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -815,10 +827,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. A custom range within the cap applies normally via the date-picker dialog.
+          <t xml:space="preserve">1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -864,11 +878,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
+          <t xml:space="preserve">1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -916,13 +932,15 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown offers exactly three options: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" as the default on first load.
+          <t xml:space="preserve">1. The dropdown offers exactly three options: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" as the default on first load.
 2. "Parts only" includes only invoices whose number starts with P.
 3. "Service only" includes only invoices whose number starts with S.
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -968,12 +986,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. An "Invoice Status" dropdown is visible in the toolbar.
+          <t xml:space="preserve">1. An "Invoice Status" dropdown is visible in the toolbar.
 2. It offers exactly four options: "All Statuses," "Unpaid," "Partially Paid," "Paid."
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1020,12 +1040,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
+          <t xml:space="preserve">1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
 2. "Partially Paid" includes the partially-paid AND the prepaid-with-a-balance-owed invoices.
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1072,12 +1094,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
+          <t xml:space="preserve">1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
 2. A rep appears only if at least one invoice matches all active filters.
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1121,10 +1145,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
+          <t xml:space="preserve">1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1169,10 +1195,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. The location filter is the rightmost control in the toolbar.
+          <t xml:space="preserve">1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1220,13 +1248,14 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
+          <t xml:space="preserve">1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
 3. "All Locations" means all locations the user can access — location Z's data is never included.
-4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1271,10 +1300,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1327,7 +1358,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
 2. A rep summary row whose invoices are all at one location shows that location's name.
 3. A rep summary row whose invoices span more than one location shows "Multiple".
 4. An invoice detail row shows that invoice's own exact location — never "Multiple".
@@ -1335,12 +1366,14 @@
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
 7. With a single location in scope the Location column is hidden.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
-Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20) differs, his decision is the authority.</t>
+The Location column is not in the column-selection dropdown — that dropdown holds the seven metric columns only — and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1386,12 +1419,14 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. Rep A occupies exactly one summary row.
+          <t xml:space="preserve">1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1438,13 +1473,15 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
+          <t xml:space="preserve">1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1491,12 +1528,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
+          <t xml:space="preserve">1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1541,11 +1580,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
+          <t xml:space="preserve">1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1591,11 +1632,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
+          <t xml:space="preserve">1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1640,10 +1683,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
+          <t xml:space="preserve">1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1689,11 +1734,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. Expanded state is preserved across filter and sort changes within the same session.
+          <t xml:space="preserve">1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1738,12 +1785,14 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. Detail rows order by invoice date descending (newest first).
+          <t xml:space="preserve">1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1790,12 +1839,14 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
+          <t xml:space="preserve">1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1840,11 +1891,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
+          <t xml:space="preserve">1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1889,10 +1942,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
+          <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1940,12 +1995,14 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
+          <t xml:space="preserve">1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1990,10 +2047,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
+          <t xml:space="preserve">1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2039,11 +2098,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
+          <t xml:space="preserve">1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2088,12 +2149,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+          <t xml:space="preserve">1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2138,10 +2201,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
+          <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2185,11 +2250,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
+          <t xml:space="preserve">1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2235,11 +2302,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
+          <t xml:space="preserve">1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2287,13 +2356,15 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. Subtotal is the rightmost column on every row type.
+          <t xml:space="preserve">1. Subtotal is the rightmost column on every row type.
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
 3. Subtotal values are bold across the header, every summary row, every detail row, and the grand Totals indicator.
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2340,13 +2411,15 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
+          <t xml:space="preserve">1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
 3. The grand totals cover the FULL filtered result set — every matching non-reversed invoice across every rep, independent of which reps are expanded or loaded.
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2392,12 +2465,14 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
+          <t xml:space="preserve">1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2442,11 +2517,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. Each financial column responds to a header click and reorders the rep rows.
+          <t xml:space="preserve">1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2490,10 +2567,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. Rows render in A→Z order by display name, case-insensitive.
+          <t xml:space="preserve">1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2540,12 +2619,14 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
+          <t xml:space="preserve">1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2590,11 +2671,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. Only the rep summary rows reorder.
+          <t xml:space="preserve">1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2639,10 +2722,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
+          <t xml:space="preserve">1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2688,11 +2773,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. Each invoice number is a clickable link.
+          <t xml:space="preserve">1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2738,11 +2825,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
+          <t xml:space="preserve">1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2788,12 +2877,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
+          <t xml:space="preserve">1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2838,10 +2929,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. The tab navigates to the application's standard not-found/access-denied state.
+          <t xml:space="preserve">1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2887,11 +2980,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
+          <t xml:space="preserve">1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2938,12 +3033,14 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
+          <t xml:space="preserve">1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2991,13 +3088,15 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
+          <t xml:space="preserve">1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
 3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3042,12 +3141,14 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
+          <t xml:space="preserve">1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3093,11 +3194,13 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. The sales-representative toggle state is unchanged by the deactivation flow.
+          <t xml:space="preserve">1. The sales-representative toggle state is unchanged by the deactivation flow.
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3143,12 +3246,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
+          <t xml:space="preserve">1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3194,11 +3299,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
+          <t xml:space="preserve">1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3244,10 +3351,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
+          <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3292,10 +3401,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
+          <t xml:space="preserve">1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3342,12 +3453,14 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
+          <t xml:space="preserve">1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3393,10 +3506,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
+          <t xml:space="preserve">1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3444,13 +3559,15 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
+          <t xml:space="preserve">1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3495,10 +3612,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. The toggle takes effect immediately — no confirm step.
+          <t xml:space="preserve">1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3543,9 +3662,11 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).</t>
+          <t xml:space="preserve">1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3590,10 +3711,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
+          <t xml:space="preserve">1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3639,10 +3762,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
+          <t xml:space="preserve">1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3687,10 +3812,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. All rows render collapsed and the scroll position resets.
+          <t xml:space="preserve">1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3735,11 +3862,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
+          <t xml:space="preserve">1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3784,10 +3913,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
+          <t xml:space="preserve">1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3832,10 +3963,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The report restores to the A→Z default order by rep display name.
+          <t xml:space="preserve">1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3881,10 +4014,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
+          <t xml:space="preserve">1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3933,13 +4068,15 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
+          <t xml:space="preserve">1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
 3. Rep rows appear in the report's currently-active order — the active column sort if one is set, otherwise the A→Z default.
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
-5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
+5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3986,13 +4123,15 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
+          <t xml:space="preserve">1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
 3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, and it has not yet been confirmed on a build.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, and it has not yet been confirmed on a build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4039,14 +4178,16 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
+          <t xml:space="preserve">1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, only when more than one location is in scope, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4091,11 +4232,13 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1. On screen, both invoice numbers show in full — never truncated.
+          <t xml:space="preserve">1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4142,12 +4285,15 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
+          <t xml:space="preserve">1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
 3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The PDF still generates normally either way.
 ---
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.</t>
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4193,11 +4339,13 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
+          <t xml:space="preserve">1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4244,11 +4392,13 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
+          <t xml:space="preserve">1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4295,7 +4445,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
+          <t xml:space="preserve">1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal. On this build only nine of them arrive - Representative, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal - because # Invoices, # Customers, Hrs Worked and Hrs Invoiced are missing by mistake. Record what you see; the four missing columns are with the developers.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
@@ -4303,7 +4453,9 @@
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4349,13 +4501,15 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
+          <t xml:space="preserve">1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S14-R16, S14-R20) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S14-R16, S14-R20) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4400,7 +4554,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
+          <t xml:space="preserve">1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
 3. Margin % is a plain number to one decimal (for example, 45.2) with no % sign, and the cell is EMPTY where Margin % is undefined (Subtotal ≤ 0).
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
@@ -4409,7 +4563,9 @@
 On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).
+AUTOMATION: READY - EXPECT FAIL (SV-8823)
+</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4456,12 +4612,14 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
+          <t xml:space="preserve">1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4508,11 +4666,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
+          <t xml:space="preserve">1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4557,12 +4717,14 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. No file is produced — the server declines rather than generating a truncated file.
+          <t xml:space="preserve">1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4607,13 +4769,15 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. All four downloads produce a FILE, not an error.
+          <t xml:space="preserve">1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
 3. The Expanded View PDF renders just the header strip with no per-rep blocks (it has no grand-totals row).
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4660,12 +4824,14 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
+          <t xml:space="preserve">1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4712,13 +4878,15 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
+          <t xml:space="preserve">1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4765,11 +4933,13 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
+          <t xml:space="preserve">1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4814,11 +4984,13 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
+          <t xml:space="preserve">1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4864,12 +5036,14 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. The customer still produces a row — the export never silently drops it.
+          <t xml:space="preserve">1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Representative" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4916,10 +5090,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
+          <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4966,13 +5142,15 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
+          <t xml:space="preserve">1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
 3. The same message appears when no staff member has ever been credited — there is no separate "no reps configured" message; the report is contributor-driven.
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5019,12 +5197,14 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
+          <t xml:space="preserve">1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
 3. The toolbar stays interactive so filters can be changed mid-load.
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5071,11 +5251,13 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
+          <t xml:space="preserve">1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5121,11 +5303,13 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. Every toolbar control is visible and operable on touch.
+          <t xml:space="preserve">1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5171,11 +5355,13 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
+          <t xml:space="preserve">1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5221,10 +5407,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
+          <t xml:space="preserve">1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5271,7 +5459,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
+          <t xml:space="preserve">1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
 2. The data area sits on the standard blue-grey page background and runs edge-to-edge against the side navigation — there is no strip of empty space down either side.
 3. A thin horizontal separator line sits between the toolbar and the column headers.
 4. Column-header cells and all body cells render on white; the pinned Subtotal column matches the row background (not a contrasting strip); the grand Totals indicator renders on the white card surface with a thin top border.
@@ -5279,7 +5467,9 @@
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5326,12 +5516,14 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
+          <t xml:space="preserve">1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5377,13 +5569,15 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1. ⋯ exports = "Report actions".
+          <t xml:space="preserve">1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
 3. Per-row chevron = "Expand {rep name}" when collapsed / "Collapse {rep name}" when expanded.
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5430,11 +5624,13 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
+          <t xml:space="preserve">1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5479,11 +5675,13 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
+          <t xml:space="preserve">1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5530,15 +5728,15 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1. The left panel includes a "Sales Representative" selector on the standard Work Order.
+          <t xml:space="preserve">1. The left panel includes a "Sales Representative" selector on the standard Work Order.
 2. The left panel includes the same "Sales Representative" selector on the Part Sale WO.
 3. The selector is NOT present on the imported Work Order.
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5584,12 +5782,14 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1. The toggle-ON staff member is offered as a selectable rep.
+          <t xml:space="preserve">1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5635,11 +5835,13 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
+          <t xml:space="preserve">1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5684,12 +5886,14 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
+          <t xml:space="preserve">1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5735,12 +5939,14 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1. Invoice (a) is credited to the WO's Sales Representative.
+          <t xml:space="preserve">1. Invoice (a) is credited to the WO's Sales Representative.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5787,14 +5993,14 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
+          <t xml:space="preserve">1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5842,11 +6048,13 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
+          <t xml:space="preserve">1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5892,11 +6100,13 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
+          <t xml:space="preserve">1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5942,11 +6152,13 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
+          <t xml:space="preserve">1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5993,11 +6205,13 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
+          <t xml:space="preserve">1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6044,12 +6258,14 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
+          <t xml:space="preserve">1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6097,11 +6313,13 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
+          <t xml:space="preserve">1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -529,7 +529,8 @@
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -579,7 +580,8 @@
           <t xml:space="preserve">1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
 2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -628,7 +630,8 @@
         <is>
           <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -681,7 +684,8 @@
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-N1, S14-N3, S15-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -729,7 +733,8 @@
         <is>
           <t xml:space="preserve">1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -780,7 +785,8 @@
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 16 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -830,7 +836,8 @@
           <t xml:space="preserve">1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S2-R3, S2-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -882,7 +889,8 @@
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S2-R5, S2-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -938,7 +946,8 @@
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -991,7 +1000,8 @@
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R1, S4-R2, S4-R3, S4-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1045,7 +1055,8 @@
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1099,7 +1110,8 @@
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1148,7 +1160,8 @@
           <t xml:space="preserve">1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1198,7 +1211,8 @@
           <t xml:space="preserve">1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R1, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1253,7 +1267,8 @@
 3. "All Locations" means all locations the user can access — location Z's data is never included.
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1303,7 +1318,8 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1364,15 +1380,13 @@
 4. An invoice detail row shows that invoice's own exact location — never "Multiple".
 5. The Unassigned summary row follows the same rule as any rep summary row.
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
-7. With a single location in scope the Location column is hidden.
+7. With only one location involved the Location column is not shown.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is not in the column-selection dropdown — that dropdown holds the seven metric columns only — and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements are that the column-selection dropdown holds the seven metric columns only, and that Location is one of the columns you can switch on and off there. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R7, S21-R8, S18-R13, S14-R20). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: its summary says it can be toggled there, while the requirement that governs the column says it appears only when the view spans more than one location and the dropdown holds the seven metric columns only. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -1424,7 +1438,8 @@
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R1, S5-R4, S5-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1479,7 +1494,8 @@
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1533,7 +1549,8 @@
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1584,7 +1601,8 @@
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R1, S6-R2, S6-R3, S6-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1636,7 +1654,8 @@
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R5, S6-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1686,7 +1705,8 @@
           <t xml:space="preserve">1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1738,7 +1758,8 @@
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R8, S6-N1, S23-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1790,7 +1811,8 @@
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R9, S11-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1844,7 +1866,8 @@
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1895,7 +1918,8 @@
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S8-R3, S18-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1945,7 +1969,8 @@
           <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R1, S9-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2000,7 +2025,8 @@
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2050,7 +2076,8 @@
           <t xml:space="preserve">1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2102,7 +2129,8 @@
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2154,7 +2182,8 @@
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R2, S21-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2204,7 +2233,8 @@
           <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (§3 Key Decisions accounting parentheses).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2254,7 +2284,8 @@
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (§3 half).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2306,7 +2337,8 @@
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2362,7 +2394,8 @@
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2417,7 +2450,8 @@
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5, S10-N1, S16-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2470,7 +2504,8 @@
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5, S17-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2521,7 +2556,8 @@
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R1, S11-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2570,7 +2606,8 @@
           <t xml:space="preserve">1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2624,7 +2661,8 @@
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R5, S23-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2675,7 +2713,8 @@
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R2, S22-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2725,7 +2764,8 @@
           <t xml:space="preserve">1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2777,7 +2817,8 @@
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R1, S12-R2, S12-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2829,7 +2870,8 @@
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R3a, S23-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2882,7 +2924,8 @@
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R4, S12-R5, S12-R6, S12-N3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2932,7 +2975,8 @@
           <t xml:space="preserve">1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-N1, S12-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2984,7 +3028,8 @@
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R1, S13-R3, S13-R4, S13-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3038,7 +3083,8 @@
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R6, S13-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3094,7 +3140,8 @@
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3146,7 +3193,8 @@
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R9, S13-R10, S13-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3198,7 +3246,8 @@
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R11, S15-R6, S5-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3251,7 +3300,8 @@
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R2, S13-N2, S13-N3, S13-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3303,7 +3353,8 @@
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3354,7 +3405,8 @@
           <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3404,7 +3456,8 @@
           <t xml:space="preserve">1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-R1, S22-R2, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3458,7 +3511,8 @@
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3509,7 +3563,8 @@
           <t xml:space="preserve">1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-N1, S6-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3565,7 +3620,8 @@
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3615,7 +3671,8 @@
           <t xml:space="preserve">1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R4, S20-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3664,7 +3721,8 @@
         <is>
           <t xml:space="preserve">1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3714,7 +3772,8 @@
           <t xml:space="preserve">1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3765,7 +3824,8 @@
           <t xml:space="preserve">1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R1, S20-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3815,7 +3875,8 @@
           <t xml:space="preserve">1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3866,7 +3927,8 @@
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3916,7 +3978,8 @@
           <t xml:space="preserve">1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3966,7 +4029,8 @@
           <t xml:space="preserve">1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R5, S11-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4017,7 +4081,8 @@
           <t xml:space="preserve">1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R1, S17-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4074,7 +4139,8 @@
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4129,7 +4195,8 @@
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, and it has not yet been confirmed on a build.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Representative report specification version 16 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, so his answers are the only basis for it.
+This has not yet been checked against a build.
 AUTOMATION: READY
 </t>
         </is>
@@ -4185,7 +4252,8 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4236,7 +4304,8 @@
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4291,7 +4360,8 @@
 ---
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 16 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -4343,7 +4413,8 @@
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R9, S14-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4396,7 +4467,8 @@
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R12, S14-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4453,7 +4525,8 @@
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 16 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -4507,7 +4580,8 @@
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S14-R16, S14-R20) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 16 (S14-R16, S14-R20) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4563,7 +4637,8 @@
 On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R17).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8823)
 </t>
         </is>
@@ -4617,7 +4692,8 @@
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R19, S22-R2, S22-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4670,7 +4746,8 @@
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-N1, S14-N2, S14-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4722,7 +4799,8 @@
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E2); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -4775,7 +4853,8 @@
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4829,7 +4908,8 @@
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R1, S15-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4884,7 +4964,8 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4937,7 +5018,8 @@
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R5, S15-R7, S15-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4988,7 +5070,8 @@
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R6, S13-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5041,7 +5124,8 @@
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R8, S15-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5093,7 +5177,8 @@
           <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R11, S15-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5148,7 +5233,8 @@
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5202,7 +5288,8 @@
 3. The toolbar stays interactive so filters can be changed mid-load.
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5255,7 +5342,8 @@
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5307,7 +5395,8 @@
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R1, S17-R2, S17-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5359,7 +5448,8 @@
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R4, S17-R5, S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5410,7 +5500,8 @@
           <t xml:space="preserve">1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R6, S17-N1, S18-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5467,7 +5558,8 @@
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5521,7 +5613,8 @@
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5575,7 +5668,8 @@
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5628,7 +5722,8 @@
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5679,7 +5774,8 @@
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R11, S18-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5734,7 +5830,8 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R1, S19-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
@@ -5787,7 +5884,8 @@
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R2, S19-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -5839,7 +5937,8 @@
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R3, S19-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5891,7 +5990,8 @@
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5944,7 +6044,8 @@
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R6, S19-N2, S22-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5998,7 +6099,8 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
@@ -6052,7 +6154,8 @@
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6104,7 +6207,8 @@
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6156,7 +6260,8 @@
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6209,7 +6314,8 @@
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R2a, S14-N2, S14-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -6263,7 +6369,8 @@
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -6317,7 +6424,8 @@
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R1, S13-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -529,7 +529,7 @@
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -580,7 +580,7 @@
           <t xml:space="preserve">1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
 2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -630,7 +630,7 @@
         <is>
           <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -684,7 +684,7 @@
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-N1, S14-N3, S15-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-N1, S14-N3, S15-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -733,7 +733,7 @@
         <is>
           <t xml:space="preserve">1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -785,7 +785,7 @@
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 16 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 17 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -836,7 +836,7 @@
           <t xml:space="preserve">1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S2-R3, S2-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S2-R3, S2-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -889,7 +889,7 @@
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S2-R5, S2-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S2-R5, S2-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -946,7 +946,7 @@
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1000,7 +1000,7 @@
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R1, S4-R2, S4-R3, S4-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R1, S4-R2, S4-R3, S4-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1055,7 +1055,7 @@
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1110,7 +1110,7 @@
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1160,7 +1160,7 @@
           <t xml:space="preserve">1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1211,7 +1211,7 @@
           <t xml:space="preserve">1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R1, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-R1, S18-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1267,7 +1267,7 @@
 3. "All Locations" means all locations the user can access — location Z's data is never included.
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1318,7 +1318,7 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1384,7 +1384,7 @@
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
 Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements are that the column-selection dropdown holds the seven metric columns only, and that Location is one of the columns you can switch on and off there. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R7, S21-R8, S18-R13, S14-R20). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: its summary says it can be toggled there, while the requirement that governs the column says it appears only when the view spans more than one location and the dropdown holds the seven metric columns only. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-R7, S21-R8, S18-R13, S14-R20). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: its summary says it can be toggled there, while the requirement that governs the column says it appears only when the view spans more than one location and the dropdown holds the seven metric columns only. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
@@ -1438,7 +1438,7 @@
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R1, S5-R4, S5-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R1, S5-R4, S5-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1494,7 +1494,7 @@
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1549,7 +1549,7 @@
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1601,7 +1601,7 @@
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R1, S6-R2, S6-R3, S6-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R1, S6-R2, S6-R3, S6-E1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1654,7 +1654,7 @@
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R5, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R5, S6-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1705,7 +1705,7 @@
           <t xml:space="preserve">1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1758,7 +1758,7 @@
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R8, S6-N1, S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R8, S6-N1, S23-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1811,7 +1811,7 @@
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R9, S11-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R9, S11-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1866,7 +1866,7 @@
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1918,7 +1918,7 @@
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S8-R3, S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S8-R3, S18-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1969,7 +1969,7 @@
           <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R1, S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-R1, S9-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2025,7 +2025,7 @@
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2076,7 +2076,7 @@
           <t xml:space="preserve">1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2129,7 +2129,7 @@
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2182,7 +2182,7 @@
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R2, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R2, S21-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2233,7 +2233,7 @@
           <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (§3 Key Decisions accounting parentheses).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (§3 Key Decisions accounting parentheses).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2284,7 +2284,7 @@
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (§3 half).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (§3 half).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2337,7 +2337,7 @@
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2394,7 +2394,7 @@
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2450,7 +2450,7 @@
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5, S10-N1, S16-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5, S10-N1, S16-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2504,7 +2504,7 @@
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5, S17-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5, S17-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2556,7 +2556,7 @@
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R1, S11-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R1, S11-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2606,7 +2606,7 @@
           <t xml:space="preserve">1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2661,7 +2661,7 @@
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R5, S23-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R5, S23-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2713,7 +2713,7 @@
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R2, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R2, S22-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2764,7 +2764,7 @@
           <t xml:space="preserve">1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2817,7 +2817,7 @@
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R1, S12-R2, S12-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-R1, S12-R2, S12-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2870,7 +2870,7 @@
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R3a, S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-R3a, S23-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2924,7 +2924,7 @@
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R4, S12-R5, S12-R6, S12-N3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-R4, S12-R5, S12-R6, S12-N3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2975,7 +2975,7 @@
           <t xml:space="preserve">1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-N1, S12-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-N1, S12-N2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3028,7 +3028,7 @@
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R1, S13-R3, S13-R4, S13-R12).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R1, S13-R3, S13-R4, S13-R12).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3083,7 +3083,7 @@
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R6, S13-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R6, S13-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3140,7 +3140,7 @@
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3193,7 +3193,7 @@
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R9, S13-R10, S13-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R9, S13-R10, S13-E1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3246,7 +3246,7 @@
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R11, S15-R6, S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R11, S15-R6, S5-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3300,7 +3300,7 @@
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R2, S13-N2, S13-N3, S13-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R2, S13-N2, S13-N3, S13-E3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3353,7 +3353,7 @@
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-N5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3405,7 +3405,7 @@
           <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-N4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3456,7 +3456,7 @@
           <t xml:space="preserve">1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-R1, S22-R2, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S22-R1, S22-R2, S18-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3511,7 +3511,7 @@
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3563,7 +3563,7 @@
           <t xml:space="preserve">1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-N1, S6-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S22-N1, S6-N2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3620,7 +3620,7 @@
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3671,7 +3671,7 @@
           <t xml:space="preserve">1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R4, S20-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R4, S20-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3721,7 +3721,7 @@
         <is>
           <t xml:space="preserve">1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3772,7 +3772,7 @@
           <t xml:space="preserve">1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3824,7 +3824,7 @@
           <t xml:space="preserve">1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R1, S20-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R1, S20-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3875,7 +3875,7 @@
           <t xml:space="preserve">1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3927,7 +3927,7 @@
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3978,7 +3978,7 @@
           <t xml:space="preserve">1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4029,7 +4029,7 @@
           <t xml:space="preserve">1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R5, S11-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R5, S11-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4081,7 +4081,7 @@
           <t xml:space="preserve">1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R1, S17-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R1, S17-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4139,7 +4139,7 @@
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4195,7 +4195,7 @@
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Representative report specification version 16 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, so his answers are the only basis for it.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Representative report specification version 17 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, so his answers are the only basis for it.
 This has not yet been checked against a build.
 AUTOMATION: READY
 </t>
@@ -4252,7 +4252,7 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4304,7 +4304,7 @@
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4360,7 +4360,7 @@
 ---
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 16 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 17 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
@@ -4413,7 +4413,7 @@
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R9, S14-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R9, S14-R10).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4467,7 +4467,7 @@
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R12, S14-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R12, S14-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4525,7 +4525,7 @@
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 16 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 17 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
@@ -4580,7 +4580,7 @@
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 16 (S14-R16, S14-R20) says something different, his decision is the later word and is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 17 (S14-R16, S14-R20) says something different, his decision is the later word and is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4637,7 +4637,7 @@
 On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R17).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R17).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8823)
 </t>
@@ -4692,7 +4692,7 @@
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R19, S22-R2, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R19, S22-R2, S22-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4746,7 +4746,7 @@
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-N1, S14-N2, S14-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-N1, S14-N2, S14-E1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4799,7 +4799,7 @@
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E2); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-E2); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
@@ -4853,7 +4853,7 @@
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-E3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4908,7 +4908,7 @@
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R1, S15-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R1, S15-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4964,7 +4964,7 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5018,7 +5018,7 @@
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R5, S15-R7, S15-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R5, S15-R7, S15-R10).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5070,7 +5070,7 @@
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R6, S13-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R6, S13-R11).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5124,7 +5124,7 @@
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R8, S15-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R8, S15-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5177,7 +5177,7 @@
           <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R11, S15-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R11, S15-N2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5233,7 +5233,7 @@
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5288,7 +5288,7 @@
 3. The toolbar stays interactive so filters can be changed mid-load.
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S16-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5342,7 +5342,7 @@
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S16-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5395,7 +5395,7 @@
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R1, S17-R2, S17-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S17-R1, S17-R2, S17-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5448,7 +5448,7 @@
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R4, S17-R5, S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S17-R4, S17-R5, S10-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5500,7 +5500,7 @@
           <t xml:space="preserve">1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R6, S17-N1, S18-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S17-R6, S17-N1, S18-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5558,7 +5558,7 @@
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5613,7 +5613,7 @@
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5668,7 +5668,7 @@
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5722,7 +5722,7 @@
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R10).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5774,7 +5774,7 @@
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R11, S18-R12).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R11, S18-R12).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5830,7 +5830,7 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R1, S19-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R1, S19-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
@@ -5884,7 +5884,7 @@
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R2, S19-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R2, S19-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
@@ -5937,7 +5937,7 @@
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R3, S19-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R3, S19-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5990,7 +5990,7 @@
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6044,7 +6044,7 @@
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R6, S19-N2, S22-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R6, S19-N2, S22-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6099,7 +6099,7 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
@@ -6154,7 +6154,7 @@
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6207,7 +6207,7 @@
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6260,7 +6260,7 @@
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6314,7 +6314,7 @@
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R2a, S14-N2, S14-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R2a, S14-N2, S14-E3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
@@ -6369,7 +6369,7 @@
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-E2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
@@ -6424,7 +6424,7 @@
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R1, S13-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R1, S13-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2992,37 +2992,96 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>Invoice # and customer name when you cannot open what they point at</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Links &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You need TWO sign-ins: one person who can open work orders, part sales and customers, and one person who can see reports but CANNOT open them. Ask whoever manages permissions to set the second one up, or set it up yourself in administration and put it back as you found it afterwards.
+3. On the Sales By Representative report you have expanded a representative so you can see the invoice rows underneath, each showing an Invoice # and a customer name.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as the person who CAN open them, click an Invoice # and note where it goes; come back and click a customer name and note where that goes.
+2. Sign in as the person who CANNOT open them and open the Sales By Representative report again.
+3. Expand the same representative and look at the Invoice # values, then try clicking one.
+4. Now CLICK a customer name — do not judge this one by looking at it.
+5. Write down exactly what happened in each case.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. For the person who CAN open them, the Invoice # takes you to the work order or the part sale, and the customer name takes you to the customer's record, both in the same browser tab.
+2. For the person who CANNOT open them, neither one takes them anywhere: the work order, the part sale and the customer record all stay out of reach.
+3. Nothing goes wrong on the way: no page saying you are not allowed in, no blank page, no error message. The report keeps showing all its rows and figures.
+4. Note for the tester: you have to CLICK the customer name rather than look at it. Even for someone who IS allowed to open it, the customer name is deliberately styled to look like ordinary text — same colour, no underline — so a name you can use and a name you cannot use look exactly the same. Clicking is the only way to tell.
+5. Note for the tester: what these two values should LOOK like for the second person is not fully settled, so do not fail the test on appearance. The report's description says they are shown as plain text when the person cannot open the target, but the numbered requirements underneath it still say the Invoice # and the customer name are always links. The product owner has been asked. Write down what you saw and carry on; only report a failure if that person actually reaches the work order, the part sale or the customer record.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17, whose §2 describes each expanded row's invoice number as a clickable link to the underlying work order or parts sale rendered as a link only when the user has permission to open that target and otherwise plain text, and the customer name as non-interactive plain text when the user cannot open the customer. That report's numbered requirements S12-R1 and S12-R3 were not updated to match and still describe both as clickable links, so this case asserts only what both readings require — that the person cannot reach the target — and the product owner has been asked to settle the rest.
+This has not yet been checked against a build.
+AUTOMATION: HOLD - waiting on one answer from the product owner about what these two values should look like, and it needs a second sign-in that cannot open work orders, part sales or customers
+</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>SV-8629 (SBR spec v17 2026-08-05 §2 expanded rows — a link is rendered only with permission to open the target; note S12-R1 and S12-R3 still read as though the links are always there)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Deactivate dialog: counted pluralized headline, reassurance, focus trap</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST rep "A" is active, toggle on, and assigned as sales representative to exactly 1 customer; ZZAUTOTEST rep "B" likewise to 3 customers.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Toggle rep B's active status off and read the dialog before confirming anything.
 2. Press Tab repeatedly and watch where focus goes; dismiss and watch where focus returns.
 3. Repeat step 1 for rep A (1 customer) and read the headline's noun.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
@@ -3034,41 +3093,41 @@
 </t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R3; S13-R4; S13-R12)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Type-YES gate: auto-focus; case-insensitive match; Enter submits</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Read the instruction text and check which element holds focus.
 2. Hover the disabled "Deactivate" button and read the tooltip.
@@ -3076,7 +3135,7 @@
 4. With a valid entry, press Enter.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
@@ -3089,41 +3148,41 @@
 </t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R6; S13-R7)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Cancel and X dismiss the Deactivate dialog; Escape and clicking outside do not</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Click the "Cancel" button and watch the dialog; then re-open it.
 2. Click the "X" close icon and watch the dialog; then re-open it.
@@ -3132,7 +3191,7 @@
 5. After each action, check the staff member's active status.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
@@ -3146,47 +3205,47 @@
 </t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Valid submit locks the dialog, then deactivates keeping assignments</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a ZZAUTOTEST rep with known customer assignments.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Type YES and submit; during the request try Cancel, X, and Escape.
 2. After success, check the staff member's status and each previously assigned customer's Sales Representative.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
@@ -3199,48 +3258,48 @@
 </t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>After deactivation: toggle unchanged, CSV shows No, report credit intact</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST rep with assignments AND matching invoices was just deactivated via the dialog flow.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Re-open the staff member and read the sales-representative toggle.
 2. Download the Sales Representative Assignments CSV and read the rep's rows.
 3. Open the report and find the rep's row.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The sales-representative toggle state is unchanged by the deactivation flow.
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
@@ -3252,48 +3311,48 @@
 </t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>No dialog: toggle off, no assignments, already inactive, or reactivation</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST staff member X is active WITHOUT the sales-representative toggle; ZZAUTOTEST rep Y (with assignments) is currently inactive; ZZAUTOTEST rep Z is active with the sales-representative toggle ON and NO customers assigned.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate X and watch for a dialog.
 2. Reactivate rep Y via the standard toggle and watch for a dialog; check Y's customer assignments afterwards.
 3. Deactivate rep Z (sales-representative toggle on, no assignments) and watch for a dialog.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
@@ -3306,48 +3365,48 @@
 </t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R2; S13-N2; S13-N3; S13-E3)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>A deactivation failure shows the error toast and leaves the status alone</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments; you can force the request to fail (go offline just before submitting).</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Type YES, force the failure condition, and submit.
 2. Read the toast; check the staff member's active status.
 3. Dismiss, re-open the dialog, and look at the confirmation input.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
@@ -3359,48 +3418,48 @@
 </t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N5; §7)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>If the assignment pre-check fails, the warning dialog still opens</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-rep toggle on.
 2. You can force the pre-deactivation assignment check to fail (for example, cut the network exactly when toggling active off) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Toggle the staff member's active status off while forcing the check to fail.
 2. Read the dialog that opens.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
@@ -3411,47 +3470,47 @@
 </t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N4)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned sits between the column selector and the date picker, off</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. No remembered settings; at least one matching invoice with NO assigned rep exists (seed via a WO with no Sales Representative whose customer also has no rep).</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Find the "Show Unassigned" toggle in the toolbar and note its position and default state.
 2. With it off, look for an Unassigned row and check the grand Totals against the rep rows only.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
@@ -3462,41 +3521,41 @@
 </t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R1; S22-R2; Story 18 S18-R7.2)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned adds one top-pinned Unassigned row that acts like a rep row</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. Matching unassigned invoices exist; the grand Totals with the toggle off are noted.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Turn "Show Unassigned" on and read the new row and its position.
 2. Read the grand Totals indicator.
@@ -3504,7 +3563,7 @@
 4. Turn the toggle off again.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
@@ -3517,48 +3576,48 @@
 </t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>No empty Unassigned row is ever rendered</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: a filter set with NO matching unassigned invoices (but some rep rows).
 2. Scenario B: the Unassigned row is populated and expanded.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: turn Show Unassigned on and look for the row; then narrow so no reps match either and read the table.
 2. Scenario B: with the Unassigned row expanded, turn the toggle off, then back on.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
@@ -3569,41 +3628,41 @@
 </t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-N1; Story 6 S6-N2)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Column selector: seven metric toggles; five always-on columns cannot be hidden</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. No remembered column preference exists (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Click the column selector button in the toolbar.
 2. Read the toggle list.
@@ -3612,7 +3671,7 @@
 5. Hide all seven metric columns and read the table and the grand Totals indicator.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
@@ -3626,47 +3685,47 @@
 </t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1 — S20-R2/S20-R3 CLOSE the seven toggles and the five always-on columns; Location is automatic and in neither list [S21-R7])</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Toggling a column applies at once to summary; detail and Totals rows</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. A rep is expanded and the Totals indicator is visible.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Toggle "Parts Margin" off and immediately check the summary rows, detail rows, and the Totals row.
 2. Toggle it back on.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
@@ -3677,47 +3736,47 @@
 </t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R4; S20-R7)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Column visibility never affects the exports</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. Several metric columns are hidden via the column selector.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Download all four exports (Summary PDF, Expanded View PDF, Summary CSV, Expanded View CSV).
 2. Check each file's columns.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
 ---
@@ -3727,47 +3786,47 @@
 </t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R8)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Hiding the active sort column keeps the sort</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. The report is sorted by a metric column (e.g., Margin descending).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Hide that column via the column selector and read the row order.
 2. Show the column again and look at its header.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
@@ -3778,48 +3837,48 @@
 </t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R9)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>All filter and view settings are restored before the first data fetch</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Set a custom date range, "Parts only," "Paid," a specific location set, Show Unassigned on, hide two metric columns, and sort by Margin descending.
 2. Leave the report and return; also try a full page reload.
 3. Watch what data loads first.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
@@ -3830,47 +3889,47 @@
 </t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R1; Story 20 S20-R5)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Expansion state and scroll position are not remembered and reset on reload</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are expanded and the table is scrolled partway.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Reload the page.
 2. Check the rows and the scroll position.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
@@ -3881,47 +3940,47 @@
 </t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R2; §2 Out of Scope)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>A stale saved value falls back to its default and never errors</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. Your saved settings include a location you are then un-assigned from (restore access afterwards).</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter, the data, and watch for any error.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
@@ -3933,47 +3992,47 @@
 </t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R3)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>First visit or cleared storage yields all defaults; no server-side profile</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You have distinctive saved settings, then clear the browser's site data (or use a fresh profile).
 2. You are working in a known active location (the application's location switcher).</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read every setting.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
@@ -3984,47 +4043,47 @@
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R4; S23-N1; Story 2 S2-R4; S2-R7; Story 21 S21-R2)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The A to Z default is its own saved value</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You have never clicked a financial column header in this browser session/profile (the report is in the A→Z default).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Change a few filters (no sort click), leave the report, and return.
 2. Read the row order and the headers.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
@@ -4035,48 +4094,48 @@
 </t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R5; Story 11 S11-R4)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>The ⋯ overflow menu lists exactly four download actions</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Sales By Representative report.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ (three-dot) button in the report toolbar — it is the first control in the toolbar's action cluster.
 2. Click it and read the menu entries top to bottom.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
@@ -4087,36 +4146,36 @@
 </t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R1 + Story 17 S17-R3 (position) — S14-R1 CLOSES it in the spec's own words ("lists exactly four actions"); so the closed list IS the requirement)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>All four downloads respect filters, full result set, and active order</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps showing.
 2. Set a specific date range, Product Type, Invoice Status, and a location selection; turn Show Unassigned on.
@@ -4124,14 +4183,14 @@
 4. Leave at least one rep collapsed (do not expand it).</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Compare each file's rows against the on-screen result: which reps appear, which invoices are included, and the row order.
 3. Check where the Unassigned row sits in each file.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
@@ -4145,49 +4204,49 @@
 </t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2; S14-R2a; S14-R20 + Story 21 S21-R6 + Story 22 S22-R4 — all four downloads honour the filters; the full result set and the active order; S14-R20 = the "Locations:" line in every export)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Summary PDF: one rolled-up row per rep with a recomputed grand totals row</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, one of them a toggled-off ("(Inactive)") contributor if one can be arranged.
 2. A date range is selected.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (PDF)" from the ⋯ menu and open the file.
 2. Read the top of the first page, the column headers, one rep row, and the last row.
 3. Compare the totals row's Margin % against the child rows.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
@@ -4201,41 +4260,41 @@
 </t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3; S14-R5; S14-R20; Story 2 S2-R5; §3 Margin % definition — Summary PDF; plus the automatic Location column in all four exports)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF: one page-block per rep with its own totals; no grand</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (PDF)" from the ⋯ menu and open the file.
 2. Check how each rep's section starts and what its table contains.
@@ -4243,7 +4302,7 @@
 4. Compare the order of one rep's invoices against the on-screen expanded order.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, only when more than one location is in scope, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
@@ -4258,47 +4317,47 @@
 </t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R6; S14-R8; S14-R20; Story 6 S6-R9 — Expanded PDF page-block per rep; plus the automatic Location column after Status)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF truncates invoice numbers longer than 18 characters</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. At least one invoice in the current view has an invoice number LONGER than 18 characters, and one has a number of 18 characters or fewer (seed data if needed).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep on screen and read both invoice numbers.
 2. Download the Expanded View PDF and read the same two invoice numbers.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
@@ -4310,49 +4369,49 @@
 </t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R7)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>PDF footer on every page, default-logo fallback, and deterministic PDF filenames</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. For the fallback check: the organization has NO configured logo (clear it in settings if permitted, and restore afterward).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs and note each saved file's name.
 2. Scroll through every page of both PDFs and read the footer.
 3. With the organization logo not configured, download a PDF again and look at the header strip's logo region.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
@@ -4366,48 +4425,48 @@
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3a; S14-R4; S14-R11 — S14-R11 CLOSES both PDF filenames verbatim ("deterministic") and S14-R4 closes the footer string; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. The current view includes at least one negative money value (for example, a net-credit/return invoice — seed one if needed) and, if arrangeable, one toggled-off "(Inactive)" contributor.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs.
 2. Find the negative money value in each and read how it is written.
 3. Read the rep names in both PDFs.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
@@ -4419,49 +4478,49 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R9; S14-R10)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>PDF body font steps down as the longest dollar value grows; no overflow</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).
 2. This test reads what is inside a downloaded PDF. Open the file in any PDF viewer and use the viewer's own text search (Ctrl+F) to find the text named below — that is enough. There is nothing to install.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Download the Summary PDF for a view whose longest positive dollar value is 9 characters or fewer; note the body text size (a relative comparison across files is enough).
 2. Repeat for views whose longest positive value is 10, 11, and 12-or-more characters (as far as seedable).
 3. In each file, check whether any value overflows or wraps its column.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
@@ -4473,41 +4532,41 @@
 </t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R12; S14-R13)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Summary CSV: file name, UTF-8 BOM, verbatim headers, one row per rep</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing; one rep has invoices for the same customer more than once (to check de-duplication).</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
@@ -4515,7 +4574,7 @@
 4. For one rep, compare "# Invoices" with the on-screen (N) count, and "# Customers" with the number of DISTINCT customers across that rep's matching invoices.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal. On this build only nine of them arrive - Representative, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal - because # Invoices, # Customers, Hrs Worked and Hrs Invoiced are missing by mistake. Record what you see; the four missing columns are with the developers.
@@ -4531,48 +4590,48 @@
 </t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R15; S14-R18; S14-R20 — Summary CSV headers; plus the automatic Location column in all four exports; S14-R15's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Expanded CSV: file name, verbatim headers, one row per invoice</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
 3. Compare the rows against the on-screen invoices (all reps, expanded).</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
@@ -4586,47 +4645,47 @@
 </t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R16; S14-R20 — Expanded CSV headers; plus the automatic Location column after Status; S14-R16's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>CSV cells: plain numbers, signed Inv. Hrs, empty Margin %, (Inactive)</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded both report CSVs from a view that includes a negative money value, a rep whose Margin % shows "—" on screen (Subtotal ≤ 0), and an "(Inactive)" contributor (seed what is missing).</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Open each CSV in a text editor (not a spreadsheet).
 2. Read a money cell, the negative value's cell, an Inv. Hrs cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Representative" cell.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
@@ -4643,41 +4702,41 @@
 </t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>The Unassigned row appears in all four downloads only when the toggle is on</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set includes at least one invoice with no assigned sales representative (seed one if needed).</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Turn Show Unassigned ON and download all four files.
 2. Find the Unassigned entry in each file.
@@ -4685,7 +4744,7 @@
 4. Search each file for the unassigned invoices.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
@@ -4698,49 +4757,49 @@
 </t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>A failed download shows the canonical error toast</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.
 3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a PDF download and watch the menu action while the file is being generated.
 2. Force a failure on a download (PDF or CSV) and read the toast.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
@@ -4752,47 +4811,47 @@
 </t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Over-cap Expanded View PDF is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. A filter set exists (or can be seeded) whose invoice detail rows exceed 10,000 — if this volume cannot be produced in the environment, mark Blocked-Env with the reason.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Apply the over-cap filter set.
 2. Choose "Download Expanded View (PDF)" and read the toast.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
@@ -4805,47 +4864,47 @@
 </t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2; §7 — 10k-row export cap; no truncated file; toast persists 120s; the toast STRING is the ONE suite-wide message ruled by Chris Ward 2026-07-31 Q2=A [newest-wins]; his SBR spec edit is pending)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>An empty-data export still generates with zeroed Summary PDF totals</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set matches ZERO invoices (for example, a date range with no activity) — the report shows its empty state.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Open each and inspect its contents.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
@@ -4859,49 +4918,49 @@
 </t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E3)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Report Name dropdown lists Sales Representative Assignments at the bottom</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Reports access.
 2. Note the current order of the Report Name dropdown entries before checking.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. In the Reports left sidebar, under the Accounting header, click the "Export Reports" entry — a dialog titled "Export Report" opens.
 2. Open the Report Name dropdown and read the list top to bottom.
 3. Select "Sales Representative Assignments" and look at the dialog body.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
@@ -4914,49 +4973,49 @@
 </t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R1; S15-R2)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Sales Representative Assignments CSV: file name, headers, success toast</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer in the organization has an assigned sales representative.
 2. The Export Report dialog is open with "Sales Representative Assignments" selected.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Click the Export action.
 2. Note the saved file's name and read the toast.
 3. Open the file in a text editor and read the header row.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
@@ -4970,41 +5029,41 @@
 </t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R3; S15-R4; §7 — S15-R4 CLOSES the three headers; "Sales Rep"→"Sales Representative" per Chris Ward 2026-07-31 Q5 [newest-wins]; NOT one of the four report exports so S14-R20 adds no Location)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Assignments CSV: one row per assigned customer, sorted customer then rep</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. The organization has several customers with assigned reps and at least one customer with NO assigned rep (seed as needed).</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Representative Assignments CSV.
 2. Count the rows against the customers with assigned reps.
@@ -5012,7 +5071,7 @@
 4. Read the row order.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
@@ -5024,47 +5083,47 @@
 </t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R5; S15-R7; S15-R10)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>"Rep is active?" tracks the staff-active status, not the toggle</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. Arrange (and afterward restore): one assigned rep whose staff record is ACTIVE but whose sales-representative toggle is OFF, and one assigned rep whose staff record is INACTIVE but whose toggle is ON.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Representative Assignments CSV.
 2. Read the "Rep is active?" value on both reps' customer rows.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
@@ -5076,48 +5135,48 @@
 </t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R6; Story 13 S13-R11)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>A deleted rep record still exports one row from the stored name, marked No</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose assigned rep's staff record has been cleared or deleted while the customer still references it (seed and delete a throwaway ZZAUTOTEST rep if needed).</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Representative Assignments CSV.
 2. Find that customer's row and read its "Sales Representative" and "Rep is active?" cells.
 3. If two customers carry different stored name spellings for the same underlying rep, compare their rows.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Representative" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
@@ -5130,49 +5189,49 @@
 </t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R8; S15-R9)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Assignments export failure and nothing-to-export use the dialog's messages</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. For the empty path: no customer in the organization has an assigned rep (or use a state where the export yields zero rows).
 2. For the failure path: you can force a generation failure (for example, cut the network on Export) — if not forceable, mark that step Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, select "Sales Representative Assignments" in the Export Report dialog and click Export.
 2. Read the dialog warning and inspect any downloaded file.
 3. Force a generation failure and read the toast.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
@@ -5183,41 +5242,41 @@
 </t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R11; S15-N2; §7)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Empty state: verbatim message, no grand Totals, toolbar stays interactive</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter set that matches no invoices for any rep (for example, a date range with no activity), with Show Unassigned OFF or with no matching unassigned invoices either.
 2. Read the data area and look for the grand Totals indicator.
@@ -5225,7 +5284,7 @@
 4. Look at the toolbar, then change the date range to a period WITH activity.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
@@ -5239,49 +5298,49 @@
 </t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R1; S16-R2; S16-R3; S16-N1; Story 2 S2-N1; Story 21 S21-N2; §7)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Loading shows a centered spinner over the data area and hides the Totals</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Reload the report and watch the data area during the initial load.
 2. Change a filter and watch the data area during the re-fetch.
 3. While loading, try to interact with the toolbar.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
@@ -5294,49 +5353,49 @@
 </t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R4)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>A load failure shows the inline could-not-load message with a Retry</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Set several non-default filters.
 2. Force a load/re-fetch failure and read the data area.
 3. Restore the network and click "Retry".</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
@@ -5348,48 +5407,48 @@
 </t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R5; §7)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. Open the report on a phone-sized viewport (real device or browser device emulation, width under 1024px).</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Find and operate each toolbar control by touch: the ⋯ exports, the column selector, the Show Unassigned toggle, the date range picker, Product Type, Invoice Status, and Location.
 2. Look at how the controls are laid out.
 3. Widen the viewport to 1024px or more and compare.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
@@ -5401,48 +5460,48 @@
 </t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R1; S17-R2; S17-R3)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>On a phone the table scrolls sideways with Subtotal pinned outside it</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a phone-sized viewport (under 1024px) with at least one rep row.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the data table sideways and watch the Subtotal column.
 2. Look below the table for the totals bar and swipe the table again.
 3. Tap a rep row's chevron.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
@@ -5454,48 +5513,48 @@
 </t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile))</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Touch targets are at least 44×44 px and touch users get no hover-only tooltips</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a touch device or touch emulation (under 1024px).
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Measure (device emulation ruler/inspector) the touch targets of a row chevron, the Show Unassigned toggle, the ⋯ button, and — via the staff deactivation dialog if opened — the dialog's X.
 2. Tap-and-hold the icon controls and watch for tooltips.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
@@ -5506,41 +5565,41 @@
 </t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R6; S17-N1; Story 18 S18-R9)</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Layout: white toolbar; blue-grey page; separator; edge-to-edge white table</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a desktop browser (light mode) with data showing.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar strip, at the space between its controls and the edges of the strip, and at how the title and the rightmost control line up with the table columns.
 2. Look at the page background around the data area, the line between the toolbar and the column headers, and the table's side edges.
@@ -5548,7 +5607,7 @@
 4. Open another report in the suite (for example Parts Velocity) side by side and compare.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
 2. The data area sits on the standard blue-grey page background and runs edge-to-edge against the side navigation — there is no strip of empty space down either side.
@@ -5564,41 +5623,41 @@
 </t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1)</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Dark mode: page, toolbar, table; Totals switch to dark equivalents</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing, including at least one expanded rep (badges visible) and non-zero Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page, toolbar, header, body cells, and the grand Totals indicator.
@@ -5606,7 +5665,7 @@
 4. Download a PDF while in dark mode and open it.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
@@ -5619,48 +5678,48 @@
 </t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Every icon-only control carries its specified accessible name</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the accessible name of: the ⋯ exports button, the column selector button, one rep row's chevron (collapsed, then expanded), and the header chevron.
 2. Open the staff deactivation dialog (Story 13 flow) and inspect its X close icon.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
@@ -5674,49 +5733,49 @@
 </t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R9)</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Chevrons and sortable headers are keyboard-operable and expose their state</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Tab to a rep row's chevron; press Enter, then Space.
 2. Tab to a financial column header; press Enter, then Space.
 3. Inspect what state each control exposes to assistive technology.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
@@ -5728,47 +5787,47 @@
 </t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R10)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>The subdued grey of the (N) count and (Inactive) tag meets WCAG AA contrast</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a rep row showing a (N) count and - if arrangeable - an "(Inactive)" tag.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Read the subdued-grey (N) count and the "(Inactive)" tag in light mode, then switch to dark mode and read them again.
 2. Review how Inv. Hrs, the status badges, and the links convey their meaning.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
@@ -5780,41 +5839,41 @@
 </t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R11; S18-R12 — subdued-grey (N) count and "(Inactive)" tag at ≥ 4.5:1 WCAG AA in both modes; nothing conveyed by colour alone; the ratio is a design-token property so the check is by-eye)</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Sales Representative selector shows on WO and Part Sale, not on imported</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You have: an open standard Work Order, an open Part Sale WO, an imported Work Order, and a way to view a WO in History mode.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Open the standard Work Order and look at the left panel.
 2. Open the Part Sale WO and look at the left panel.
@@ -5822,7 +5881,7 @@
 4. View a WO in History mode and look for the field.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The left panel includes a "Sales Representative" selector on the standard Work Order.
 2. The left panel includes the same "Sales Representative" selector on the Part Sale WO.
@@ -5836,48 +5895,48 @@
 </t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R1; S19-N1)</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Selector offers only reps whose sales-representative toggle is on</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member has the sales-representative toggle ON and at least one has it OFF. To arrange this: open Settings, go to Staff, edit the staff member, and use the sales-representative toggle there (restore both afterward).</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Open a Work Order and open the "Sales Representative" selector.
 2. Search the option list for both staff members.
 3. Inspect the selector's accessible name.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
@@ -5890,48 +5949,48 @@
 </t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>A new WO opens with Sales Representative unassigned; a change saves at once</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member is offered as a sales representative.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Create a new Work Order (mark it ZZAUTOTEST) and read the Sales Representative field before touching it.
 2. Select a rep in the field, then navigate away WITHOUT any explicit save and reopen the WO.
 3. Repeat the unassigned-open check on a new Part Sale WO.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
@@ -5943,47 +6002,47 @@
 </t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R3; S19-R4)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>The Sales Representative selector is read-only when Invoiced or Paid</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. One Work Order is in "Invoiced" status and one is in "Paid" status (drive throwaway ZZAUTOTEST WOs into these states if needed).</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Open the Invoiced WO and try to change the Sales Representative field.
 2. Open the Paid WO and try the same.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.
@@ -5996,48 +6055,48 @@
 </t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R5)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Invoice credit snapshot: WO rep, else customer rep, else unassigned</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. Three throwaway ZZAUTOTEST setups: (a) a WO WITH a Sales Representative assigned; (b) a WO with NO rep whose customer HAS an assigned rep; (c) a WO with NO rep whose customer has NO assigned rep.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Invoice all three WOs.
 2. On the report (Show Unassigned on, filters covering the invoices), find each invoice and note which row it sits under.
 3. Go back to WO (a), change its Sales Representative to a different rep, and re-check the already-created invoice on the report.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Invoice (a) is credited to the WO's Sales Representative.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
@@ -6050,49 +6109,49 @@
 </t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Customer record shows a "Sales Representative" row; "Unassigned" when none</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. One customer HAS an assigned sales representative and one customer has NONE.
 2. A Work Order exists whose bound Sales Representative can have their toggle turned off (arrange and restore afterward).</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open the assigned customer's record and read the left-panel sidebar.
 2. Open the unassigned customer's record and read the same row.
 3. Turn the bound rep's sales-representative toggle OFF, reopen the Work Order, and read the Sales Representative selector; then open its option list.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
@@ -6105,50 +6164,50 @@
 </t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec Story 19 S19-R7; S19-E1 — customer-card label RE-RULED to the full "Sales Representative" per the PRD companion video 2026-07-30 + Chris Ward answer 2026-07-31 Q5=A; the spec text still says "Sales Rep")</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>A rep's invoice detail rows are fetched from the server only on the first expand</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows, one with a large invoice count if seedable.
 2. The browser's network panel is open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note which requests deliver the summary rows.
 2. Expand one rep and watch the network panel; collapse and re-expand it.
 3. If a rep has many invoices, scroll/page through its expanded detail rows.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
@@ -6160,48 +6219,48 @@
 </t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R2)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Sorting is performed server-side and returns the first page</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several rep rows; the network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Click a financial column header and watch the network panel.
 2. Click the same header again (descending) and watch again.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
@@ -6213,48 +6272,48 @@
 </t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R5)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Grand totals are server-computed over the full filtered set</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Load the report with everything collapsed and inspect the summary response and the grand Totals indicator.
 2. Compare the grand totals against the full filtered result (for example, via the Summary CSV), not just the loaded rows.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
@@ -6266,49 +6325,49 @@
 </t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>All four exports are generated server-side against the active filters and sort</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Trigger each of the four downloads and observe the export requests and responses.
 2. Compare the delivered files against the active filters and sort.
 3. If forceable, fail one export server-side and check what (if anything) downloads.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
@@ -6320,49 +6379,49 @@
 </t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2a; S14-N2; S14-E3)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>The Expanded View PDF's 10,000-row cap is enforced server-side BEFORE generation</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. A filter set producing more than 10,000 invoice detail rows exists or can be seeded — otherwise mark Blocked-Env with the reason.
 2. The network panel is open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download Expanded View (PDF)" against the over-cap filter set and observe the export request/response.
 2. Check whether any file arrives.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
@@ -6375,50 +6434,50 @@
 </t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Deactivating a rep first runs a server pre-check returning the count</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-representative toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
 2. The network panel is open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. In staff administration, toggle that staff member's active status off and watch the network panel BEFORE the dialog appears.
 2. Read the pre-check response and compare it with the dialog's "{N} customer{s}" headline.
 3. Cancel the dialog (leave the staff member active).</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
@@ -6430,13 +6489,13 @@
 </t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R4)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -523,222 +523,220 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
+          <t>1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
 2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
 3. Selecting the entry opens the report in the main content area.
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>SV-8619 (SBR spec Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6 — 'at the bottom' = below the four named anchor reports per PRD video 2026-07-30 01:18-02:05; order among the four new reports not important)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>The nav entry fits the full Sales By Representative label; no truncation</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Access &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Reports navigation with the entry visible.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Look closely at the "Sales By Representative" entry's label against the entry's left and right edges.
+2. Compare its padding with the neighbouring entries.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
+2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S1-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R7; §1 naming note)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sales By Representative is visible to anyone who sees another Performance report</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Permissions</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1. A test user exists whose role can see another Performance-group report (create/assign a ZZAUTOTEST role if needed; restore afterwards).
+2. You are signed in as that user.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Reports navigation and read the Performance group.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S1-R1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SV-8619 (SBR spec Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6 — 'at the bottom' = below the four named anchor reports per PRD video 2026-07-30 01:18-02:05; order among the four new reports not important)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>The nav entry fits the full Sales By Representative label; no truncation</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Access &amp; Navigation</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Reports navigation with the entry visible.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Look closely at the "Sales By Representative" entry's label against the entry's left and right edges.
-2. Compare its padding with the neighbouring entries.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
-2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-R7).
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R1)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Without Reports access: no navigation, no export menu, no Export dialog</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Permissions</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1. A test user exists whose role has no Reports access (use/create a ZZAUTOTEST role; restore afterwards).
+2. You are signed in as that user.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Look for the Reports navigation.
+2. Try to open the report by direct link (address copied from a permitted session).
+3. Try to reach the Export Reports dialog.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
+2. The report (and its ⋯ export menu) is not reachable.
+3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S1-N1, S14-N3, S15-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R7; §1 naming note)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Sales By Representative is visible to anyone who sees another Performance report</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Without staff-administration access the deactivation flow is unreachable</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>SBR — Permissions</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1. A test user exists whose role can see another Performance-group report (create/assign a ZZAUTOTEST role if needed; restore afterwards).
-2. You are signed in as that user.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Reports navigation and read the Performance group.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-R1).
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user without staff-administration access.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to reach staff administration and open a staff member for editing.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R1)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Without Reports access: no navigation, no export menu, no Export dialog</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Permissions</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1. A test user exists whose role has no Reports access (use/create a ZZAUTOTEST role; restore afterwards).
-2. You are signed in as that user.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Look for the Reports navigation.
-2. Try to open the report by direct link (address copied from a permitted session).
-3. Try to reach the Export Reports dialog.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
-2. The report (and its ⋯ export menu) is not reachable.
-3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S1-N1, S14-N3, S15-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Without staff-administration access the deactivation flow is unreachable</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Permissions</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in as a user without staff-administration access.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to reach staff administration and open a staff member for editing.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N1)</t>
@@ -781,14 +779,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A date range picker is visible in the report toolbar.
+          <t>1. A date range picker is visible in the report toolbar.
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 17 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Sales By Representative report specification version 18 (S2-R1, S2-R2), read on 11 August 2026, says something different, his decision is the later word and is the authority.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -833,13 +830,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A custom range within the cap applies normally via the date-picker dialog.
+          <t>1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S2-R3, S2-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S2-R3, S2-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - needs the calendar driven past a 366-day span, which this harness could not do</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -885,14 +881,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
+          <t>1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S2-R5, S2-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S2-R5, S2-R8), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -940,16 +935,15 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The dropdown offers exactly three options: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" as the default on first load.
+          <t>1. The dropdown offers exactly three options: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" as the default on first load.
 2. "Parts only" includes only invoices whose number starts with P.
 3. "Service only" includes only invoices whose number starts with S.
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -995,15 +989,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. An "Invoice Status" dropdown is visible in the toolbar.
+          <t>1. An "Invoice Status" dropdown is visible in the toolbar.
 2. It offers exactly four options: "All Statuses," "Unpaid," "Partially Paid," "Paid."
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R1, S4-R2, S4-R3, S4-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S4-R1, S4-R2, S4-R3, S4-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1050,15 +1043,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
+          <t>1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
 2. "Partially Paid" includes the partially-paid AND the prepaid-with-a-balance-owed invoices.
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S4-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1105,15 +1097,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
+          <t>1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
 2. A rep appears only if at least one invoice matches all active filters.
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1157,13 +1148,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
+          <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S4-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S4-R8), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1208,13 +1198,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The location filter is the rightmost control in the toolbar.
+          <t>1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-R1, S18-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S21-R1, S18-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1262,15 +1251,14 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
+          <t>1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
 3. "All Locations" means all locations the user can access — location Z's data is never included.
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S21-R3, S21-R4, S21-R5), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1318,7 +1306,7 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S21-N1), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1374,7 +1362,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
+          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
 2. A rep summary row whose invoices are all at one location shows that location's name.
 3. A rep summary row whose invoices span more than one location shows "Multiple".
 4. An invoice detail row shows that invoice's own exact location — never "Multiple".
@@ -1384,10 +1372,9 @@
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
 Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements are that the column-selection dropdown holds the seven metric columns only, and that Location is one of the columns you can switch on and off there. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S21-R7, S21-R8, S18-R13, S14-R20). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: its summary says it can be toggled there, while the requirement that governs the column says it appears only when the view spans more than one location and the dropdown holds the seven metric columns only. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S21-R7, S21-R8, S18-R13, S14-R20), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: its summary says it can be toggled there, while the requirement that governs the column says it appears only when the view spans more than one location and the dropdown holds the seven metric columns only. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1433,15 +1420,14 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Rep A occupies exactly one summary row.
+          <t>1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R1, S5-R4, S5-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S5-R1, S5-R4, S5-N1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1488,16 +1474,19 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
+          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: on a representative's summary row the name is stretched across the Date, Invoice, Customer and Status columns as ONE merged cell, so that row has eleven cells where the table has fourteen column positions — the Invoice, Customer and Status cells are not there to be blank. Everything still lines up under the correct headings, and items 1, 2, 4 and the alignment part of item 5 all pass; it is item 3 that does not. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-9001.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-9001)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1544,15 +1533,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
+          <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S5-R9), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1597,14 +1585,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
+          <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R1, S6-R2, S6-R3, S6-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S6-R1, S6-R2, S6-R3, S6-E1), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1650,14 +1637,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With at least one rep collapsed the header chevron shows the "expand" glyph.
+          <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R5, S6-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S6-R5, S6-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1702,13 +1688,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
+          <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S6-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1754,14 +1739,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Expanded state is preserved across filter and sort changes within the same session.
+          <t>1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R8, S6-N1, S23-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S6-R8, S6-N1, S23-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1806,15 +1790,18 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Detail rows order by invoice date descending (newest first).
+          <t>1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R9, S11-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the newest-first part is right, but invoices that share a date come out in the order they were created rather than by invoice number. On 12 June 2026, for example, the rows run S-15487, P-117, P-113, S-15750, S-15646, S-15828, S-15812 - the numbers are in no order at all. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8974
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S6-R9, S11-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8974)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1861,15 +1848,14 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
+          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1914,14 +1900,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
+          <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S8-R3, S18-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S8-R3, S18-R8), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1966,13 +1951,16 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
+          <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-R1, S9-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: item 1 passes — the heading really does read "Inv. Hrs" with the period. Item 2 does not: the value reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-R1, S9-R2), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2020,15 +2008,18 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
+          <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Inv. Hrs column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2073,13 +2064,16 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
+          <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Inv. Hrs column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-N1), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2129,7 +2123,7 @@
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S10-R5), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2182,7 +2176,7 @@
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S5-R2, S21-R7).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S5-R2, S21-R7), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2233,7 +2227,7 @@
           <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (§3 Key Decisions accounting parentheses).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (§3 Key Decisions accounting parentheses), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2284,7 +2278,7 @@
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (§3 half).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (§3 half), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2333,14 +2327,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
+          <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S9-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Inv. Hrs column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-R2), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2388,16 +2385,19 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Subtotal is the rightmost column on every row type.
+          <t>1. Subtotal is the rightmost column on every row type.
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
 3. Subtotal values are bold across the header, every summary row, every detail row, and the grand Totals indicator.
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: Subtotal itself is correct - it is the last column, it stays stuck to the right edge while you scroll sideways, and it is bold on the heading row, on every representative row and on the Totals row. What fails is the heading row: it does NOT stay stuck to the top when you scroll down the page, it scrolls away with the rows. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8977
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8977)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2444,16 +2444,19 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
+          <t>1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
 3. The grand totals cover the FULL filtered result set — every matching non-reversed invoice across every rep, independent of which reps are expanded or loaded.
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5, S10-N1, S16-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Totals row does not stay stuck to the bottom of the scrolling area - it scrolls away with the rows. The row itself is correct otherwise: it reads "Totals", the four name columns are merged, and every figure is the total across the whole filtered result. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8977
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S10-R5, S10-N1, S16-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8977)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2499,15 +2502,18 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
+          <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5, S17-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: on a phone there is no separate totals bar underneath the table. The full wide Totals row stays inside the table and scrolls sideways with it, so you have to scroll right to read the Subtotal total. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8978
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S10-R5, S17-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8978)</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2552,14 +2558,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each financial column responds to a header click and reorders the rep rows.
+          <t>1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R1, S11-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S11-R1, S11-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2603,13 +2608,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Rows render in A→Z order by display name, case-insensitive.
+          <t>1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S11-R4), read on 11 August 2026.
+Last checked against build v3.5-f77875c on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2656,15 +2660,14 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
+          <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R5, S23-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S11-R5, S23-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2709,14 +2712,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only the rep summary rows reorder.
+          <t>1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R2, S22-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S11-R2, S22-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2761,13 +2763,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Reps with equal values in the sorted column retain the default A→Z order between them.
+          <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S11-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2813,14 +2814,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each invoice number is a clickable link.
+          <t>1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-R1, S12-R2, S12-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S12-R1, S12-R2, S12-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2866,14 +2866,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
+          <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-R3a, S23-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S12-R3a, S23-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2919,15 +2918,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
+          <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-R4, S12-R5, S12-R6, S12-N3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S12-R4, S12-R5, S12-R6, S12-N3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2972,13 +2970,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The tab navigates to the application's standard not-found/access-denied state.
+          <t>1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S12-N1, S12-N2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S12-N1, S12-N2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3028,16 +3025,15 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For the person who CAN open them, the Invoice # takes you to the work order or the part sale, and the customer name takes you to the customer's record, both in the same browser tab.
+          <t>1. For the person who CAN open them, the Invoice # takes you to the work order or the part sale, and the customer name takes you to the customer's record, both in the same browser tab.
 2. For the person who CANNOT open them, neither one takes them anywhere: the work order, the part sale and the customer record all stay out of reach.
 3. Nothing goes wrong on the way: no page saying you are not allowed in, no blank page, no error message. The report keeps showing all its rows and figures.
 4. Note for the tester: you have to CLICK the customer name rather than look at it. Even for someone who IS allowed to open it, the customer name is deliberately styled to look like ordinary text — same colour, no underline — so a name you can use and a name you cannot use look exactly the same. Clicking is the only way to tell.
 5. Note for the tester: what these two values should LOOK like for the second person is not fully settled, so do not fail the test on appearance. The report's description says they are shown as plain text when the person cannot open the target, but the numbered requirements underneath it still say the Invoice # and the customer name are always links. The product owner has been asked. Write down what you saw and carry on; only report a failure if that person actually reaches the work order, the part sale or the customer record.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17, whose §2 describes each expanded row's invoice number as a clickable link to the underlying work order or parts sale rendered as a link only when the user has permission to open that target and otherwise plain text, and the customer name as non-interactive plain text when the user cannot open the customer. That report's numbered requirements S12-R1 and S12-R3 were not updated to match and still describe both as clickable links, so this case asserts only what both readings require — that the person cannot reach the target — and the product owner has been asked to settle the rest.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18, read on 11 August 2026, whose §2 describes each expanded row's invoice number as a clickable link to the underlying work order or parts sale rendered as a link only when the user has permission to open that target and otherwise plain text, and the customer name as non-interactive plain text when the user cannot open the customer. That report's numbered requirements S12-R1 and S12-R3 were not updated to match and still describe both as clickable links, so this case asserts only what both readings require — that the person cannot reach the target — and the product owner has been asked to settle the rest.
 This has not yet been checked against a build.
-AUTOMATION: HOLD - waiting on one answer from the product owner about what these two values should look like, and it needs a second sign-in that cannot open work orders, part sales or customers
-</t>
+AUTOMATION: HOLD - waiting on one answer from the product owner about what these two values should look like, and it needs a second sign-in that cannot open work orders, part sales or customers</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3087,7 +3083,7 @@
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R1, S13-R3, S13-R4, S13-R12).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-R1, S13-R3, S13-R4, S13-R12), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3142,7 +3138,7 @@
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R6, S13-R7).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-R6, S13-R7), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3199,7 +3195,7 @@
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R8).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-R8), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3252,7 +3248,7 @@
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R9, S13-R10, S13-E1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-R9, S13-R10, S13-E1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3305,7 +3301,7 @@
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R11, S15-R6, S5-R9).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-R11, S15-R6, S5-R9), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3359,7 +3355,7 @@
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R2, S13-N2, S13-N3, S13-E3).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-R2, S13-N2, S13-N3, S13-E3), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3412,7 +3408,7 @@
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-N5).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-N5), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3464,7 +3460,7 @@
           <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-N4).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-N4), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3512,13 +3508,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
+          <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S22-R1, S22-R2, S18-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S22-R1, S22-R2, S18-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3565,15 +3560,14 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
+          <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3619,13 +3613,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
+          <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S22-N1, S6-N2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S22-N1, S6-N2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3673,16 +3666,15 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
+          <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3727,13 +3719,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The toggle takes effect immediately — no confirm step.
+          <t>1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R4, S20-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S20-R4, S20-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3778,12 +3769,11 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S20-R8), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3828,13 +3818,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
+          <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S20-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S20-R9), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3880,13 +3869,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
+          <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R1, S20-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S23-R1, S20-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3931,13 +3919,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. All rows render collapsed and the scroll position resets.
+          <t>1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S23-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3982,14 +3969,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
+          <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: a saved date range that is no longer valid does NOT fall back to This Month. The date button reads "Select Date Range", no data is requested at all, and the report sits empty with the no-data message. Nothing errors, so the second half of this test does pass - it is only the fall-back to the default that is missing. Every other saved setting does fall back correctly. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8976
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S23-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8976)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4034,13 +4024,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
+          <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4085,13 +4074,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report restores to the A→Z default order by rep display name.
+          <t>1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S23-R5, S11-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S23-R5, S11-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4137,13 +4125,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
+          <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R1, S17-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R1, S17-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4192,16 +4179,19 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
+          <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
 3. Rep rows appear in the report's currently-active order — the active column sort if one is set, otherwise the A→Z default.
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the spreadsheets write money with a dollar sign and thousands commas - "$1,979.40" - and write Margin % with a percent sign, where they should hold plain numbers so the file can be re-sorted and totalled. The filters, the full result set and the active order are all respected correctly. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8925
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8925)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4248,16 +4238,15 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
+          <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
 3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Representative report specification version 17 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, so his answers are the only basis for it.
-This has not yet been checked against a build.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. the Sales By Representative report specification version 18 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, so his answers are the only basis for it.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4304,180 +4293,186 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
+          <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, only when more than one location is in scope, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+What you should see today: the Expanded View PDF is not built as one block per representative. It is a single flat table with every representative and every invoice in it, one grand Totals row at the bottom that this file should not have, no page break between representatives and no per-representative totals row. It also comes out on A3 paper instead of A4. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8981
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R6, S14-R8, S14-R20, S6-R9), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8981)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R6; S14-R8; S14-R20; Story 6 S6-R9 — Expanded PDF page-block per rep; plus the automatic Location column after Status)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Expanded View PDF truncates invoice numbers longer than 18 characters</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Exports</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1. At least one invoice in the current view has an invoice number LONGER than 18 characters, and one has a number of 18 characters or fewer (seed data if needed).</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Expand the rep on screen and read both invoice numbers.
+2. Download the Expanded View PDF and read the same two invoice numbers.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On screen, both invoice numbers show in full — never truncated.
+2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
+3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R7), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R6; S14-R8; S14-R20; Story 6 S6-R9 — Expanded PDF page-block per rep; plus the automatic Location column after Status)</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Expanded View PDF truncates invoice numbers longer than 18 characters</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R7)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>PDF footer on every page, default-logo fallback, and deterministic PDF filenames</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>1. At least one invoice in the current view has an invoice number LONGER than 18 characters, and one has a number of 18 characters or fewer (seed data if needed).</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>1. Expand the rep on screen and read both invoice numbers.
-2. Download the Expanded View PDF and read the same two invoice numbers.</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On screen, both invoice numbers show in full — never truncated.
-2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
-3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R7).
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with data showing.
+2. For the fallback check: the organization has NO configured logo (clear it in settings if permitted, and restore afterward).</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Download both PDFs and note each saved file's name.
+2. Scroll through every page of both PDFs and read the footer.
+3. With the organization logo not configured, download a PDF again and look at the header strip's logo region.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
+2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
+3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The PDF still generates normally either way.
+What you should see today: the footer and the logo are correct on both files, but the file names are not the fixed names above - a date-range word is added to each one, so you get "sales-by-representative-summary-this_month.pdf" rather than "sales-by-representative-summary.pdf". The same happens to both spreadsheets. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8982
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Sales By Representative report specification version 18 (S14-R3a, S14-R4, S14-R11), read on 11 August 2026, differs, his decision is the authority.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8982)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3a; S14-R4; S14-R11 — S14-R11 CLOSES both PDF filenames verbatim ("deterministic") and S14-R4 closes the footer string; so the exact strings ARE the requirement)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Exports</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1. The current view includes at least one negative money value (for example, a net-credit/return invoice — seed one if needed) and, if arrangeable, one toggled-off "(Inactive)" contributor.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Download both PDFs.
+2. Find the negative money value in each and read how it is written.
+3. Read the rep names in both PDFs.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
+2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
+3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R9, S14-R10), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R7)</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>PDF footer on every page, default-logo fallback, and deterministic PDF filenames</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Exports</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data showing.
-2. For the fallback check: the organization has NO configured logo (clear it in settings if permitted, and restore afterward).</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>1. Download both PDFs and note each saved file's name.
-2. Scroll through every page of both PDFs and read the footer.
-3. With the organization logo not configured, download a PDF again and look at the header strip's logo region.</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
-2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
-3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The PDF still generates normally either way.
----
-Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
----
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 17 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3a; S14-R4; S14-R11 — S14-R11 CLOSES both PDF filenames verbatim ("deterministic") and S14-R4 closes the footer string; so the exact strings ARE the requirement)</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Exports</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>1. The current view includes at least one negative money value (for example, a net-credit/return invoice — seed one if needed) and, if arrangeable, one toggled-off "(Inactive)" contributor.</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>1. Download both PDFs.
-2. Find the negative money value in each and read how it is written.
-3. Read the rep names in both PDFs.</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
-2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
-3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R9, S14-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R9; S14-R10)</t>
@@ -4526,7 +4521,7 @@
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R12, S14-R13).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R12, S14-R13), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4576,18 +4571,21 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
+          <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal. On this build only nine of them arrive - Representative, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal - because # Invoices, # Customers, Hrs Worked and Hrs Invoiced are missing by mistake. Record what you see; the four missing columns are with the developers.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
----
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 17 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
-AUTOMATION: READY
-</t>
+What you should see today: the Summary spreadsheet arrives with only nine of the thirteen column headings - # Invoices, # Customers, Hrs Worked and Hrs Invoiced are all absent - and the file still ends with a Totals row that this version is not supposed to have. The Location column, the UTF-8 marker and the one-row-per-representative shape are all correct. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8880
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Sales By Representative report specification version 18 (S14-R15, S14-R18, S14-R20), read on 11 August 2026, differs, his decision is the authority.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8880)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4633,16 +4631,19 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
+          <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
----
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 17 (S14-R16, S14-R20) says something different, his decision is the later word and is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Expanded spreadsheet puts Invoice # BEFORE Date instead of after it, and heads that column "Invoice Status" instead of "Status". Everything else in the heading row is right, including the Location column in its correct place after the status column. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8972
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Sales By Representative report specification version 18 (S14-R16, S14-R20), read on 11 August 2026, says something different, his decision is the later word and is the authority.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8972)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4687,19 +4688,21 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
+          <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
 3. Margin % is a plain number to one decimal (for example, 45.2) with no % sign, and the cell is EMPTY where Margin % is undefined (Subtotal ≤ 0).
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R17).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8823)
-</t>
+What you should see today: in the spreadsheet the money arrives as text with a dollar sign and thousands separators, such as $11,176.88, and the columns come out in the file's own fixed order - Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Total Cost, Total Sell, Margin, Margin % - which is not the order on screen, does not put Total Cost last, and leaves out the Location column even when it is showing on screen. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R17), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8823)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4713,7 +4716,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>The Unassigned row appears in all four downloads only when the toggle is on</t>
+          <t>The Unassigned row appears in both CSV downloads only when the toggle is on</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4738,79 +4741,77 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>1. Turn Show Unassigned ON and download all four files.
+          <t>1. Turn Show Unassigned ON and download Summary (CSV) and Expanded View (CSV).
 2. Find the Unassigned entry in each file.
-3. Turn Show Unassigned OFF and download all four files again.
+3. Turn Show Unassigned OFF and download both CSVs again.
 4. Search each file for the unassigned invoices.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
-2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
-3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R19, S22-R2, S22-R4).
+          <t>1. With the toggle ON, the Summary CSV carries one rolled-up row whose "Sales Representative" cell reads the literal "Unassigned", sorted to the top of the data rows.
+2. With the toggle ON, the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned".
+3. With the toggle OFF, no Unassigned row and no unassigned invoices appear in EITHER CSV.
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If a file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+Scope note: this case covers the CSV only. The same rule applies to both PDF downloads (the Summary PDF grand-totals row aggregates Unassigned; the Expanded PDF gets its own top page-block), but PDF body structure is not observable by the automation suite — see the Deferred PDF-visual cases.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification (S22-R2, S22-R4, S14-R19), read on 11 August 2026.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>A failed download shows the canonical error toast</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Exports</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with data showing.
+2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.
+3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>1. Trigger a PDF download and watch the menu action while the file is being generated.
+2. Force a failure on a download (PDF or CSV) and read the toast.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
+2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
+3. A genuine failure downloads nothing — never a malformed file.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-N1, S14-N2, S14-E1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>A failed download shows the canonical error toast</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Exports</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data showing.
-2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.
-3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger a PDF download and watch the menu action while the file is being generated.
-2. Force a failure on a download (PDF or CSV) and read the toast.</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
-2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
-3. A genuine failure downloads nothing — never a malformed file.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-N1, S14-N2, S14-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
@@ -4853,15 +4854,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. No file is produced — the server declines rather than generating a truncated file.
+          <t>1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-E2); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8818)
-</t>
+What you should see today: the spreadsheet download works and produces a file, but the PDF download of the same view fails with a server error and no file arrives. It depends on how much is in the view, not on which report - filtered down to one or two rows the PDF downloads normally, and on a full unfiltered view of several thousand rows it fails every time. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8818
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-E2), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4906,16 +4909,15 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. All four downloads produce a FILE, not an error.
+          <t>1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
 3. The Expanded View PDF renders just the header strip with no per-rep blocks (it has no grand-totals row).
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-E3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-E3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4967,7 +4969,7 @@
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R1, S15-R2).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S15-R1, S15-R2), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5017,16 +5019,19 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
+          <t>1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the file name, the three headings and the success message are all correct, but the file does NOT start with the UTF-8 marker. The report's own two spreadsheets do start with it, so this one file is the odd one out. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8983
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S15-R3, S15-R4, S14-R20), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8983)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5077,7 +5082,7 @@
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R5, S15-R7, S15-R10).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S15-R5, S15-R7, S15-R10), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5129,7 +5134,7 @@
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R6, S13-R11).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S15-R6, S13-R11), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5183,7 +5188,7 @@
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R8, S15-R9).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S15-R8, S15-R9), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5236,7 +5241,7 @@
           <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S15-R11, S15-N2).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S15-R11, S15-N2), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5286,127 +5291,129 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
+          <t>1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
 3. The same message appears when no staff member has ever been credited — there is no separate "no reps configured" message; the report is contributor-driven.
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+What you should see today: the message reads "No sales data found for the selected filters." instead of the wording above. The rest of this test is correct - no data rows are drawn and the toolbar stays usable. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8973
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8973)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R1; S16-R2; S16-R3; S16-N1; Story 2 S2-N1; Story 21 S21-N2; §7)</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Loading shows a centered spinner over the data area and hides the Totals</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Loading, Empty &amp; Error States</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Reload the report and watch the data area during the initial load.
+2. Change a filter and watch the data area during the re-fetch.
+3. While loading, try to interact with the toolbar.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
+2. The grand Totals indicator is hidden during loading.
+3. The toolbar stays interactive so filters can be changed mid-load.
+4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S16-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R4)</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>A load failure shows the inline could-not-load message with a Retry</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Loading, Empty &amp; Error States</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1. Set several non-default filters.
+2. Force a load/re-fetch failure and read the data area.
+3. Restore the network and click "Retry".</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
+2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
+3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S16-R5), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R1; S16-R2; S16-R3; S16-N1; Story 2 S2-N1; Story 21 S21-N2; §7)</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Loading shows a centered spinner over the data area and hides the Totals</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Loading, Empty &amp; Error States</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).
-2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>1. Reload the report and watch the data area during the initial load.
-2. Change a filter and watch the data area during the re-fetch.
-3. While loading, try to interact with the toolbar.</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
-2. The grand Totals indicator is hidden during loading.
-3. The toolbar stays interactive so filters can be changed mid-load.
-4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S16-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R4)</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>A load failure shows the inline could-not-load message with a Retry</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>SBR — Loading, Empty &amp; Error States</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.
-2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>1. Set several non-default filters.
-2. Force a load/re-fetch failure and read the data area.
-3. Restore the network and click "Retry".</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
-2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
-3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S16-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R5; §7)</t>
@@ -5450,14 +5457,13 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every toolbar control is visible and operable on touch.
+          <t>1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S17-R1, S17-R2, S17-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S17-R1, S17-R2, S17-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5503,14 +5509,13 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
+          <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S17-R4, S17-R5, S10-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S17-R4, S17-R5, S10-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5556,13 +5561,16 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each of these interactive controls presents a touch target of at least 44×44 px.
+          <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S17-R6, S17-N1, S18-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the expand/collapse chevrons measure 22 by 22 pixels, half the size they should be. The three-dot button and the Show Unassigned switch are both correctly 44 pixels tall. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8979
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S17-R6, S17-N1, S18-R9), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8979)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5609,18 +5617,21 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
+          <t>1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
 2. The data area sits on the standard blue-grey page background and runs edge-to-edge against the side navigation — there is no strip of empty space down either side.
 3. A thin horizontal separator line sits between the toolbar and the column headers.
 4. Column-header cells and all body cells render on white; the pinned Subtotal column matches the row background (not a contrasting strip); the grand Totals indicator renders on the white card surface with a thin top border.
 5. Row types are told apart by how heavy and what colour their text is, not by a different background colour.
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the table is not white. Every heading cell and every data row is the same pale grey as the page behind it, so the table does not read as a separate white surface. Two things are also out of line: the report title starts well to the left of the first column of data, and the Location filter stops short of the right-hand edge of the table. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8980
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8980)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5672,7 +5683,7 @@
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R8).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S18-R8), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5721,16 +5732,19 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. ⋯ exports = "Report actions".
+          <t>1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
 3. Per-row chevron = "Expand {rep name}" when collapsed / "Collapse {rep name}" when expanded.
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: three of the five names are wrong. The three-dot download button reads "Export report" instead of "Report actions", the column button reads "Column Selection" instead of "Show or hide columns", and the top chevron reads "Expand all representatives" / "Collapse all representatives" instead of "Expand all reps" / "Collapse all reps". The per-row chevrons are correct - they read "Expand ZZAUTOTEST RepA" and "Collapse ZZAUTOTEST RepA". This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8975
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S18-R9), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8975)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5777,14 +5791,13 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
+          <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S18-R10), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5833,7 +5846,7 @@
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S18-R11, S18-R12).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S18-R11, S18-R12), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5889,7 +5902,7 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R1, S19-N1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S19-R1, S19-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
@@ -5943,7 +5956,7 @@
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R2, S19-R8).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S19-R2, S19-R8), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
@@ -5996,7 +6009,7 @@
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R3, S19-R4).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S19-R3, S19-R4), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6049,7 +6062,7 @@
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R5).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S19-R5), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6103,7 +6116,7 @@
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R6, S19-N2, S22-R3).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S19-R6, S19-N2, S22-R3), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -6158,7 +6171,7 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S19-R7, S19-E1), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
@@ -6209,14 +6222,13 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
+          <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S6-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S6-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6262,14 +6274,13 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
+          <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S11-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S11-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6315,14 +6326,13 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
+          <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S10-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S10-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6369,14 +6379,13 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
+          <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-R2a, S14-N2, S14-E3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - this part of the report is not built yet
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R2a, S14-N2, S14-E3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6423,15 +6432,17 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
+          <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S14-E2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8818)
-</t>
+What you should see today: the spreadsheet download works and produces a file, but the PDF download of the same view fails with a server error and no file arrives. It depends on how much is in the view, not on which report - filtered down to one or two rows the PDF downloads normally, and on a full unfiltered view of several thousand rows it fails every time. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8818
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-E2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6483,7 +6494,7 @@
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 17 (S13-R1, S13-R4).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S13-R1, S13-R4), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -1323,7 +1323,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>The Location column shows only with more than one location; rep rows Multiple</t>
+          <t>Location column: shown to any multi-location user; toggleable; rep rows Multiple</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1356,23 +1356,25 @@
 4. Expand that rep and read an invoice detail row's Location cell.
 5. Read the Location cell on the Unassigned summary row.
 6. Check that the pinned Subtotal column is still the rightmost column.
-7. Narrow to a single location and read the headers again.
-8. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
+7. Narrow the selection to a single location and read the headers again.
+8. Open the column selector, switch Location off, read the headers again, then switch it back on.
+9. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
+          <t>1. Because you have access to more than one location, a Location column is shown by default, positioned immediately after the Status column and before Inv. Hrs.
 2. A rep summary row whose invoices are all at one location shows that location's name.
 3. A rep summary row whose invoices span more than one location shows "Multiple".
 4. An invoice detail row shows that invoice's own exact location — never "Multiple".
 5. The Unassigned summary row follows the same rule as any rep summary row.
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
-7. With only one location involved the Location column is not shown.
-8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
-Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements are that the column-selection dropdown holds the seven metric columns only, and that Location is one of the columns you can switch on and off there. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S21-R7, S21-R8, S18-R13, S14-R20), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: its summary says it can be toggled there, while the requirement that governs the column says it appears only when the view spans more than one location and the dropdown holds the seven metric columns only. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+7. Narrowing the selection to a single location does NOT hide the column; it stays on screen.
+8. Switching Location off in the column selector removes it; switching it back on restores it in the same position.
+9. Whenever the column is shown on screen, all four downloads include it in the same position. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
+Note for the tester: whether this column appears depends on how many locations your login can reach, not on how many you have currently selected. Someone who can reach only one location never sees it at all. If it stays on screen after you narrow to a single location, that is correct.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S21-R7, S21-R8, S18-R13, S14-R20), read on 11 August 2026.
 Last checked against build v3.5-7168d14 on 8/6/2026.
 AUTOMATION: READY</t>
         </is>
@@ -1474,7 +1476,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
+          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When the Location column is shown — it is shown by default to anyone whose login can reach more than one location — it sits immediately after Status, making 13.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
@@ -1848,7 +1850,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
+          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when the Location column is shown it is inserted immediately after Status, so Inv. Hrs then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
@@ -4240,7 +4242,7 @@
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
-3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
+3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When the Location column is shown on screen a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
@@ -4294,7 +4296,7 @@
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
-2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, only when more than one location is in scope, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
+2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, whenever that column is shown on screen, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
@@ -4577,7 +4579,7 @@
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
-7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
+7. When the Location column is shown on screen the file also carries it, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
 What you should see today: the Summary spreadsheet arrives with only nine of the thirteen column headings - # Invoices, # Customers, Hrs Worked and Hrs Invoiced are all absent - and the file still ends with a Totals row that this version is not supposed to have. The Location column, the UTF-8 marker and the one-row-per-representative shape are all correct. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8880
 · If you see exactly that, mark this test FAILED and do not raise anything new.
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
@@ -4635,7 +4637,7 @@
 2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
-5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
+5. When the Location column is shown on screen the file also carries it immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 What you should see today: the Expanded spreadsheet puts Invoice # BEFORE Date instead of after it, and heads that column "Invoice Status" instead of "Status". Everything else in the heading row is right, including the Location column in its correct place after the status column. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8972
 · If you see exactly that, mark this test FAILED and do not raise anything new.
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -4757,7 +4757,8 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If a file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
 Scope note: this case covers the CSV only. The same rule applies to both PDF downloads (the Summary PDF grand-totals row aggregates Unassigned; the Expanded PDF gets its own top page-block), but PDF body structure is not observable by the automation suite — see the Deferred PDF-visual cases.
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification (S22-R2, S22-R4, S14-R19), read on 11 August 2026.</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S22-R2, S22-R4, S14-R19), read on 11 August 2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1390,37 +1390,87 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>Adjustments column appears between Parts Margin and Margin</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Rep Rows &amp; Tree</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A representative has an invoice carrying an invoice-level fee or discount in the selected date range.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Representative report.
+2. Look at the columns left to right.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1. The columns appear left-to-right: Date, Invoice, Customer, Status, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %, Subtotal (13 columns).
+2. "Adjustments" sits between "Parts Margin" and "Margin".
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9281, and the Sales By Representative report specification version 22 (S5-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>SV-9281 (SBR spec v22 2026-08-12 S5-R2 — 13-column order includes Adjustments between Parts Margin and Margin)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>A rep row appears only when the rep has a matching non-reversed invoice</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. Rep A has invoices in the current filtered view; rep B (sales-rep toggle on) has NONE; rep C has only a reversed invoice (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the summary rows.
 2. Look for reps B and C.
 3. Read the count in parentheses after rep A's name.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
@@ -1432,41 +1482,41 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>SV-8623 (SBR spec v15 2026-07-29 Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Row layout: 12 columns in order, blanks in position, bold summary rows</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep expanded.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Read a rep summary row cell by cell.
@@ -1474,7 +1524,7 @@
 4. Look for any cell whose content has shifted into a neighbouring column or wrapped; check the desktop Totals row's leading cells.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When the Location column is shown — it is shown by default to anyone whose login can reach more than one location — it sits immediately after Status, making 13.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
@@ -1491,49 +1541,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-9001)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>SV-8623; SV-8638 (SBR spec v15 2026-07-29 Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a + Story 21 S21-R7 — plus the Location column after Status)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>A toggled-off or deleted contributor still appears; tagged (Inactive)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. Rep A has matching invoices; you then turn rep A's sales-rep toggle OFF (restore afterwards).
 2. If a rep whose staff record was DELETED but who has invoices in range exists (or can be produced), note it for step 3.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Refresh the report and find rep A's row.
 2. Read the name, tag, metrics, and position in the A→Z order; try expanding the row.
 3. If a deleted-rep contributor exists, read that row's name and sort position.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
@@ -1545,47 +1595,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SV-8623 (SBR spec v15 2026-07-29 Story 5 S5-R9; §3 Key Decisions; §4 Snapshot)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Expanding a rep loads its invoices on demand with a row-level spinner</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. A rep with several matching invoices is on the report.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron in the rep's Date cell and watch the row.
 2. Read a detail row left to right.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
@@ -1596,48 +1646,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R1; S6-R2; S6-R3; S6-E1)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>The header chevron expands every visible rep and its glyph tracks state</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. Several reps are on the report, all collapsed.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Look at the header-row chevron's glyph.
 2. Click it; watch the rep rows and the glyph.
 3. Click it again.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
@@ -1648,47 +1698,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Each invoice appears under exactly one rep or the Unassigned row</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. A known ZZAUTOTEST invoice set exists across two reps plus at least one unassigned invoice; Show Unassigned is on.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Expand every rep and the Unassigned row.
 2. Search the expanded rows for each seeded invoice number.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
@@ -1698,48 +1748,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R7; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Expansion survives filter and sort changes within the session, resets on reload</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are on the report; one of them stops matching under a stricter filter you can apply and re-remove.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Expand both reps, then change the sort and a filter that keeps both matching; check the expansion.
 2. Apply the stricter filter that removes rep B, then remove it again; check rep B.
 3. Reload the page and check all rows.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
@@ -1750,47 +1800,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R8; S6-N1; Story 23 S23-R2)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Detail rows run newest first with a numeric invoice-number tie-break</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBR — Rep Rows &amp; Tree</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. One rep has invoices allowing the tie-breaks: two invoices on different dates; two on the same date with numeric parts like 999 and 1000; and if producible a P and an S invoice with the same numeric part on the same day (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep and read the detail rows top to bottom.
 2. Change the rep-row column sort and re-read the detail order.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
@@ -1806,49 +1856,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8974)</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R9; Story 11 S11-R2)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Status badge between Customer and Inv. Hrs; every detail row shows mapped text</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBR — Payment Status Badge</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist covering paid, overpaid, prepaid (zero balance), prepaid (balance owed), partially paid, and unpaid.
 2. The owning rep is expanded.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Locate the Status column relative to its neighbours.
 2. Read the badge on each seeded invoice's detail row.
 3. Look at a badge's vertical position in its cell, read the Status cell on a rep summary row, and check the status is readable from the badge text alone.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when the Location column is shown it is inserted immediately after Status, so Inv. Hrs then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
@@ -1860,47 +1910,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SV-8625 (SBR spec v15 2026-07-29 Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Badge colors use the canonical payment-status tokens in light and dark</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBR — Payment Status Badge</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows with all three badge values are visible; you can switch to dark mode.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Read the color treatment of each badge in light mode and compare with the badges on the application's invoice list.
 2. Switch to dark mode and compare again.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
@@ -1911,47 +1961,98 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SV-8625 (SBR spec v15 2026-07-29 Story 8 S8-R3; Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Adjustments is the signed net of invoice-level fees and discounts</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Inv. Hrs &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A representative has invoices with invoice-level fees and discounts in the selected date range.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Representative report.
+2. Read the Adjustments value on a rep row and an invoice detail row.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. Adjustments shows the signed net of invoice-level fees and discounts: fees count positive, discounts count negative.
+2. A line-level fee or discount stays folded into that line's Labor or Parts value.
+3. An invoice-level amount is never allocated into the Labor or Parts columns.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9281, and the Sales By Representative report specification version 22 (S5-R11), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>SV-9281 (SBR spec v22 2026-08-12 S5-R11 — signed net of invoice-level fees/discounts; never allocated into Labor/Parts)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs is hours invoiced minus hours worked; half-up to one decimal</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST work order exists with known billed labor-line hours and known technician clocked (timesheet) hours, invoiced under a rep.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Expand the rep and read the invoice's Inv. Hrs value; recalculate by hand.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
@@ -1965,42 +2066,42 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R1; S9-R2; §3)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs: +green, -red, 0.0 default on every row; rollups from unrounded deltas</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist under one rep with a positive, a negative, and a break-even labor delta (seed ZZAUTOTEST data).
 2. If producible, an invoice whose delta is tiny (e.g., +0.04) and one with a small negative delta (e.g., -0.5) also exist.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Read the three detail rows' Inv. Hrs values and colors.
 2. Read the rep summary row's and the Totals row's Inv. Hrs.
@@ -2008,7 +2109,7 @@
 4. Read the tiny-delta and small-negative invoices' Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
@@ -2024,47 +2125,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>No-labor-no-time invoices show 0.0; clocked-unbilled work shows negative</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice with no labor and no clocked time exists, AND an invoice whose work order has clocked technician hours but no billed labor line (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Read the parts-only invoice's Inv. Hrs cell.
 2. Read the clocked-but-unbilled invoice's Inv. Hrs cell.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
@@ -2078,48 +2179,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-N1)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Margin % to one decimal; em dash when Subtotal &lt;= 0; recomputed on rollups</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. A rep has two invoices with clearly different Margin % values; if producible, a row with Subtotal ≤ 0 also exists.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on both detail rows and on the rep's summary row; recompute the summary value as (total Margin ÷ total Subtotal) × 100.
 2. Read the Subtotal ≤ 0 row's Margin % cell.
 3. If a negative-margin row exists, read its format.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
@@ -2131,47 +2232,47 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8627 (SBR spec v15 2026-07-29 §3 Margin % definition; Story 10 S10-R5)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Money columns use the standardized labels and definitions</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known billed labor, billed parts, labor cost, parts cost, and tax.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Read the money column headers.
 2. Read that invoice's row values and recalculate each by hand.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
@@ -2184,47 +2285,47 @@
 </t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8623; SV-8582 (SBR spec v15 2026-07-29 S5-R2 = the authoritative 12-column left-to-right order; §3 definitions; §4 Terminology — S5-R2 CLOSES the money-label list; Location sits after Status [S21-R7] and is not a money column)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Negative dollar values render in accounting parentheses; money columns only</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. A row with a negative money value exists (e.g., a net credit/return invoice, or a negative Labor Margin from cost exceeding billed labor — seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Read the negative money cell.
 2. Read a negative Inv. Hrs cell and a negative Margin % cell for comparison.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
@@ -2235,46 +2336,46 @@
 </t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8593 (SBR spec §3 Key Decisions accounting parentheses — owned by the shared A5 report-shell formatter module: verbatim 'accounting-parens negatives')</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Half-up rounding at each precision; totals may differ by one last-decimal unit</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. Several invoices whose money values come from calculations that produce fractions of a cent sit under one rep — seed ZZAUTOTEST invoices whose amounts come from hours × rate or percentage-based lines that do not land on a whole cent (money fields themselves only take two decimals, so the sub-cent amounts must come from the math, not be typed in).</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Read the displayed per-invoice values, sum them by hand, and compare with the rep summary and Totals cells.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
@@ -2286,48 +2387,48 @@
 </t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (SBR spec §3 half-up rounding rule + round of unrounded rollups; CROSS-CUTTING display rule with no single owning story)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>A clock-record edit after invoicing updates Inv. Hrs; billed money stays put</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBR — Inv. Hrs &amp; Calculations</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoiced (not reversed, not void) work order exists with billed labor and clocked technician hours, and its invoice row is visible under its rep in the report.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Note the invoice row's Inv. Hrs value and its money columns.
 2. Edit a technician clock record on that work order (change its length), or delete one.
 3. Reload the report and re-read the same invoice row.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
@@ -2342,42 +2443,95 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8626 (SBR spec v15 2026-07-29 §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Every row ties out once Adjustments is included</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Subtotal &amp; Totals</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A representative has an invoice carrying an invoice-level fee or discount.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Representative report.
+2. On a rep row, add Labor Invoiced, Parts Invoiced and Adjustments and compare to Subtotal.
+3. Add Labor Margin, Parts Margin and Adjustments and compare to Margin.
+4. Repeat on an invoice detail row and the Totals row.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1. Labor Invoiced + Parts Invoiced + Adjustments equals Subtotal.
+2. Labor Margin + Parts Margin + Adjustments equals Margin.
+3. The ties hold on rep summary rows, invoice detail rows and the grand Totals indicator alike.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9281, and the Sales By Representative report specification version 22 (S5-R12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>SV-9281 (SBR spec v22 2026-08-12 S5-R12 — row ties out: Labor+Parts+Adjustments=Subtotal; LaborMargin+PartsMargin+Adjustments=Margin)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Subtotal: rightmost, pinned right, bold everywhere; header row sticky on scroll</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, narrow enough to force horizontal scrolling.
 2. Enough rows exist to also force vertical scrolling.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Confirm nothing renders to the right of Subtotal on any row type.
 2. Scroll horizontally and watch the Subtotal column on summary and detail rows.
@@ -2385,7 +2539,7 @@
 4. Scroll down through the rows and watch the header row; scroll right and watch the Subtotal header cell.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column on every row type.
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
@@ -2402,41 +2556,41 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8977)</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Desktop Totals row merges the identifier columns and sticks to the bottom</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. Desktop viewport (1024px or wider); several reps with known amounts are on the report; at least one rep is left collapsed.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the table and find the Totals row.
 2. Read its first cell and the per-metric cells.
@@ -2444,7 +2598,7 @@
 4. Empty the results with a no-data filter and look for the indicator; also watch during a re-fetch.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
@@ -2461,48 +2615,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8977)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5; S10-N1; Story 16 S16-R4)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Mobile shows a simplified totals bar below the table; Subtotal at right</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBR — Subtotal &amp; Totals</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data in a viewport below 1024px.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Find the totals bar and read it.
 2. Swipe the table horizontally and watch the bar.
 3. Scroll the page vertically and watch the bar.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
@@ -2518,47 +2672,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8978)</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5 (mobile branch) + Story 17 S17-R4 — S10-R5 CLOSES it in the spec's own words: "Totals" left and the grand Subtotal right "(no other metrics)")</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>All eight financial columns are sortable</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Several reps with differing values are on the report.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Click each financial column header in turn: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Click the Date, Invoice, Customer, and Status headers.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
@@ -2569,46 +2723,46 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R1; S11-R6)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Default order is plain A to Z by display name, case-insensitive</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. No remembered sort exists (first visit or cleared storage); contributing reps include an "(Inactive)"-tagged rep and mixed-case names.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the rep order top to bottom.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
@@ -2618,41 +2772,41 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R4; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>First header click sorts ascending; second descending; no third state</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Several reps are on the report in the A→Z default.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Click the Subtotal header once and read the order and the direction indicator.
 2. Click it again.
@@ -2660,7 +2814,7 @@
 4. Try to get back to the A→Z order using only the column headers.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
@@ -2672,47 +2826,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R5; Story 23 S23-R5)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders rep rows only; Unassigned stays pinned on top</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Show Unassigned is on with a populated Unassigned row; at least one rep is expanded.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Sort by a financial column.
 2. Read the Unassigned row's position, the expanded rep's detail rows, and their order.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
@@ -2723,47 +2877,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R2; Story 22 S22-R4)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Ties keep the A to Z order and an em-dash Margin % sorts as zero</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBR — Sorting</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. Two reps have equal values in a sortable column; if producible, one rep shows "—" in Margin % (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Sort by the column where the two reps tie and read their relative order.
 2. Sort by Margin % ascending and locate the "—" rep.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
@@ -2773,48 +2927,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R7)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Detail-row invoice number and customer name links navigate in the current tab</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. A rep row is expanded with at least one S and one P invoice visible.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Click a service invoice's number link and note the destination and tab.
 2. Go back, then click a parts invoice's number link.
 3. Click the customer name on a detail row.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
@@ -2825,48 +2979,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R1; S12-R2; S12-R3)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Browser back from a drilldown restores expansion and scroll; no reload</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. Non-default filters are set (date range, product type, invoice status, location, Show Unassigned on), two reps are expanded, and the table is scrolled partway down.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Click an invoice link, then press the browser back button; check every piece of state.
 2. Repeat via a customer-name link.
 3. Watch whether the report performs a full reload on back.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
@@ -2877,48 +3031,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R3a; Story 23 S23-R2)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Invoice links use theme-primary; customer links use the body color</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. Detail rows are visible; at least one invoice and one customer link have been clicked earlier; you can switch to dark mode.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Inspect an invoice-number link at rest, on hover, on keyboard focus, and after a click.
 2. Inspect a customer-name link the same way.
 3. Switch to dark mode and repeat.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
@@ -2930,47 +3084,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R4; S12-R5; S12-R6; S12-N3)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>An unavailable link destination shows the standard not-found state</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with detail rows visible; in another session the target invoice is reversed/deleted (and, for the customer leg, a customer record is made unavailable if the app allows).</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Without refreshing, click the now-unavailable invoice's link; read the destination, then press back.
 2. If producible, repeat for an unavailable customer record.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
@@ -2980,43 +3134,43 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-N1; S12-N2)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Invoice # and customer name when you cannot open what they point at</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBR — Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You need TWO sign-ins: one person who can open work orders, part sales and customers, and one person who can see reports but CANNOT open them. Ask whoever manages permissions to set the second one up, or set it up yourself in administration and put it back as you found it afterwards.
 3. On the Sales By Representative report you have expanded a representative so you can see the invoice rows underneath, each showing an Invoice # and a customer name.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as the person who CAN open them, click an Invoice # and note where it goes; come back and click a customer name and note where that goes.
 2. Sign in as the person who CANNOT open them and open the Sales By Representative report again.
@@ -3025,7 +3179,7 @@
 5. Write down exactly what happened in each case.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. For the person who CAN open them, the Invoice # takes you to the work order or the part sale, and the customer name takes you to the customer's record, both in the same browser tab.
 2. For the person who CANNOT open them, neither one takes them anywhere: the work order, the part sale and the customer record all stay out of reach.
@@ -3038,48 +3192,48 @@
 AUTOMATION: HOLD - waiting on one answer from the product owner about what these two values should look like, and it needs a second sign-in that cannot open work orders, part sales or customers</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8629 (SBR spec v17 2026-08-05 §2 expanded rows — a link is rendered only with permission to open the target; note S12-R1 and S12-R3 still read as though the links are always there)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Deactivate dialog: counted pluralized headline, reassurance, focus trap</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST rep "A" is active, toggle on, and assigned as sales representative to exactly 1 customer; ZZAUTOTEST rep "B" likewise to 3 customers.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Toggle rep B's active status off and read the dialog before confirming anything.
 2. Press Tab repeatedly and watch where focus goes; dismiss and watch where focus returns.
 3. Repeat step 1 for rep A (1 customer) and read the headline's noun.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
@@ -3091,41 +3245,41 @@
 </t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R3; S13-R4; S13-R12)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Type-YES gate: auto-focus; case-insensitive match; Enter submits</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Read the instruction text and check which element holds focus.
 2. Hover the disabled "Deactivate" button and read the tooltip.
@@ -3133,7 +3287,7 @@
 4. With a valid entry, press Enter.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
@@ -3146,41 +3300,41 @@
 </t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R6; S13-R7)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Cancel and X dismiss the Deactivate dialog; Escape and clicking outside do not</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Click the "Cancel" button and watch the dialog; then re-open it.
 2. Click the "X" close icon and watch the dialog; then re-open it.
@@ -3189,7 +3343,7 @@
 5. After each action, check the staff member's active status.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
@@ -3203,47 +3357,47 @@
 </t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Valid submit locks the dialog, then deactivates keeping assignments</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a ZZAUTOTEST rep with known customer assignments.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Type YES and submit; during the request try Cancel, X, and Escape.
 2. After success, check the staff member's status and each previously assigned customer's Sales Representative.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
@@ -3256,48 +3410,48 @@
 </t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>After deactivation: toggle unchanged, CSV shows No, report credit intact</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST rep with assignments AND matching invoices was just deactivated via the dialog flow.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Re-open the staff member and read the sales-representative toggle.
 2. Download the Sales Representative Assignments CSV and read the rep's rows.
 3. Open the report and find the rep's row.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The sales-representative toggle state is unchanged by the deactivation flow.
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
@@ -3309,48 +3463,48 @@
 </t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>No dialog: toggle off, no assignments, already inactive, or reactivation</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. ZZAUTOTEST staff member X is active WITHOUT the sales-representative toggle; ZZAUTOTEST rep Y (with assignments) is currently inactive; ZZAUTOTEST rep Z is active with the sales-representative toggle ON and NO customers assigned.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate X and watch for a dialog.
 2. Reactivate rep Y via the standard toggle and watch for a dialog; check Y's customer assignments afterwards.
 3. Deactivate rep Z (sales-representative toggle on, no assignments) and watch for a dialog.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
@@ -3363,48 +3517,48 @@
 </t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R2; S13-N2; S13-N3; S13-E3)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>A deactivation failure shows the error toast and leaves the status alone</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. The Deactivate dialog is open for a rep with assignments; you can force the request to fail (go offline just before submitting).</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Type YES, force the failure condition, and submit.
 2. Read the toast; check the staff member's active status.
 3. Dismiss, re-open the dialog, and look at the confirmation input.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
@@ -3416,48 +3570,48 @@
 </t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N5; §7)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>If the assignment pre-check fails, the warning dialog still opens</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBR — Staff Deactivation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-rep toggle on.
 2. You can force the pre-deactivation assignment check to fail (for example, cut the network exactly when toggling active off) — if not forceable, mark Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Toggle the staff member's active status off while forcing the check to fail.
 2. Read the dialog that opens.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
@@ -3468,47 +3622,47 @@
 </t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N4)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned sits between the column selector and the date picker, off</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. No remembered settings; at least one matching invoice with NO assigned rep exists (seed via a WO with no Sales Representative whose customer also has no rep).</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Find the "Show Unassigned" toggle in the toolbar and note its position and default state.
 2. With it off, look for an Unassigned row and check the grand Totals against the rep rows only.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
@@ -3518,41 +3672,41 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R1; S22-R2; Story 18 S18-R7.2)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Show Unassigned adds one top-pinned Unassigned row that acts like a rep row</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. Matching unassigned invoices exist; the grand Totals with the toggle off are noted.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Turn "Show Unassigned" on and read the new row and its position.
 2. Read the grand Totals indicator.
@@ -3560,7 +3714,7 @@
 4. Turn the toggle off again.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
@@ -3572,48 +3726,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>No empty Unassigned row is ever rendered</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBR — Show Unassigned</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: a filter set with NO matching unassigned invoices (but some rep rows).
 2. Scenario B: the Unassigned row is populated and expanded.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: turn Show Unassigned on and look for the row; then narrow so no reps match either and read the table.
 2. Scenario B: with the Unassigned row expanded, turn the toggle off, then back on.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
@@ -3623,41 +3777,90 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-N1; Story 6 S6-N2)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>The eight toggleable metric columns include Adjustments</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Column Selector</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Representative report.
+2. Open the column selector.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1. The eight toggleable columns are: Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %.
+2. "Adjustments" is one of the toggleable columns, between Parts Margin and Margin.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9281, and the Sales By Representative report specification version 22 (S20-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>SV-9281 (SBR spec v22 2026-08-12 S20-R2 — eight toggleable columns include Adjustments)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Column selector: seven metric toggles; five always-on columns cannot be hidden</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. No remembered column preference exists (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Click the column selector button in the toolbar.
 2. Read the toggle list.
@@ -3666,7 +3869,7 @@
 5. Hide all seven metric columns and read the table and the grand Totals indicator.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
@@ -3679,47 +3882,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1 — S20-R2/S20-R3 CLOSE the seven toggles and the five always-on columns; Location is automatic and in neither list [S21-R7])</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Toggling a column applies at once to summary; detail and Totals rows</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. A rep is expanded and the Totals indicator is visible.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Toggle "Parts Margin" off and immediately check the summary rows, detail rows, and the Totals row.
 2. Toggle it back on.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
@@ -3729,47 +3932,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R4; S20-R7)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Column visibility never affects the exports</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. Several metric columns are hidden via the column selector.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Download all four exports (Summary PDF, Expanded View PDF, Summary CSV, Expanded View CSV).
 2. Check each file's columns.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
 ---
@@ -3778,47 +3981,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R8)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Hiding the active sort column keeps the sort</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBR — Column Selector</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. The report is sorted by a metric column (e.g., Margin descending).</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Hide that column via the column selector and read the row order.
 2. Show the column again and look at its header.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
@@ -3828,48 +4031,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R9)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>All filter and view settings are restored before the first data fetch</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Set a custom date range, "Parts only," "Paid," a specific location set, Show Unassigned on, hide two metric columns, and sort by Margin descending.
 2. Leave the report and return; also try a full page reload.
 3. Watch what data loads first.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
@@ -3879,47 +4082,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R1; Story 20 S20-R5)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Expansion state and scroll position are not remembered and reset on reload</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Two reps are expanded and the table is scrolled partway.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Reload the page.
 2. Check the rows and the scroll position.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
@@ -3929,47 +4132,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R2; §2 Out of Scope)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>A stale saved value falls back to its default and never errors</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. Your saved settings include a location you are then un-assigned from (restore access afterwards).</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter, the data, and watch for any error.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
@@ -3984,47 +4187,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8976)</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R3)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>First visit or cleared storage yields all defaults; no server-side profile</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You have distinctive saved settings, then clear the browser's site data (or use a fresh profile).
 2. You are working in a known active location (the application's location switcher).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read every setting.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
@@ -4034,47 +4237,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R4; S23-N1; Story 2 S2-R4; S2-R7; Story 21 S21-R2)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>The A to Z default is its own saved value</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBR — Persistence</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You have never clicked a financial column header in this browser session/profile (the report is in the A→Z default).</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Change a few filters (no sort click), leave the report, and return.
 2. Read the row order and the headers.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
@@ -4084,48 +4287,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R5; Story 11 S11-R4)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>The ⋯ overflow menu lists exactly four download actions</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are on the Sales By Representative report.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ (three-dot) button in the report toolbar — it is the first control in the toolbar's action cluster.
 2. Click it and read the menu entries top to bottom.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
@@ -4135,36 +4338,36 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R1 + Story 17 S17-R3 (position) — S14-R1 CLOSES it in the spec's own words ("lists exactly four actions"); so the closed list IS the requirement)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>All four downloads respect filters, full result set, and active order</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps showing.
 2. Set a specific date range, Product Type, Invoice Status, and a location selection; turn Show Unassigned on.
@@ -4172,14 +4375,14 @@
 4. Leave at least one rep collapsed (do not expand it).</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Compare each file's rows against the on-screen result: which reps appear, which invoices are included, and the row order.
 3. Check where the Unassigned row sits in each file.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
@@ -4196,49 +4399,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8925)</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2; S14-R2a; S14-R20 + Story 21 S21-R6 + Story 22 S22-R4 — all four downloads honour the filters; the full result set and the active order; S14-R20 = the "Locations:" line in every export)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Summary PDF: one rolled-up row per rep with a recomputed grand totals row</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, one of them a toggled-off ("(Inactive)") contributor if one can be arranged.
 2. A date range is selected.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (PDF)" from the ⋯ menu and open the file.
 2. Read the top of the first page, the column headers, one rep row, and the last row.
 3. Compare the totals row's Margin % against the child rows.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
@@ -4251,41 +4454,41 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3; S14-R5; S14-R20; Story 2 S2-R5; §3 Margin % definition — Summary PDF; plus the automatic Location column in all four exports)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF: one page-block per rep with its own totals; no grand</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (PDF)" from the ⋯ menu and open the file.
 2. Check how each rep's section starts and what its table contains.
@@ -4293,7 +4496,7 @@
 4. Compare the order of one rep's invoices against the on-screen expanded order.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, whenever that column is shown on screen, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
@@ -4311,47 +4514,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8981)</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R6; S14-R8; S14-R20; Story 6 S6-R9 — Expanded PDF page-block per rep; plus the automatic Location column after Status)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF truncates invoice numbers longer than 18 characters</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. At least one invoice in the current view has an invoice number LONGER than 18 characters, and one has a number of 18 characters or fewer (seed data if needed).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Expand the rep on screen and read both invoice numbers.
 2. Download the Expanded View PDF and read the same two invoice numbers.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
@@ -4363,49 +4566,49 @@
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R7)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>PDF footer on every page, default-logo fallback, and deterministic PDF filenames</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. For the fallback check: the organization has NO configured logo (clear it in settings if permitted, and restore afterward).</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs and note each saved file's name.
 2. Scroll through every page of both PDFs and read the footer.
 3. With the organization logo not configured, download a PDF again and look at the header strip's logo region.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
@@ -4422,48 +4625,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8982)</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3a; S14-R4; S14-R11 — S14-R11 CLOSES both PDF filenames verbatim ("deterministic") and S14-R4 closes the footer string; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>PDFs render negative dollars in accounting parentheses, keep the (Inactive) tag</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. The current view includes at least one negative money value (for example, a net-credit/return invoice — seed one if needed) and, if arrangeable, one toggled-off "(Inactive)" contributor.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Download both PDFs.
 2. Find the negative money value in each and read how it is written.
 3. Read the rep names in both PDFs.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
@@ -4475,49 +4678,49 @@
 </t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R9; S14-R10)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>PDF body font steps down as the longest dollar value grows; no overflow</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).
 2. This test reads what is inside a downloaded PDF. Open the file in any PDF viewer and use the viewer's own text search (Ctrl+F) to find the text named below — that is enough. There is nothing to install.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Download the Summary PDF for a view whose longest positive dollar value is 9 characters or fewer; note the body text size (a relative comparison across files is enough).
 2. Repeat for views whose longest positive value is 10, 11, and 12-or-more characters (as far as seedable).
 3. In each file, check whether any value overflows or wraps its column.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
@@ -4529,41 +4732,41 @@
 </t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R12; S14-R13)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Summary CSV: file name, UTF-8 BOM, verbatim headers, one row per rep</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing; one rep has invoices for the same customer more than once (to check de-duplication).</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
@@ -4571,7 +4774,7 @@
 4. For one rep, compare "# Invoices" with the on-screen (N) count, and "# Customers" with the number of DISTINCT customers across that rep's matching invoices.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal. On this build only nine of them arrive - Representative, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal - because # Invoices, # Customers, Hrs Worked and Hrs Invoiced are missing by mistake. Record what you see; the four missing columns are with the developers.
@@ -4590,48 +4793,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8880)</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R15; S14-R18; S14-R20 — Summary CSV headers; plus the automatic Location column in all four exports; S14-R15's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Expanded CSV: file name, verbatim headers, one row per invoice</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two reps showing, each with at least one invoice.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Expanded View (CSV)" from the ⋯ menu and note the saved file's name.
 2. Open the file in a text editor and read the header row.
 3. Compare the rows against the on-screen invoices (all reps, expanded).</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
@@ -4648,47 +4851,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8972)</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R16; S14-R20 — Expanded CSV headers; plus the automatic Location column after Status; S14-R16's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>CSV cells: plain numbers, signed Inv. Hrs, empty Margin %, (Inactive)</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded both report CSVs from a view that includes a negative money value, a rep whose Margin % shows "—" on screen (Subtotal ≤ 0), and an "(Inactive)" contributor (seed what is missing).</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open each CSV in a text editor (not a spreadsheet).
 2. Read a money cell, the negative value's cell, an Inv. Hrs cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Representative" cell.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
@@ -4696,8 +4899,7 @@
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
-What you should see today: in the spreadsheet the money arrives as text with a dollar sign and thousands separators, such as $11,176.88, and the columns come out in the file's own fixed order - Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Total Cost, Total Sell, Margin, Margin % - which is not the order on screen, does not put Total Cost last, and leaves out the Location column even when it is showing on screen. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
+What you should see today: the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
@@ -4707,41 +4909,41 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8823)</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>The Unassigned row appears in both CSV downloads only when the toggle is on</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set includes at least one invoice with no assigned sales representative (seed one if needed).</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Turn Show Unassigned ON and download Summary (CSV) and Expanded View (CSV).
 2. Find the Unassigned entry in each file.
@@ -4749,7 +4951,7 @@
 4. Search each file for the unassigned invoices.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle ON, the Summary CSV carries one rolled-up row whose "Sales Representative" cell reads the literal "Unassigned", sorted to the top of the data rows.
 2. With the toggle ON, the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned".
@@ -4761,49 +4963,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>A failed download shows the canonical error toast</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
 2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.
 3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a PDF download and watch the menu action while the file is being generated.
 2. Force a failure on a download (PDF or CSV) and read the toast.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
@@ -4815,47 +5017,47 @@
 </t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Over-cap Expanded View PDF is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. A filter set exists (or can be seeded) whose invoice detail rows exceed 10,000 — if this volume cannot be produced in the environment, mark Blocked-Env with the reason.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Apply the over-cap filter set.
 2. Choose "Download Expanded View (PDF)" and read the toast.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
@@ -4870,47 +5072,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2; §7 — 10k-row export cap; no truncated file; toast persists 120s; the toast STRING is the ONE suite-wide message ruled by Chris Ward 2026-07-31 Q2=A [newest-wins]; his SBR spec edit is pending)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>An empty-data export still generates with zeroed Summary PDF totals</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBR — Exports</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. The current filter set matches ZERO invoices (for example, a date range with no activity) — the report shows its empty state.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Download all four files from the ⋯ menu.
 2. Open each and inspect its contents.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
@@ -4923,49 +5125,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E3)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Report Name dropdown lists Sales Representative Assignments at the bottom</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Reports access.
 2. Note the current order of the Report Name dropdown entries before checking.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. In the Reports left sidebar, under the Accounting header, click the "Export Reports" entry — a dialog titled "Export Report" opens.
 2. Open the Report Name dropdown and read the list top to bottom.
 3. Select "Sales Representative Assignments" and look at the dialog body.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
@@ -4978,49 +5180,49 @@
 </t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R1; S15-R2)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Sales Representative Assignments CSV: file name, headers, success toast</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer in the organization has an assigned sales representative.
 2. The Export Report dialog is open with "Sales Representative Assignments" selected.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Click the Export action.
 2. Note the saved file's name and read the toast.
 3. Open the file in a text editor and read the header row.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
@@ -5037,41 +5239,41 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8983)</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R3; S15-R4; §7 — S15-R4 CLOSES the three headers; "Sales Rep"→"Sales Representative" per Chris Ward 2026-07-31 Q5 [newest-wins]; NOT one of the four report exports so S14-R20 adds no Location)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Assignments CSV: one row per assigned customer, sorted customer then rep</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. The organization has several customers with assigned reps and at least one customer with NO assigned rep (seed as needed).</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Representative Assignments CSV.
 2. Count the rows against the customers with assigned reps.
@@ -5079,7 +5281,7 @@
 4. Read the row order.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
@@ -5091,47 +5293,47 @@
 </t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R5; S15-R7; S15-R10)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>"Rep is active?" tracks the staff-active status, not the toggle</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. Arrange (and afterward restore): one assigned rep whose staff record is ACTIVE but whose sales-representative toggle is OFF, and one assigned rep whose staff record is INACTIVE but whose toggle is ON.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Representative Assignments CSV.
 2. Read the "Rep is active?" value on both reps' customer rows.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
@@ -5143,48 +5345,48 @@
 </t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R6; Story 13 S13-R11)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>A deleted rep record still exports one row from the stored name, marked No</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose assigned rep's staff record has been cleared or deleted while the customer still references it (seed and delete a throwaway ZZAUTOTEST rep if needed).</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Download the Sales Representative Assignments CSV.
 2. Find that customer's row and read its "Sales Representative" and "Rep is active?" cells.
 3. If two customers carry different stored name spellings for the same underlying rep, compare their rows.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Representative" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
@@ -5197,49 +5399,49 @@
 </t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R8; S15-R9)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Assignments export failure and nothing-to-export use the dialog's messages</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. For the empty path: no customer in the organization has an assigned rep (or use a state where the export yields zero rows).
 2. For the failure path: you can force a generation failure (for example, cut the network on Export) — if not forceable, mark that step Blocked with the reason.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, select "Sales Representative Assignments" in the Export Report dialog and click Export.
 2. Read the dialog warning and inspect any downloaded file.
 3. Force a generation failure and read the toast.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
@@ -5250,41 +5452,41 @@
 </t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R11; S15-N2; §7)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Empty state: verbatim message, no grand Totals, toolbar stays interactive</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter set that matches no invoices for any rep (for example, a date range with no activity), with Show Unassigned OFF or with no matching unassigned invoices either.
 2. Read the data area and look for the grand Totals indicator.
@@ -5292,7 +5494,7 @@
 4. Look at the toolbar, then change the date range to a period WITH activity.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
@@ -5309,49 +5511,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8973)</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R1; S16-R2; S16-R3; S16-N1; Story 2 S2-N1; Story 21 S21-N2; §7)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Loading shows a centered spinner over the data area and hides the Totals</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Reload the report and watch the data area during the initial load.
 2. Change a filter and watch the data area during the re-fetch.
 3. While loading, try to interact with the toolbar.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
@@ -5363,49 +5565,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R4)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>A load failure shows the inline could-not-load message with a Retry</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>SBR — Loading, Empty &amp; Error States</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Set several non-default filters.
 2. Force a load/re-fetch failure and read the data area.
 3. Restore the network and click "Retry".</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
@@ -5417,48 +5619,48 @@
 </t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R5; §7)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. Open the report on a phone-sized viewport (real device or browser device emulation, width under 1024px).</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Find and operate each toolbar control by touch: the ⋯ exports, the column selector, the Show Unassigned toggle, the date range picker, Product Type, Invoice Status, and Location.
 2. Look at how the controls are laid out.
 3. Widen the viewport to 1024px or more and compare.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
@@ -5469,48 +5671,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R1; S17-R2; S17-R3)</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>On a phone the table scrolls sideways with Subtotal pinned outside it</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a phone-sized viewport (under 1024px) with at least one rep row.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the data table sideways and watch the Subtotal column.
 2. Look below the table for the totals bar and swipe the table again.
 3. Tap a rep row's chevron.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
@@ -5521,48 +5723,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile))</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Touch targets are at least 44×44 px and touch users get no hover-only tooltips</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>SBR — Mobile</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. The report is open on a touch device or touch emulation (under 1024px).
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Measure (device emulation ruler/inspector) the touch targets of a row chevron, the Show Unassigned toggle, the ⋯ button, and — via the staff deactivation dialog if opened — the dialog's X.
 2. Tap-and-hold the icon controls and watch for tooltips.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
@@ -5576,41 +5778,41 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8979)</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R6; S17-N1; Story 18 S18-R9)</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Layout: white toolbar; blue-grey page; separator; edge-to-edge white table</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a desktop browser (light mode) with data showing.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar strip, at the space between its controls and the edges of the strip, and at how the title and the rightmost control line up with the table columns.
 2. Look at the page background around the data area, the line between the toolbar and the column headers, and the table's side edges.
@@ -5618,7 +5820,7 @@
 4. Open another report in the suite (for example Parts Velocity) side by side and compare.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
 2. The data area sits on the standard blue-grey page background and runs edge-to-edge against the side navigation — there is no strip of empty space down either side.
@@ -5637,41 +5839,41 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8980)</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Dark mode: page, toolbar, table; Totals switch to dark equivalents</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing, including at least one expanded rep (badges visible) and non-zero Inv. Hrs values.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page, toolbar, header, body cells, and the grand Totals indicator.
@@ -5679,7 +5881,7 @@
 4. Download a PDF while in dark mode and open it.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
@@ -5692,48 +5894,48 @@
 </t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Every icon-only control carries its specified accessible name</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the accessible name of: the ⋯ exports button, the column selector button, one rep row's chevron (collapsed, then expanded), and the header chevron.
 2. Open the staff deactivation dialog (Story 13 flow) and inspect its X close icon.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
@@ -5750,49 +5952,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8975)</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R9)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Chevrons and sortable headers are keyboard-operable and expose their state</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.
 2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Tab to a rep row's chevron; press Enter, then Space.
 2. Tab to a financial column header; press Enter, then Space.
 3. Inspect what state each control exposes to assistive technology.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
@@ -5803,47 +6005,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R10)</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>The subdued grey of the (N) count and (Inactive) tag meets WCAG AA contrast</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>SBR — Visual Conformance &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a rep row showing a (N) count and - if arrangeable - an "(Inactive)" tag.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Read the subdued-grey (N) count and the "(Inactive)" tag in light mode, then switch to dark mode and read them again.
 2. Review how Inv. Hrs, the status badges, and the links convey their meaning.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
@@ -5855,41 +6057,41 @@
 </t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R11; S18-R12 — subdued-grey (N) count and "(Inactive)" tag at ≥ 4.5:1 WCAG AA in both modes; nothing conveyed by colour alone; the ratio is a design-token property so the check is by-eye)</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Sales Representative selector shows on WO and Part Sale, not on imported</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. You have: an open standard Work Order, an open Part Sale WO, an imported Work Order, and a way to view a WO in History mode.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Open the standard Work Order and look at the left panel.
 2. Open the Part Sale WO and look at the left panel.
@@ -5897,7 +6099,7 @@
 4. View a WO in History mode and look for the field.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The left panel includes a "Sales Representative" selector on the standard Work Order.
 2. The left panel includes the same "Sales Representative" selector on the Part Sale WO.
@@ -5911,48 +6113,48 @@
 </t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R1; S19-N1)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Selector offers only reps whose sales-representative toggle is on</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member has the sales-representative toggle ON and at least one has it OFF. To arrange this: open Settings, go to Staff, edit the staff member, and use the sales-representative toggle there (restore both afterward).</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open a Work Order and open the "Sales Representative" selector.
 2. Search the option list for both staff members.
 3. Inspect the selector's accessible name.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
@@ -5965,48 +6167,48 @@
 </t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>A new WO opens with Sales Representative unassigned; a change saves at once</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. At least one staff member is offered as a sales representative.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Create a new Work Order (mark it ZZAUTOTEST) and read the Sales Representative field before touching it.
 2. Select a rep in the field, then navigate away WITHOUT any explicit save and reopen the WO.
 3. Repeat the unassigned-open check on a new Part Sale WO.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
@@ -6018,47 +6220,47 @@
 </t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R3; S19-R4)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>The Sales Representative selector is read-only when Invoiced or Paid</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. One Work Order is in "Invoiced" status and one is in "Paid" status (drive throwaway ZZAUTOTEST WOs into these states if needed).</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Open the Invoiced WO and try to change the Sales Representative field.
 2. Open the Paid WO and try the same.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.
@@ -6071,48 +6273,48 @@
 </t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R5)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Invoice credit snapshot: WO rep, else customer rep, else unassigned</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. Three throwaway ZZAUTOTEST setups: (a) a WO WITH a Sales Representative assigned; (b) a WO with NO rep whose customer HAS an assigned rep; (c) a WO with NO rep whose customer has NO assigned rep.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Invoice all three WOs.
 2. On the report (Show Unassigned on, filters covering the invoices), find each invoice and note which row it sits under.
 3. Go back to WO (a), change its Sales Representative to a different rep, and re-check the already-created invoice on the report.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Invoice (a) is credited to the WO's Sales Representative.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
@@ -6125,49 +6327,49 @@
 </t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Customer record shows a "Sales Representative" row; "Unassigned" when none</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>SBR — Work Order Sales Rep</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. One customer HAS an assigned sales representative and one customer has NONE.
 2. A Work Order exists whose bound Sales Representative can have their toggle turned off (arrange and restore afterward).</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Open the assigned customer's record and read the left-panel sidebar.
 2. Open the unassigned customer's record and read the same row.
 3. Turn the bound rep's sales-representative toggle OFF, reopen the Work Order, and read the Sales Representative selector; then open its option list.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
@@ -6180,50 +6382,50 @@
 </t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-8636 (SBR spec Story 19 S19-R7; S19-E1 — customer-card label RE-RULED to the full "Sales Representative" per the PRD companion video 2026-07-30 + Chris Ward answer 2026-07-31 Q5=A; the spec text still says "Sales Rep")</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>A rep's invoice detail rows are fetched from the server only on the first expand</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows, one with a large invoice count if seedable.
 2. The browser's network panel is open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note which requests deliver the summary rows.
 2. Expand one rep and watch the network panel; collapse and re-expand it.
 3. If a rep has many invoices, scroll/page through its expanded detail rows.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
@@ -6234,48 +6436,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R2)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Sorting is performed server-side and returns the first page</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several rep rows; the network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Click a financial column header and watch the network panel.
 2. Click the same header again (descending) and watch again.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
@@ -6286,48 +6488,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R5)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Grand totals are server-computed over the full filtered set</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Load the report with everything collapsed and inspect the summary response and the grand Totals indicator.
 2. Compare the grand totals against the full filtered result (for example, via the Summary CSV), not just the loaded rows.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
@@ -6338,49 +6540,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>All four exports are generated server-side against the active filters and sort</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Trigger each of the four downloads and observe the export requests and responses.
 2. Compare the delivered files against the active filters and sort.
 3. If forceable, fail one export server-side and check what (if anything) downloads.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
@@ -6391,49 +6593,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2a; S14-N2; S14-E3)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>The Expanded View PDF's 10,000-row cap is enforced server-side BEFORE generation</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. A filter set producing more than 10,000 invoice detail rows exists or can be seeded — otherwise mark Blocked-Env with the reason.
 2. The network panel is open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download Expanded View (PDF)" against the over-cap filter set and observe the export request/response.
 2. Check whether any file arrives.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
@@ -6448,50 +6650,50 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Deactivating a rep first runs a server pre-check returning the count</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>SBR — API</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-representative toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
 2. The network panel is open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. In staff administration, toggle that staff member's active status off and watch the network panel BEFORE the dialog appears.
 2. Read the pre-check response and compare it with the dialog's "{N} customer{s}" headline.
 3. Cancel the dialog (leave the staff member active).</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
@@ -6503,13 +6705,13 @@
 </t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R4)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Representative-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. Because you have access to more than one location, a Location column is shown by default, positioned immediately after the Status column and before Inv. Hrs.
+          <t>1. Because you have access to more than one location, a Location column is shown by default, positioned immediately after the Status column and before Labor Delta.
 2. A rep summary row whose invoices are all at one location shows that location's name.
 3. A rep summary row whose invoices span more than one location shows "Multiple".
 4. An invoice detail row shows that invoice's own exact location — never "Multiple".
@@ -1373,15 +1373,15 @@
 8. Switching Location off in the column selector removes it; switching it back on restores it in the same position.
 9. Whenever the column is shown on screen, all four downloads include it in the same position. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
 Note for the tester: whether this column appears depends on how many locations your login can reach, not on how many you have currently selected. Someone who can reach only one location never sees it at all. If it stays on screen after you narrow to a single location, that is correct.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S21-R7, S21-R8, S18-R13, S14-R20), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+Note for the tester about step 8: the column selector on this report lists the metric columns (Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %) and no Location entry, because the Location column is shown automatically rather than toggled. Step 8 therefore cannot be carried out as written: mark step 8 as blocked and record the other steps as normal.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S21-R7; S14-R20), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8638; SV-8631 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13; S14-R20 — per-row Location column; "Multiple" on a rep row spanning locations; position after Status; constant-width filter; S14-R20 = the same column in all four exports)</t>
+          <t>SV-8638 (SBR spec v22 2026-08-17 S21-R7; S14-R20; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Row layout: 12 columns in order, blanks in position, bold summary rows</t>
+          <t>Row layout: 13 columns in order, blanks in position, bold summary rows</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When the Location column is shown — it is shown by default to anyone whose login can reach more than one location — it sits immediately after Status, making 13.
+          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %, Subtotal (13 columns). When the Location column is shown — it is shown by default to anyone whose login can reach more than one location — it sits immediately after Status, making 14.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
@@ -1536,14 +1536,13 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-9001)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S5-R2), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8623; SV-8638 (SBR spec v15 2026-07-29 Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a + Story 21 S21-R7 — plus the Location column after Status)</t>
+          <t>SV-8622 (SBR spec v22 2026-08-17 S5-R2; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1638,17 +1637,16 @@
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
-2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
+2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Labor Delta and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S6-R1, S6-R2, S6-R3, S6-E1), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S6-R1, S6-R2, S6-R3, S6-E1), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R1; S6-R2; S6-R3; S6-E1)</t>
+          <t>SV-8624 (SBR spec v22 2026-08-17 S6-R1,S6-R2,S6-R3,S6-E1; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1867,7 +1865,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Status badge between Customer and Inv. Hrs; every detail row shows mapped text</t>
+          <t>Status badge between Customer and Labor Delta; every detail row shows mapped text</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1900,19 +1898,18 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when the Location column is shown it is inserted immediately after Status, so Inv. Hrs then follows Location.
+          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Labor Delta; when the Location column is shown it is inserted immediately after Status, so Labor Delta then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8625 (SBR spec v15 2026-07-29 Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6)</t>
+          <t>SV-8625 (SBR spec v22 2026-08-17 S8-R1,S8-R2,S8-R4,S8-R5,S8-R6,S8-N1,S18-R6; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2023,7 +2020,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs is hours invoiced minus hours worked; half-up to one decimal</t>
+          <t>Labor Delta is hours invoiced minus hours worked; half-up to one decimal</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2049,26 +2046,25 @@
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
-2. Expand the rep and read the invoice's Inv. Hrs value; recalculate by hand.</t>
+2. Expand the rep and read the invoice's Labor Delta value; recalculate by hand.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
+          <t>1. The column heading reads "Labor Delta".
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
-What you should see today: item 1 passes — the heading really does read "Inv. Hrs" with the period. Item 2 does not: the value reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+What you should see today: the Labor Delta value reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-R1, S9-R2), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S9-R1; S9-R2; §3), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R1; S9-R2; §3)</t>
+          <t>SV-8626 (SBR spec v22 2026-08-17 S9-R1; S9-R2; §3; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2077,7 +2073,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs: +green, -red, 0.0 default on every row; rollups from unrounded deltas</t>
+          <t>Labor Delta: +green, -red, 0.0 default on every row; rollups from unrounded deltas</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2103,10 +2099,10 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Read the three detail rows' Inv. Hrs values and colors.
-2. Read the rep summary row's and the Totals row's Inv. Hrs.
+          <t>1. Read the three detail rows' Labor Delta values and colors.
+2. Read the rep summary row's and the Totals row's Labor Delta.
 3. Recalculate the rollup as the rounded sum of the unrounded per-invoice deltas.
-4. Read the tiny-delta and small-negative invoices' Inv. Hrs.</t>
+4. Read the tiny-delta and small-negative invoices' Labor Delta.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2115,19 +2111,18 @@
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
-What you should see today: the Inv. Hrs column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+What you should see today: the Labor Delta column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2)</t>
+          <t>SV-8626 (SBR spec v22 2026-08-17 S9-R3,S9-R4,S9-R5,S9-R6,S9-E1,S9-E2; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2161,27 +2156,26 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Read the parts-only invoice's Inv. Hrs cell.
-2. Read the clocked-but-unbilled invoice's Inv. Hrs cell.</t>
+          <t>1. Read the parts-only invoice's Labor Delta cell.
+2. Read the clocked-but-unbilled invoice's Labor Delta cell.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
+          <t>1. The invoice with neither billed labor hours nor clocked hours shows Labor Delta 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
-What you should see today: the Inv. Hrs column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+What you should see today: the Labor Delta column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-N1), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S9-N1), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-N1)</t>
+          <t>SV-8626 (SBR spec v22 2026-08-17 S9-N1; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2274,20 +2268,18 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
-2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
-3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
+          <t>1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %, Subtotal.
+2. Subtotal = Labor Invoiced + Parts Invoiced + Adjustments, BEFORE tax.
+3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin + Adjustments.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S5-R2, S21-R7), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S5-R2; S5-R12; §3), both read on 17 August 2026. The Adjustments column (the signed net of invoice-level fees and discounts) is included in Subtotal and Margin so every row ties out (SV-9281, added 2026-08-12).
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8623; SV-8582 (SBR spec v15 2026-07-29 S5-R2 = the authoritative 12-column left-to-right order; §3 definitions; §4 Terminology — S5-R2 CLOSES the money-label list; Location sits after Status [S21-R7] and is not a money column)</t>
+          <t>SV-8622 (SBR spec v22 2026-08-17 S5-R2; S5-R12; §3; Adjustments column added to labels and tie-out per SV-9281)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2322,23 +2314,21 @@
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Read the negative money cell.
-2. Read a negative Inv. Hrs cell and a negative Margin % cell for comparison.</t>
+2. Read a negative Labor Delta cell and a negative Margin % cell for comparison.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
-2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (§3 Key Decisions accounting parentheses), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Subtotal).
+2. Labor Delta (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (§3 negative money columns), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8593 (SBR spec §3 Key Decisions accounting parentheses — owned by the shared A5 report-shell formatter module: verbatim 'accounting-parens negatives')</t>
+          <t>SV-8626 (SBR spec v22 2026-08-17 §3 negative money columns; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2377,19 +2367,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
+          <t>1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Labor Delta and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (§3 half), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (§3 half), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8582 (SBR spec §3 half-up rounding rule + round of unrounded rollups; CROSS-CUTTING display rule with no single owning story)</t>
+          <t>SV-8582 (SBR spec v22 2026-08-17 §3 half; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2398,7 +2386,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>A clock-record edit after invoicing updates Inv. Hrs; billed money stays put</t>
+          <t>A clock-record edit after invoicing updates Labor Delta; billed money stays put</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2423,29 +2411,28 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Note the invoice row's Inv. Hrs value and its money columns.
+          <t>1. Note the invoice row's Labor Delta value and its money columns.
 2. Edit a technician clock record on that work order (change its length), or delete one.
 3. Reload the report and re-read the same invoice row.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
+          <t>1. The worked-hours side updates — Labor Delta (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
-What you should see today: the Inv. Hrs column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
+What you should see today: the Labor Delta column reads 0.0 everywhere — on every representative row, on every invoice row underneath, and on the Totals row — no matter which date range you choose, even where the same row shows real money in Labor Invoiced. The hours themselves are not missing from the system: the Work In Progress report shows real quoted and worked hours for the same work orders. This is a known problem and it is already reported — see https://shopview.atlassian.net/browse/SV-8999.
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem — please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S9-R2), read on 11 August 2026.
-Last checked against build v3.5-f77875c on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8999)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S9-R2), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (SBR spec v15 2026-07-29 §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
+          <t>SV-8626 (SBR spec v22 2026-08-17 S9-R2; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2683,7 +2670,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>All eight financial columns are sortable</t>
+          <t>All nine financial columns are sortable</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2708,7 +2695,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1. Click each financial column header in turn: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+          <t>1. Click each financial column header in turn: Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %, Subtotal.
 2. Click the Date, Invoice, Customer, and Status headers.</t>
         </is>
       </c>
@@ -2718,14 +2705,13 @@
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S11-R1, S11-R6), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S11-R1; S11-R6), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R1; S11-R6)</t>
+          <t>SV-8628 (SBR spec v22 2026-08-17 S11-R1; S11-R6; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3837,7 +3823,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Column selector: seven metric toggles; five always-on columns cannot be hidden</t>
+          <t>Column selector: eight metric toggles; five always-on columns cannot be hidden</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3871,20 +3857,19 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
-2. On first visit all seven metric columns are visible.
+          <t>1. The dropdown lists the eight toggleable metric columns, each with a toggle switch: Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %.
+2. On first visit all eight metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
-4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
+4. With all eight metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S20-R2), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1 — S20-R2/S20-R3 CLOSE the seven toggles and the five always-on columns; Location is automatic and in neither list [S21-R7])</t>
+          <t>SV-8630 (SBR spec v22 2026-08-17 S20-R2; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4445,18 +4430,17 @@
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
-3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When the Location column is shown on screen a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
-4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
+3. With a single location in scope the columns are: Rep / Labor Delta / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Adjustments / Margin / Margin % / Subtotal. When the Location column is shown on screen a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
+4. Subtotal is bolded across the header, the body rows, and the grand totals row; Labor Delta keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. the Sales By Representative report specification version 18 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, so his answers are the only basis for it.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S14-R5), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed. Chris Ward's decision of 5 August 2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, governs the layout where the specification is silent (read on 11 August 2026).
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3; S14-R5; S14-R20; Story 2 S2-R5; §3 Margin % definition — Summary PDF; plus the automatic Location column in all four exports)</t>
+          <t>SV-8631 (SBR spec v22 2026-08-17 S14-R5; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4499,7 +4483,7 @@
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
-2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, whenever that column is shown on screen, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
+2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, whenever that column is shown on screen, carrying that invoice's own location) / Labor Delta / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Adjustments / Margin / Margin % / Subtotal.
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
@@ -4509,14 +4493,13 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R6, S14-R8, S14-R20, S6-R9), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8981)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S14-R6), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R6; S14-R8; S14-R20; Story 6 S6-R9 — Expanded PDF page-block per rep; plus the automatic Location column after Status)</t>
+          <t>SV-8631 (SBR spec v22 2026-08-17 S14-R6; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4777,25 +4760,24 @@
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
-2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal. On this build only nine of them arrive - Representative, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal - because # Invoices, # Customers, Hrs Worked and Hrs Invoiced are missing by mistake. Record what you see; the four missing columns are with the developers.
+2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %, Subtotal. On this build the four hours-related columns - # Invoices, # Customers, Hrs Worked and Hrs Invoiced - are missing by mistake. Record what you see; the four missing columns are with the developers.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 7. When the Location column is shown on screen the file also carries it, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
-What you should see today: the Summary spreadsheet arrives with only nine of the thirteen column headings - # Invoices, # Customers, Hrs Worked and Hrs Invoiced are all absent - and the file still ends with a Totals row that this version is not supposed to have. The Location column, the UTF-8 marker and the one-row-per-representative shape are all correct. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8880
+What you should see today: the Summary spreadsheet is missing four column headings - # Invoices, # Customers, Hrs Worked and Hrs Invoiced are all absent - and the file still ends with a Totals row that this version is not supposed to have. The Location column, the UTF-8 marker and the one-row-per-representative shape are all correct. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8880
 · If you see exactly that, mark this test FAILED and do not raise anything new.
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Sales By Representative report specification version 18 (S14-R15, S14-R18, S14-R20), read on 11 August 2026, differs, his decision is the authority.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8880)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S14-R15), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed. Chris Ward's decision of 5 August 2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, governs where the specification differs (read on 11 August 2026).
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R15; S14-R18; S14-R20 — Summary CSV headers; plus the automatic Location column in all four exports; S14-R15's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
+          <t>SV-8631 (SBR spec v22 2026-08-17 S14-R15; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4837,7 +4819,7 @@
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
-2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Adjustments, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When the Location column is shown on screen the file also carries it immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
@@ -4846,14 +4828,13 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Sales By Representative report specification version 18 (S14-R16, S14-R20), read on 11 August 2026, says something different, his decision is the later word and is the authority.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8972)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S14-R16), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed. Chris Ward's decision of 5 August 2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, governs where the specification differs (read on 11 August 2026).
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R16; S14-R20 — Expanded CSV headers; plus the automatic Location column after Status; S14-R16's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
+          <t>SV-8631 (SBR spec v22 2026-08-17 S14-R16; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4862,7 +4843,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>CSV cells: plain numbers, signed Inv. Hrs, empty Margin %, (Inactive)</t>
+          <t>CSV cells: plain numbers, signed Labor Delta, empty Margin %, (Inactive)</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4888,30 +4869,29 @@
       <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open each CSV in a text editor (not a spreadsheet).
-2. Read a money cell, the negative value's cell, an Inv. Hrs cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Representative" cell.</t>
+2. Read a money cell, the negative value's cell, an Labor Delta cell, the undefined Margin % cell, and the (Inactive) rep's "Sales Representative" cell.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
-2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
+2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Labor Delta carry their full stored precision; Labor Delta keeps its leading + or - sign.
 3. Margin % is a plain number to one decimal (for example, 45.2) with no % sign, and the cell is EMPTY where Margin % is undefined (Subtotal ≤ 0).
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
-5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
+5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Labor Delta conveys direction only by its sign).
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 What you should see today: the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-R17), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8823)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S14-R17), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
+          <t>SV-8631 (SBR spec v22 2026-08-17 S14-R17; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -5115,19 +5095,18 @@
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. All four downloads produce a FILE, not an error.
-2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
+2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Labor Delta columns and "—" for Margin %.
 3. The Expanded View PDF renders just the header strip with no per-rep blocks (it has no grand-totals row).
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Representative report specification version 18 (S14-E3), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S14-E3), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E3)</t>
+          <t>SV-8631 (SBR spec v22 2026-08-17 S14-E3; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -5136,38 +5115,91 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>CSV export repeats the PDF header's Product Type, status and Locations lines</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SBR — Exports</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Sales By Representative report is open with at least one filter narrowed (for example a chosen date/scope and one or more locations) so the PDF header would show more than one filter line.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the report as a PDF and read the filter-summary lines in its header area.
+2. Download the report as a CSV and open it in a plain text editor or spreadsheet.
+3. Compare the leading rows of the CSV (above the column-header row) with the PDF header lines.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1. The CSV carries the same filter-summary lines as the PDF header - the date range, the Product Type and payment-status filter lines, and the "Locations:" line - each as a leading metadata row above the column-header row.
+2. The lines appear verbatim (the same wording) and in the same order as in the PDF header.
+3. A CSV saved or forwarded later is never ambiguous about which filters produced it: every filter the PDF header names is present in the CSV.
+4. Note for the tester: this is the suite-wide rule that the CSV must name the same filters as the PDF. If your report shows no narrowed filters, widen or narrow one so at least one filter line appears, then compare again.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 22 (S14-R20a), both read on 17 August 2026. S14-R20a is the suite-wide rule (added 2026-08-12, SV-9283) that the CSV carries every filter-summary line the PDF header names.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>SV-8631 (SBR spec v22 2026-08-17 S14-R20a; suite-wide CSV filter-summary rule SV-9283)</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
           <t>Report Name dropdown lists Sales Representative Assignments at the bottom</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBR — Sales Rep Assignments Export</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Reports access.
 2. Note the current order of the Report Name dropdown entries before checking.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. In the Reports left sidebar, under the Accounting header, click the "Export Reports" entry — a dialog titled "Export Report" opens.
 2. Open the Report Name dropdown and read the list top to bottom.
 3. Select "Sales Representative Assignments" and look at the dialog body.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
@@ -5180,49 +5212,49 @@
 </t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R1; S15-R2)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Sales Representative Assignments CSV: file name, headers, success toast</t>
         </is>
 